--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E67F5B8-FC51-954F-8452-B5E9FE41C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888616D6-A447-A348-9176-28A0B5556B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.6.1.1" sheetId="5" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1319" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1318" uniqueCount="224">
   <si>
     <t/>
   </si>
@@ -854,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -879,7 +879,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -6918,11 +6917,11 @@
       <c r="B16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>76</v>
+      <c r="C16" s="9">
+        <v>0</v>
       </c>
       <c r="D16" s="9">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>76</v>
@@ -8107,7 +8106,7 @@
       </c>
       <c r="L11">
         <f>IF('Input Scenarios'!L32&lt;&gt;"", 'Input Scenarios'!L32,_xlfn.XLOOKUP($F11,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11">
         <f>'Input Scenarios'!M32</f>
@@ -8397,7 +8396,7 @@
       </c>
       <c r="L12">
         <f>IF('Input Scenarios'!L33&lt;&gt;"", 'Input Scenarios'!L33,_xlfn.XLOOKUP($F12,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M12">
         <f>'Input Scenarios'!M33</f>
@@ -8683,7 +8682,7 @@
       </c>
       <c r="L13">
         <f>IF('Input Scenarios'!L34&lt;&gt;"", 'Input Scenarios'!L34,_xlfn.XLOOKUP($F13,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="M13">
         <f>'Input Scenarios'!M34</f>
@@ -8969,7 +8968,7 @@
       </c>
       <c r="L14">
         <f>IF('Input Scenarios'!L35&lt;&gt;"", 'Input Scenarios'!L35,_xlfn.XLOOKUP($F14,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M14">
         <f>'Input Scenarios'!M35</f>
@@ -9831,7 +9830,7 @@
       </c>
       <c r="L17">
         <f>IF('Input Scenarios'!L38&lt;&gt;"", 'Input Scenarios'!L38,_xlfn.XLOOKUP($F17,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="M17">
         <f>'Input Scenarios'!M38</f>
@@ -10117,7 +10116,7 @@
       </c>
       <c r="L18">
         <f>IF('Input Scenarios'!L39&lt;&gt;"", 'Input Scenarios'!L39,_xlfn.XLOOKUP($F18,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M18">
         <f>'Input Scenarios'!M39</f>
@@ -10403,7 +10402,7 @@
       </c>
       <c r="L19">
         <f>IF('Input Scenarios'!L40&lt;&gt;"", 'Input Scenarios'!L40,_xlfn.XLOOKUP($F19,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M19">
         <f>'Input Scenarios'!M40</f>
@@ -10693,7 +10692,7 @@
       </c>
       <c r="L20">
         <f>IF('Input Scenarios'!L41&lt;&gt;"", 'Input Scenarios'!L41,_xlfn.XLOOKUP($F20,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="M20">
         <f>'Input Scenarios'!M41</f>
@@ -10979,7 +10978,7 @@
       </c>
       <c r="L21">
         <f>IF('Input Scenarios'!L42&lt;&gt;"", 'Input Scenarios'!L42,_xlfn.XLOOKUP($F21,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M21">
         <f>'Input Scenarios'!M42</f>
@@ -11265,7 +11264,7 @@
       </c>
       <c r="L22">
         <f>IF('Input Scenarios'!L43&lt;&gt;"", 'Input Scenarios'!L43,_xlfn.XLOOKUP($F22,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M22">
         <f>'Input Scenarios'!M43</f>
@@ -12127,7 +12126,7 @@
       </c>
       <c r="L25">
         <f>IF('Input Scenarios'!L46&lt;&gt;"", 'Input Scenarios'!L46,_xlfn.XLOOKUP($F25,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M25">
         <f>'Input Scenarios'!M46</f>
@@ -13351,9 +13350,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -13369,7 +13368,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -13493,7 +13492,7 @@
       </c>
       <c r="BS11">
         <f t="shared" si="13"/>
-        <v>5.3408457142857158</v>
+        <v>0</v>
       </c>
       <c r="BT11">
         <f>BI11*AT11*$BO11</f>
@@ -13517,11 +13516,11 @@
       </c>
       <c r="BY11">
         <f>SUM(BP11:BW11)</f>
-        <v>6.5481105077142869</v>
+        <v>1.2072647934285716</v>
       </c>
       <c r="BZ11">
         <f>SUM(BX11:BY14)/1000</f>
-        <v>3.5761535964000009E-2</v>
+        <v>1.2327387392571429E-2</v>
       </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.2">
@@ -13665,9 +13664,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -13683,7 +13682,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -13807,7 +13806,7 @@
       </c>
       <c r="BS12">
         <f t="shared" ref="BS12:BS26" si="20">BE12*AN12*$BO12</f>
-        <v>6.6918217142857142</v>
+        <v>0</v>
       </c>
       <c r="BT12">
         <f t="shared" ref="BT12:BT26" si="21">BI12*AT12*$BO12</f>
@@ -13831,7 +13830,7 @@
       </c>
       <c r="BY12">
         <f t="shared" ref="BY12:BY26" si="26">SUM(BP12:BW12)</f>
-        <v>8.2044661889142851</v>
+        <v>1.5126444746285714</v>
       </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.2">
@@ -13975,9 +13974,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -13993,7 +13992,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -14117,7 +14116,7 @@
       </c>
       <c r="BS13">
         <f t="shared" si="20"/>
-        <v>5.7007405714285717</v>
+        <v>0</v>
       </c>
       <c r="BT13">
         <f t="shared" si="21"/>
@@ -14141,7 +14140,7 @@
       </c>
       <c r="BY13">
         <f t="shared" si="26"/>
-        <v>6.9893573479714295</v>
+        <v>1.2886167765428573</v>
       </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.2">
@@ -14285,9 +14284,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -14303,7 +14302,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -14427,7 +14426,7 @@
       </c>
       <c r="BS14">
         <f t="shared" si="20"/>
-        <v>5.7007405714285717</v>
+        <v>0</v>
       </c>
       <c r="BT14">
         <f t="shared" si="21"/>
@@ -14451,7 +14450,7 @@
       </c>
       <c r="BY14">
         <f t="shared" si="26"/>
-        <v>6.9893573479714295</v>
+        <v>1.2886167765428573</v>
       </c>
     </row>
     <row r="15" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14595,9 +14594,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -14613,7 +14612,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -14737,7 +14736,7 @@
       </c>
       <c r="BS15">
         <f t="shared" si="20"/>
-        <v>1.5021128571428572</v>
+        <v>0</v>
       </c>
       <c r="BT15">
         <f t="shared" si="21"/>
@@ -14761,11 +14760,11 @@
       </c>
       <c r="BY15">
         <f t="shared" si="26"/>
-        <v>3.9763556026071432</v>
+        <v>2.4742427454642861</v>
       </c>
       <c r="BZ15">
         <f>SUM(BX15:BY18)/1000</f>
-        <v>1.8106230122357146E-2</v>
+        <v>1.1515375836642855E-2</v>
       </c>
       <c r="CA15"/>
       <c r="CB15"/>
@@ -14918,9 +14917,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -14936,7 +14935,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -15060,7 +15059,7 @@
       </c>
       <c r="BS16">
         <f t="shared" si="20"/>
-        <v>1.8820748571428572</v>
+        <v>0</v>
       </c>
       <c r="BT16">
         <f t="shared" si="21"/>
@@ -15084,7 +15083,7 @@
       </c>
       <c r="BY16">
         <f t="shared" si="26"/>
-        <v>4.982181509957142</v>
+        <v>3.1001066528142851</v>
       </c>
     </row>
     <row r="17" spans="1:87" x14ac:dyDescent="0.2">
@@ -15228,9 +15227,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -15246,7 +15245,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -15370,7 +15369,7 @@
       </c>
       <c r="BS17">
         <f t="shared" si="20"/>
-        <v>1.6033332857142859</v>
+        <v>0</v>
       </c>
       <c r="BT17">
         <f t="shared" si="21"/>
@@ -15394,7 +15393,7 @@
       </c>
       <c r="BY17">
         <f t="shared" si="26"/>
-        <v>4.2443037906107142</v>
+        <v>2.640970504896428</v>
       </c>
     </row>
     <row r="18" spans="1:87" x14ac:dyDescent="0.2">
@@ -15538,9 +15537,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -15556,7 +15555,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -15680,7 +15679,7 @@
       </c>
       <c r="BS18">
         <f t="shared" si="20"/>
-        <v>1.6033332857142859</v>
+        <v>0</v>
       </c>
       <c r="BT18">
         <f t="shared" si="21"/>
@@ -15704,7 +15703,7 @@
       </c>
       <c r="BY18">
         <f t="shared" si="26"/>
-        <v>4.2443037906107142</v>
+        <v>2.640970504896428</v>
       </c>
     </row>
     <row r="19" spans="1:87" x14ac:dyDescent="0.2">
@@ -15848,9 +15847,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -15866,7 +15865,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -15990,7 +15989,7 @@
       </c>
       <c r="BS19">
         <f t="shared" si="20"/>
-        <v>1.9759153029942862</v>
+        <v>0</v>
       </c>
       <c r="BT19">
         <f t="shared" si="21"/>
@@ -16014,11 +16013,11 @@
       </c>
       <c r="BY19">
         <f t="shared" si="26"/>
-        <v>9.3624498414482815</v>
+        <v>7.3865345384539953</v>
       </c>
       <c r="BZ19">
         <f>SUM(BX19:BY22)/1000</f>
-        <v>4.3680761604012297E-2</v>
+        <v>3.5010993696080864E-2</v>
       </c>
     </row>
     <row r="20" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16162,9 +16161,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -16180,7 +16179,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -16304,7 +16303,7 @@
       </c>
       <c r="BS20">
         <f t="shared" si="20"/>
-        <v>2.4757264368822853</v>
+        <v>0</v>
       </c>
       <c r="BT20">
         <f t="shared" si="21"/>
@@ -16328,7 +16327,7 @@
       </c>
       <c r="BY20">
         <f t="shared" si="26"/>
-        <v>11.73069743998278</v>
+        <v>9.2549710031004935</v>
       </c>
       <c r="BZ20"/>
       <c r="CA20"/>
@@ -16482,9 +16481,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -16500,7 +16499,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -16624,7 +16623,7 @@
       </c>
       <c r="BS21">
         <f t="shared" si="20"/>
-        <v>2.1090630840274289</v>
+        <v>0</v>
       </c>
       <c r="BT21">
         <f t="shared" si="21"/>
@@ -16648,7 +16647,7 @@
       </c>
       <c r="BY21">
         <f t="shared" si="26"/>
-        <v>9.9933419751009041</v>
+        <v>7.8842788910734765</v>
       </c>
     </row>
     <row r="22" spans="1:87" x14ac:dyDescent="0.2">
@@ -16792,9 +16791,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -16810,7 +16809,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -16934,7 +16933,7 @@
       </c>
       <c r="BS22">
         <f t="shared" si="20"/>
-        <v>2.1090630840274289</v>
+        <v>0</v>
       </c>
       <c r="BT22">
         <f t="shared" si="21"/>
@@ -16958,7 +16957,7 @@
       </c>
       <c r="BY22">
         <f t="shared" si="26"/>
-        <v>9.9933419751009041</v>
+        <v>7.8842788910734765</v>
       </c>
     </row>
     <row r="23" spans="1:87" x14ac:dyDescent="0.2">
@@ -17102,9 +17101,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -17120,7 +17119,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -17244,7 +17243,7 @@
       </c>
       <c r="BS23">
         <f t="shared" si="20"/>
-        <v>8.897314875428572</v>
+        <v>0</v>
       </c>
       <c r="BT23">
         <f t="shared" si="21"/>
@@ -17268,11 +17267,11 @@
       </c>
       <c r="BY23">
         <f t="shared" si="26"/>
-        <v>9.1195005996788563</v>
+        <v>0.22218572425028577</v>
       </c>
       <c r="BZ23">
         <f>SUM(BX23:BY26)/1000</f>
-        <v>4.3917732203060569E-2</v>
+        <v>4.8787840979177136E-3</v>
       </c>
     </row>
     <row r="24" spans="1:87" x14ac:dyDescent="0.2">
@@ -17416,9 +17415,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -17434,7 +17433,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -17558,7 +17557,7 @@
       </c>
       <c r="BS24">
         <f t="shared" si="20"/>
-        <v>11.147905793828571</v>
+        <v>0</v>
       </c>
       <c r="BT24">
         <f t="shared" si="21"/>
@@ -17582,7 +17581,7 @@
       </c>
       <c r="BY24">
         <f t="shared" si="26"/>
-        <v>11.426293774624458</v>
+        <v>0.27838798079588567</v>
       </c>
     </row>
     <row r="25" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17726,9 +17725,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -17744,7 +17743,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -17868,7 +17867,7 @@
       </c>
       <c r="BS25">
         <f t="shared" si="20"/>
-        <v>9.4968637179428566</v>
+        <v>0</v>
       </c>
       <c r="BT25">
         <f t="shared" si="21"/>
@@ -17892,7 +17891,7 @@
       </c>
       <c r="BY25">
         <f t="shared" si="26"/>
-        <v>9.7340215091214848</v>
+        <v>0.23715779117862854</v>
       </c>
       <c r="BZ25"/>
       <c r="CA25"/>
@@ -18046,9 +18045,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -18064,7 +18063,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -18188,7 +18187,7 @@
       </c>
       <c r="BS26">
         <f t="shared" si="20"/>
-        <v>9.4968637179428566</v>
+        <v>0</v>
       </c>
       <c r="BT26">
         <f t="shared" si="21"/>
@@ -18212,7 +18211,7 @@
       </c>
       <c r="BY26">
         <f t="shared" si="26"/>
-        <v>9.7340215091214848</v>
+        <v>0.23715779117862854</v>
       </c>
     </row>
     <row r="30" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18713,7 +18712,7 @@
       </c>
       <c r="L11">
         <f>IF('Input Scenarios'!L32&lt;&gt;"", 'Input Scenarios'!L32,_xlfn.XLOOKUP($F11,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11">
         <f>'Input Scenarios'!M32</f>
@@ -18807,9 +18806,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -18825,7 +18824,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -18873,59 +18872,59 @@
       </c>
       <c r="AZ11">
         <f>AY11*(1-L11)</f>
-        <v>1.8867199999999999E-3</v>
+        <v>1.8304000000000003E-3</v>
       </c>
       <c r="BA11">
         <f t="shared" ref="BA11:BA26" si="0">G11*AZ11*H11</f>
-        <v>471.68</v>
+        <v>457.6</v>
       </c>
       <c r="BB11">
         <f t="shared" ref="BB11:BE26" si="1">$BA11*M11</f>
-        <v>47.168000000000006</v>
+        <v>45.760000000000005</v>
       </c>
       <c r="BC11">
         <f t="shared" si="1"/>
-        <v>94.336000000000013</v>
+        <v>91.52000000000001</v>
       </c>
       <c r="BD11">
         <f t="shared" si="1"/>
-        <v>141.50399999999999</v>
+        <v>137.28</v>
       </c>
       <c r="BE11">
         <f t="shared" si="1"/>
-        <v>188.67200000000003</v>
+        <v>183.04000000000002</v>
       </c>
       <c r="BF11">
         <f t="shared" ref="BF11:BH26" si="2">(BB11*(1-AG11-AK11))</f>
-        <v>32.970432000000002</v>
+        <v>31.986240000000002</v>
       </c>
       <c r="BG11">
         <f t="shared" si="2"/>
-        <v>89.524864000000008</v>
+        <v>86.85248</v>
       </c>
       <c r="BH11">
         <f t="shared" si="2"/>
-        <v>84.760895999999988</v>
+        <v>82.230719999999991</v>
       </c>
       <c r="BI11">
         <f t="shared" ref="BI11:BM26" si="3">($BF11*Q11)+($BG11*V11)+($BH11*AA11)</f>
-        <v>16.485216000000001</v>
+        <v>15.993120000000001</v>
       </c>
       <c r="BJ11">
         <f t="shared" si="3"/>
-        <v>16.485216000000001</v>
+        <v>15.993120000000001</v>
       </c>
       <c r="BK11">
         <f t="shared" si="3"/>
-        <v>67.143648000000013</v>
+        <v>65.139359999999996</v>
       </c>
       <c r="BL11">
         <f t="shared" si="3"/>
-        <v>22.381216000000002</v>
+        <v>21.71312</v>
       </c>
       <c r="BM11">
         <f t="shared" si="3"/>
-        <v>84.760895999999988</v>
+        <v>82.230719999999991</v>
       </c>
       <c r="BN11">
         <f>IF(D11="", "", _xlfn.XLOOKUP('4.6.1.4'!D11, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -18937,27 +18936,27 @@
       </c>
       <c r="BP11">
         <f>BB11*AK11*$BO11</f>
-        <v>7.4121142857142872E-2</v>
+        <v>7.1908571428571447E-2</v>
       </c>
       <c r="BQ11">
         <f t="shared" ref="BQ11:BS26" si="4">BC11*AL11*$BO11</f>
-        <v>0.14824228571428574</v>
+        <v>0.14381714285714289</v>
       </c>
       <c r="BR11">
         <f t="shared" si="4"/>
-        <v>0.22236342857142855</v>
+        <v>0.2157257142857143</v>
       </c>
       <c r="BS11">
         <f t="shared" si="4"/>
-        <v>5.9296914285714299</v>
+        <v>0</v>
       </c>
       <c r="BT11">
         <f>BI11*AT11*$BO11</f>
-        <v>0.12952669714285717</v>
+        <v>0.12566022857142858</v>
       </c>
       <c r="BU11">
         <f t="shared" ref="BU11:BW26" si="5">BJ11*AU11*$BO11</f>
-        <v>0.25905339428571433</v>
+        <v>0.25132045714285717</v>
       </c>
       <c r="BV11">
         <f t="shared" si="5"/>
@@ -18969,15 +18968,15 @@
       </c>
       <c r="BX11">
         <f>BE11* BN11*BO11</f>
-        <v>1.7789074285714288</v>
+        <v>1.7258057142857144</v>
       </c>
       <c r="BY11">
         <f>SUM(BP11:BW11)</f>
-        <v>6.7629983771428588</v>
+        <v>0.80843211428571449</v>
       </c>
       <c r="BZ11">
         <f>SUM(BX11:BY14)/1000</f>
-        <v>3.3667075655714293E-2</v>
+        <v>1.0198313541428573E-2</v>
       </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.2">
@@ -19027,7 +19026,7 @@
       </c>
       <c r="L12">
         <f>IF('Input Scenarios'!L33&lt;&gt;"", 'Input Scenarios'!L33,_xlfn.XLOOKUP($F12,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M12">
         <f>'Input Scenarios'!M33</f>
@@ -19121,9 +19120,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -19139,7 +19138,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -19187,59 +19186,59 @@
       </c>
       <c r="AZ12">
         <f t="shared" ref="AZ12:AZ26" si="7">AY12*(1-L12)</f>
-        <v>2.0976000000000002E-3</v>
+        <v>2.0672000000000004E-3</v>
       </c>
       <c r="BA12">
         <f t="shared" si="0"/>
-        <v>524.40000000000009</v>
+        <v>516.80000000000007</v>
       </c>
       <c r="BB12">
         <f t="shared" si="1"/>
-        <v>52.440000000000012</v>
+        <v>51.680000000000007</v>
       </c>
       <c r="BC12">
         <f t="shared" si="1"/>
-        <v>104.88000000000002</v>
+        <v>103.36000000000001</v>
       </c>
       <c r="BD12">
         <f t="shared" si="1"/>
-        <v>157.32000000000002</v>
+        <v>155.04000000000002</v>
       </c>
       <c r="BE12">
         <f t="shared" si="1"/>
-        <v>209.76000000000005</v>
+        <v>206.72000000000003</v>
       </c>
       <c r="BF12">
         <f t="shared" si="2"/>
-        <v>36.655560000000008</v>
+        <v>36.124320000000004</v>
       </c>
       <c r="BG12">
         <f t="shared" si="2"/>
-        <v>99.531120000000016</v>
+        <v>98.088640000000012</v>
       </c>
       <c r="BH12">
         <f t="shared" si="2"/>
-        <v>94.234680000000012</v>
+        <v>92.868960000000015</v>
       </c>
       <c r="BI12">
         <f t="shared" si="3"/>
-        <v>18.327780000000004</v>
+        <v>18.062160000000002</v>
       </c>
       <c r="BJ12">
         <f t="shared" si="3"/>
-        <v>18.327780000000004</v>
+        <v>18.062160000000002</v>
       </c>
       <c r="BK12">
         <f t="shared" si="3"/>
-        <v>74.648340000000019</v>
+        <v>73.566480000000013</v>
       </c>
       <c r="BL12">
         <f t="shared" si="3"/>
-        <v>24.882780000000004</v>
+        <v>24.522160000000003</v>
       </c>
       <c r="BM12">
         <f t="shared" si="3"/>
-        <v>94.234680000000012</v>
+        <v>92.868960000000015</v>
       </c>
       <c r="BN12">
         <f>IF(D12="", "", _xlfn.XLOOKUP('4.6.1.4'!D12, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -19251,27 +19250,27 @@
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BP26" si="8">BB12*AK12*$BO12</f>
-        <v>8.2405714285714304E-2</v>
+        <v>8.1211428571428587E-2</v>
       </c>
       <c r="BQ12">
         <f t="shared" si="4"/>
-        <v>0.16481142857142861</v>
+        <v>0.16242285714285717</v>
       </c>
       <c r="BR12">
         <f t="shared" si="4"/>
-        <v>0.24721714285714289</v>
+        <v>0.24363428571428572</v>
       </c>
       <c r="BS12">
         <f t="shared" si="4"/>
-        <v>6.5924571428571435</v>
+        <v>0</v>
       </c>
       <c r="BT12">
         <f t="shared" ref="BT12:BT26" si="9">BI12*AT12*$BO12</f>
-        <v>0.14400398571428574</v>
+        <v>0.14191697142857143</v>
       </c>
       <c r="BU12">
         <f t="shared" si="5"/>
-        <v>0.28800797142857149</v>
+        <v>0.28383394285714286</v>
       </c>
       <c r="BV12">
         <f t="shared" si="5"/>
@@ -19283,11 +19282,11 @@
       </c>
       <c r="BX12">
         <f t="shared" ref="BX12:BX26" si="10">BE12* BN12*BO12</f>
-        <v>1.9777371428571433</v>
+        <v>1.9490742857142858</v>
       </c>
       <c r="BY12">
         <f t="shared" ref="BY12:BY26" si="11">SUM(BP12:BW12)</f>
-        <v>7.5189033857142871</v>
+        <v>0.91301948571428571</v>
       </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.2">
@@ -19337,7 +19336,7 @@
       </c>
       <c r="L13">
         <f>IF('Input Scenarios'!L34&lt;&gt;"", 'Input Scenarios'!L34,_xlfn.XLOOKUP($F13,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="M13">
         <f>'Input Scenarios'!M34</f>
@@ -19431,9 +19430,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -19449,7 +19448,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -19497,59 +19496,59 @@
       </c>
       <c r="AZ13">
         <f t="shared" si="7"/>
-        <v>1.98E-3</v>
+        <v>1.908E-3</v>
       </c>
       <c r="BA13">
         <f t="shared" si="0"/>
-        <v>495</v>
+        <v>476.99999999999994</v>
       </c>
       <c r="BB13">
         <f t="shared" si="1"/>
-        <v>49.5</v>
+        <v>47.699999999999996</v>
       </c>
       <c r="BC13">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>95.399999999999991</v>
       </c>
       <c r="BD13">
         <f t="shared" si="1"/>
-        <v>148.5</v>
+        <v>143.09999999999997</v>
       </c>
       <c r="BE13">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>190.79999999999998</v>
       </c>
       <c r="BF13">
         <f t="shared" si="2"/>
-        <v>34.600499999999997</v>
+        <v>33.342299999999994</v>
       </c>
       <c r="BG13">
         <f t="shared" si="2"/>
-        <v>93.950999999999993</v>
+        <v>90.534599999999983</v>
       </c>
       <c r="BH13">
         <f t="shared" si="2"/>
-        <v>88.951499999999996</v>
+        <v>85.716899999999981</v>
       </c>
       <c r="BI13">
         <f t="shared" si="3"/>
-        <v>17.300249999999998</v>
+        <v>16.671149999999997</v>
       </c>
       <c r="BJ13">
         <f t="shared" si="3"/>
-        <v>17.300249999999998</v>
+        <v>16.671149999999997</v>
       </c>
       <c r="BK13">
         <f t="shared" si="3"/>
-        <v>70.463249999999988</v>
+        <v>67.900949999999995</v>
       </c>
       <c r="BL13">
         <f t="shared" si="3"/>
-        <v>23.487749999999998</v>
+        <v>22.633649999999996</v>
       </c>
       <c r="BM13">
         <f t="shared" si="3"/>
-        <v>88.951499999999996</v>
+        <v>85.716899999999981</v>
       </c>
       <c r="BN13">
         <f>IF(D13="", "", _xlfn.XLOOKUP('4.6.1.4'!D13, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -19561,27 +19560,27 @@
       </c>
       <c r="BP13">
         <f t="shared" si="8"/>
-        <v>7.7785714285714291E-2</v>
+        <v>7.4957142857142861E-2</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="4"/>
-        <v>0.15557142857142858</v>
+        <v>0.14991428571428572</v>
       </c>
       <c r="BR13">
         <f t="shared" si="4"/>
-        <v>0.23335714285714285</v>
+        <v>0.22487142857142853</v>
       </c>
       <c r="BS13">
         <f t="shared" si="4"/>
-        <v>6.2228571428571424</v>
+        <v>0</v>
       </c>
       <c r="BT13">
         <f t="shared" si="9"/>
-        <v>0.13593053571428571</v>
+        <v>0.13098760714285712</v>
       </c>
       <c r="BU13">
         <f t="shared" si="5"/>
-        <v>0.27186107142857141</v>
+        <v>0.26197521428571424</v>
       </c>
       <c r="BV13">
         <f t="shared" si="5"/>
@@ -19593,11 +19592,11 @@
       </c>
       <c r="BX13">
         <f t="shared" si="10"/>
-        <v>1.8668571428571428</v>
+        <v>1.7989714285714282</v>
       </c>
       <c r="BY13">
         <f t="shared" si="11"/>
-        <v>7.0973630357142845</v>
+        <v>0.84270567857142853</v>
       </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.2">
@@ -19647,7 +19646,7 @@
       </c>
       <c r="L14">
         <f>IF('Input Scenarios'!L35&lt;&gt;"", 'Input Scenarios'!L35,_xlfn.XLOOKUP($F14,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M14">
         <f>'Input Scenarios'!M35</f>
@@ -19741,9 +19740,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -19759,7 +19758,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -19807,59 +19806,59 @@
       </c>
       <c r="AZ14">
         <f t="shared" si="7"/>
-        <v>1.472E-3</v>
+        <v>1.56032E-3</v>
       </c>
       <c r="BA14">
         <f t="shared" si="0"/>
-        <v>368</v>
+        <v>390.08000000000004</v>
       </c>
       <c r="BB14">
         <f t="shared" si="1"/>
-        <v>36.800000000000004</v>
+        <v>39.00800000000001</v>
       </c>
       <c r="BC14">
         <f t="shared" si="1"/>
-        <v>73.600000000000009</v>
+        <v>78.01600000000002</v>
       </c>
       <c r="BD14">
         <f t="shared" si="1"/>
-        <v>110.39999999999999</v>
+        <v>117.024</v>
       </c>
       <c r="BE14">
         <f t="shared" si="1"/>
-        <v>147.20000000000002</v>
+        <v>156.03200000000004</v>
       </c>
       <c r="BF14">
         <f t="shared" si="2"/>
-        <v>25.723200000000002</v>
+        <v>27.266592000000006</v>
       </c>
       <c r="BG14">
         <f t="shared" si="2"/>
-        <v>69.846400000000003</v>
+        <v>74.037184000000011</v>
       </c>
       <c r="BH14">
         <f t="shared" si="2"/>
-        <v>66.129599999999996</v>
+        <v>70.097375999999997</v>
       </c>
       <c r="BI14">
         <f t="shared" si="3"/>
-        <v>12.861600000000001</v>
+        <v>13.633296000000003</v>
       </c>
       <c r="BJ14">
         <f t="shared" si="3"/>
-        <v>12.861600000000001</v>
+        <v>13.633296000000003</v>
       </c>
       <c r="BK14">
         <f t="shared" si="3"/>
-        <v>52.384799999999998</v>
+        <v>55.527888000000004</v>
       </c>
       <c r="BL14">
         <f t="shared" si="3"/>
-        <v>17.461600000000001</v>
+        <v>18.509296000000003</v>
       </c>
       <c r="BM14">
         <f t="shared" si="3"/>
-        <v>66.129599999999996</v>
+        <v>70.097375999999997</v>
       </c>
       <c r="BN14">
         <f>IF(D14="", "", _xlfn.XLOOKUP('4.6.1.4'!D14, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -19871,27 +19870,27 @@
       </c>
       <c r="BP14">
         <f t="shared" si="8"/>
-        <v>5.7828571428571438E-2</v>
+        <v>6.1298285714285729E-2</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="4"/>
-        <v>0.11565714285714288</v>
+        <v>0.12259657142857146</v>
       </c>
       <c r="BR14">
         <f t="shared" si="4"/>
-        <v>0.17348571428571427</v>
+        <v>0.18389485714285714</v>
       </c>
       <c r="BS14">
         <f t="shared" si="4"/>
-        <v>4.6262857142857152</v>
+        <v>0</v>
       </c>
       <c r="BT14">
         <f t="shared" si="9"/>
-        <v>0.10105542857142857</v>
+        <v>0.10711875428571431</v>
       </c>
       <c r="BU14">
         <f t="shared" si="5"/>
-        <v>0.20211085714285715</v>
+        <v>0.21423750857142862</v>
       </c>
       <c r="BV14">
         <f t="shared" si="5"/>
@@ -19903,11 +19902,11 @@
       </c>
       <c r="BX14">
         <f t="shared" si="10"/>
-        <v>1.3878857142857144</v>
+        <v>1.4711588571428575</v>
       </c>
       <c r="BY14">
         <f t="shared" si="11"/>
-        <v>5.2764234285714302</v>
+        <v>0.6891459771428573</v>
       </c>
     </row>
     <row r="15" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -20051,9 +20050,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -20069,7 +20068,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -20193,7 +20192,7 @@
       </c>
       <c r="BS15">
         <f t="shared" si="4"/>
-        <v>1.323771428571429</v>
+        <v>0</v>
       </c>
       <c r="BT15">
         <f t="shared" si="9"/>
@@ -20217,11 +20216,11 @@
       </c>
       <c r="BY15">
         <f t="shared" si="11"/>
-        <v>4.4146387182857154</v>
+        <v>3.0908672897142857</v>
       </c>
       <c r="BZ15">
         <f>SUM(BX15:BY18)/1000</f>
-        <v>2.4019076914965007E-2</v>
+        <v>1.6883051297734285E-2</v>
       </c>
       <c r="CA15"/>
       <c r="CB15"/>
@@ -20374,9 +20373,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -20392,7 +20391,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -20516,7 +20515,7 @@
       </c>
       <c r="BS16">
         <f t="shared" si="4"/>
-        <v>2.6447142857142856</v>
+        <v>0</v>
       </c>
       <c r="BT16">
         <f t="shared" si="9"/>
@@ -20540,7 +20539,7 @@
       </c>
       <c r="BY16">
         <f t="shared" si="11"/>
-        <v>8.8198444478571414</v>
+        <v>6.1751301621428549</v>
       </c>
     </row>
     <row r="17" spans="1:87" x14ac:dyDescent="0.2">
@@ -20590,7 +20589,7 @@
       </c>
       <c r="L17">
         <f>IF('Input Scenarios'!L38&lt;&gt;"", 'Input Scenarios'!L38,_xlfn.XLOOKUP($F17,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="M17">
         <f>'Input Scenarios'!M38</f>
@@ -20684,9 +20683,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -20702,7 +20701,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -20750,59 +20749,59 @@
       </c>
       <c r="AZ17">
         <f t="shared" si="7"/>
-        <v>1.7443200000000002E-3</v>
+        <v>1.5408160000000002E-3</v>
       </c>
       <c r="BA17">
         <f t="shared" si="0"/>
-        <v>490.59000000000003</v>
+        <v>433.35450000000003</v>
       </c>
       <c r="BB17">
         <f t="shared" si="1"/>
-        <v>196.23600000000002</v>
+        <v>173.34180000000003</v>
       </c>
       <c r="BC17">
         <f t="shared" si="1"/>
-        <v>147.17699999999999</v>
+        <v>130.00635</v>
       </c>
       <c r="BD17">
         <f t="shared" si="1"/>
-        <v>98.118000000000009</v>
+        <v>86.670900000000017</v>
       </c>
       <c r="BE17">
         <f t="shared" si="1"/>
-        <v>49.059000000000005</v>
+        <v>43.335450000000009</v>
       </c>
       <c r="BF17">
         <f t="shared" si="2"/>
-        <v>137.16896400000002</v>
+        <v>121.16591820000002</v>
       </c>
       <c r="BG17">
         <f t="shared" si="2"/>
-        <v>139.67097299999998</v>
+        <v>123.37602614999999</v>
       </c>
       <c r="BH17">
         <f t="shared" si="2"/>
-        <v>58.772682000000003</v>
+        <v>51.915869100000009</v>
       </c>
       <c r="BI17">
         <f t="shared" si="3"/>
-        <v>104.30826462</v>
+        <v>92.138967081000004</v>
       </c>
       <c r="BJ17">
         <f t="shared" si="3"/>
-        <v>132.78799529999998</v>
+        <v>117.296062515</v>
       </c>
       <c r="BK17">
         <f t="shared" si="3"/>
-        <v>42.126963300000007</v>
+        <v>37.212150915000009</v>
       </c>
       <c r="BL17">
         <f t="shared" si="3"/>
-        <v>34.292241000000004</v>
+        <v>30.291479550000005</v>
       </c>
       <c r="BM17">
         <f t="shared" si="3"/>
-        <v>22.097154780000004</v>
+        <v>19.519153389000003</v>
       </c>
       <c r="BN17">
         <f>IF(D17="", "", _xlfn.XLOOKUP('4.6.1.4'!D17, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -20814,27 +20813,27 @@
       </c>
       <c r="BP17">
         <f t="shared" si="8"/>
-        <v>0.30837085714285717</v>
+        <v>0.2723942571428572</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="4"/>
-        <v>0.23127814285714285</v>
+        <v>0.20429569285714283</v>
       </c>
       <c r="BR17">
         <f t="shared" si="4"/>
-        <v>0.15418542857142858</v>
+        <v>0.1361971285714286</v>
       </c>
       <c r="BS17">
         <f t="shared" si="4"/>
-        <v>1.5418542857142858</v>
+        <v>0</v>
       </c>
       <c r="BT17">
         <f t="shared" si="9"/>
-        <v>0.81956493630000005</v>
+        <v>0.72394902706499997</v>
       </c>
       <c r="BU17">
         <f t="shared" si="5"/>
-        <v>2.0866684975714285</v>
+        <v>1.8432238395214284</v>
       </c>
       <c r="BV17">
         <f t="shared" si="5"/>
@@ -20846,11 +20845,11 @@
       </c>
       <c r="BX17">
         <f t="shared" si="10"/>
-        <v>0.15418542857142858</v>
+        <v>0.1361971285714286</v>
       </c>
       <c r="BY17">
         <f t="shared" si="11"/>
-        <v>5.1419221481571427</v>
+        <v>3.1800599451578568</v>
       </c>
     </row>
     <row r="18" spans="1:87" x14ac:dyDescent="0.2">
@@ -20900,7 +20899,7 @@
       </c>
       <c r="L18">
         <f>IF('Input Scenarios'!L39&lt;&gt;"", 'Input Scenarios'!L39,_xlfn.XLOOKUP($F18,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M18">
         <f>'Input Scenarios'!M39</f>
@@ -20994,9 +20993,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -21012,7 +21011,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -21060,59 +21059,59 @@
       </c>
       <c r="AZ18">
         <f t="shared" si="7"/>
-        <v>1.6769759999999999E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA18">
         <f t="shared" si="0"/>
-        <v>471.64949999999999</v>
+        <v>510.1515</v>
       </c>
       <c r="BB18">
         <f t="shared" si="1"/>
-        <v>188.65980000000002</v>
+        <v>204.06060000000002</v>
       </c>
       <c r="BC18">
         <f t="shared" si="1"/>
-        <v>141.49484999999999</v>
+        <v>153.04544999999999</v>
       </c>
       <c r="BD18">
         <f t="shared" si="1"/>
-        <v>94.329900000000009</v>
+        <v>102.03030000000001</v>
       </c>
       <c r="BE18">
         <f t="shared" si="1"/>
-        <v>47.164950000000005</v>
+        <v>51.015150000000006</v>
       </c>
       <c r="BF18">
         <f t="shared" si="2"/>
-        <v>131.87320020000001</v>
+        <v>142.63835940000001</v>
       </c>
       <c r="BG18">
         <f t="shared" si="2"/>
-        <v>134.27861264999999</v>
+        <v>145.24013204999997</v>
       </c>
       <c r="BH18">
         <f t="shared" si="2"/>
-        <v>56.503610100000003</v>
+        <v>61.116149700000001</v>
       </c>
       <c r="BI18">
         <f t="shared" si="3"/>
-        <v>100.28117339100001</v>
+        <v>108.467391627</v>
       </c>
       <c r="BJ18">
         <f t="shared" si="3"/>
-        <v>127.66137016499998</v>
+        <v>138.08270650499998</v>
       </c>
       <c r="BK18">
         <f t="shared" si="3"/>
-        <v>40.500542565000003</v>
+        <v>43.806709305000005</v>
       </c>
       <c r="BL18">
         <f t="shared" si="3"/>
-        <v>32.968300050000003</v>
+        <v>35.659589850000003</v>
       </c>
       <c r="BM18">
         <f t="shared" si="3"/>
-        <v>21.244036778999998</v>
+        <v>22.978243862999999</v>
       </c>
       <c r="BN18">
         <f>IF(D18="", "", _xlfn.XLOOKUP('4.6.1.4'!D18, Constants!$I$5:$I$6, Constants!$J$5:$J$6))</f>
@@ -21124,27 +21123,27 @@
       </c>
       <c r="BP18">
         <f t="shared" si="8"/>
-        <v>0.29646540000000005</v>
+        <v>0.32066665714285719</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="4"/>
-        <v>0.22234904999999996</v>
+        <v>0.24049999285714285</v>
       </c>
       <c r="BR18">
         <f t="shared" si="4"/>
-        <v>0.14823270000000002</v>
+        <v>0.1603333285714286</v>
       </c>
       <c r="BS18">
         <f t="shared" si="4"/>
-        <v>1.4823270000000002</v>
+        <v>0</v>
       </c>
       <c r="BT18">
         <f t="shared" si="9"/>
-        <v>0.78792350521500021</v>
+        <v>0.85224379135500006</v>
       </c>
       <c r="BU18">
         <f t="shared" si="5"/>
-        <v>2.00610724545</v>
+        <v>2.1698711022214283</v>
       </c>
       <c r="BV18">
         <f t="shared" si="5"/>
@@ -21156,11 +21155,11 @@
       </c>
       <c r="BX18">
         <f t="shared" si="10"/>
-        <v>0.14823270000000002</v>
+        <v>0.1603333285714286</v>
       </c>
       <c r="BY18">
         <f t="shared" si="11"/>
-        <v>4.9434049006650005</v>
+        <v>3.743614872147857</v>
       </c>
     </row>
     <row r="19" spans="1:87" x14ac:dyDescent="0.2">
@@ -21210,7 +21209,7 @@
       </c>
       <c r="L19">
         <f>IF('Input Scenarios'!L40&lt;&gt;"", 'Input Scenarios'!L40,_xlfn.XLOOKUP($F19,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M19">
         <f>'Input Scenarios'!M40</f>
@@ -21304,9 +21303,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -21322,7 +21321,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -21370,11 +21369,11 @@
       </c>
       <c r="AZ19">
         <f t="shared" si="7"/>
-        <v>1.7089919999999999E-3</v>
+        <v>1.6099199999999999E-3</v>
       </c>
       <c r="BA19">
         <f t="shared" si="0"/>
-        <v>632.26380729599998</v>
+        <v>595.61083295999993</v>
       </c>
       <c r="BB19">
         <f t="shared" si="1"/>
@@ -21382,7 +21381,7 @@
       </c>
       <c r="BC19">
         <f t="shared" si="1"/>
-        <v>569.03742656639997</v>
+        <v>536.04974966399993</v>
       </c>
       <c r="BD19">
         <f t="shared" si="1"/>
@@ -21390,7 +21389,7 @@
       </c>
       <c r="BE19">
         <f t="shared" si="1"/>
-        <v>63.226380729600002</v>
+        <v>59.561083295999993</v>
       </c>
       <c r="BF19">
         <f t="shared" si="2"/>
@@ -21398,7 +21397,7 @@
       </c>
       <c r="BG19">
         <f t="shared" si="2"/>
-        <v>540.01651781151349</v>
+        <v>508.71121243113589</v>
       </c>
       <c r="BH19">
         <f t="shared" si="2"/>
@@ -21410,7 +21409,7 @@
       </c>
       <c r="BJ19">
         <f t="shared" si="3"/>
-        <v>540.01651781151349</v>
+        <v>508.71121243113589</v>
       </c>
       <c r="BK19">
         <f t="shared" si="3"/>
@@ -21438,7 +21437,7 @@
       </c>
       <c r="BQ19">
         <f t="shared" si="4"/>
-        <v>0.89420167031862852</v>
+        <v>0.84236389232914277</v>
       </c>
       <c r="BR19">
         <f t="shared" si="4"/>
@@ -21446,7 +21445,7 @@
       </c>
       <c r="BS19">
         <f t="shared" si="4"/>
-        <v>1.987114822930286</v>
+        <v>0</v>
       </c>
       <c r="BT19">
         <f t="shared" si="9"/>
@@ -21454,7 +21453,7 @@
       </c>
       <c r="BU19">
         <f t="shared" si="5"/>
-        <v>8.4859738513237843</v>
+        <v>7.9940333382035638</v>
       </c>
       <c r="BV19">
         <f t="shared" si="5"/>
@@ -21466,15 +21465,15 @@
       </c>
       <c r="BX19">
         <f t="shared" si="10"/>
-        <v>0.59613444687908568</v>
+        <v>0.56157592821942848</v>
       </c>
       <c r="BY19">
         <f t="shared" si="11"/>
-        <v>11.367290344572698</v>
+        <v>8.8363972305327074</v>
       </c>
       <c r="BZ19">
         <f>SUM(BX19:BY22)/1000</f>
-        <v>4.8663939728116265E-2</v>
+        <v>4.0435288549060339E-2</v>
       </c>
     </row>
     <row r="20" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -21524,7 +21523,7 @@
       </c>
       <c r="L20">
         <f>IF('Input Scenarios'!L41&lt;&gt;"", 'Input Scenarios'!L41,_xlfn.XLOOKUP($F20,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="M20">
         <f>'Input Scenarios'!M41</f>
@@ -21618,9 +21617,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -21636,7 +21635,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -21684,11 +21683,11 @@
       </c>
       <c r="AZ20">
         <f t="shared" si="7"/>
-        <v>1.7221600000000004E-3</v>
+        <v>2.1292159999999997E-3</v>
       </c>
       <c r="BA20">
         <f t="shared" si="0"/>
-        <v>637.13548008000009</v>
+        <v>787.7311390079999</v>
       </c>
       <c r="BB20">
         <f t="shared" si="1"/>
@@ -21696,7 +21695,7 @@
       </c>
       <c r="BC20">
         <f t="shared" si="1"/>
-        <v>573.42193207200012</v>
+        <v>708.95802510719989</v>
       </c>
       <c r="BD20">
         <f t="shared" si="1"/>
@@ -21704,7 +21703,7 @@
       </c>
       <c r="BE20">
         <f t="shared" si="1"/>
-        <v>63.713548008000011</v>
+        <v>78.773113900799999</v>
       </c>
       <c r="BF20">
         <f t="shared" si="2"/>
@@ -21712,7 +21711,7 @@
       </c>
       <c r="BG20">
         <f t="shared" si="2"/>
-        <v>544.17741353632812</v>
+        <v>672.8011658267327</v>
       </c>
       <c r="BH20">
         <f t="shared" si="2"/>
@@ -21724,7 +21723,7 @@
       </c>
       <c r="BJ20">
         <f t="shared" si="3"/>
-        <v>544.17741353632812</v>
+        <v>672.8011658267327</v>
       </c>
       <c r="BK20">
         <f t="shared" si="3"/>
@@ -21752,7 +21751,7 @@
       </c>
       <c r="BQ20">
         <f t="shared" si="4"/>
-        <v>0.90109160754171447</v>
+        <v>1.1140768965970282</v>
       </c>
       <c r="BR20">
         <f t="shared" si="4"/>
@@ -21760,7 +21759,7 @@
       </c>
       <c r="BS20">
         <f t="shared" si="4"/>
-        <v>2.0024257945371433</v>
+        <v>0</v>
       </c>
       <c r="BT20">
         <f t="shared" si="9"/>
@@ -21768,7 +21767,7 @@
       </c>
       <c r="BU20">
         <f t="shared" si="5"/>
-        <v>8.5513593555708702</v>
+        <v>10.5725897487058</v>
       </c>
       <c r="BV20">
         <f t="shared" si="5"/>
@@ -21780,11 +21779,11 @@
       </c>
       <c r="BX20">
         <f t="shared" si="10"/>
-        <v>0.6007277383611429</v>
+        <v>0.74271793106468564</v>
       </c>
       <c r="BY20">
         <f t="shared" si="11"/>
-        <v>11.454876757649728</v>
+        <v>11.686666645302829</v>
       </c>
       <c r="BZ20"/>
       <c r="CA20"/>
@@ -21844,7 +21843,7 @@
       </c>
       <c r="L21">
         <f>IF('Input Scenarios'!L42&lt;&gt;"", 'Input Scenarios'!L42,_xlfn.XLOOKUP($F21,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M21">
         <f>'Input Scenarios'!M42</f>
@@ -21938,9 +21937,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -21956,7 +21955,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -22004,11 +22003,11 @@
       </c>
       <c r="AZ21">
         <f t="shared" si="7"/>
-        <v>1.2959999999999998E-3</v>
+        <v>1.3737599999999999E-3</v>
       </c>
       <c r="BA21">
         <f t="shared" si="0"/>
-        <v>479.47204799999992</v>
+        <v>508.24037087999994</v>
       </c>
       <c r="BB21">
         <f t="shared" si="1"/>
@@ -22016,7 +22015,7 @@
       </c>
       <c r="BC21">
         <f t="shared" si="1"/>
-        <v>431.52484319999991</v>
+        <v>457.41633379199993</v>
       </c>
       <c r="BD21">
         <f t="shared" si="1"/>
@@ -22024,7 +22023,7 @@
       </c>
       <c r="BE21">
         <f t="shared" si="1"/>
-        <v>47.947204799999994</v>
+        <v>50.824037087999997</v>
       </c>
       <c r="BF21">
         <f t="shared" si="2"/>
@@ -22032,7 +22031,7 @@
       </c>
       <c r="BG21">
         <f t="shared" si="2"/>
-        <v>409.51707619679991</v>
+        <v>434.08810076860789</v>
       </c>
       <c r="BH21">
         <f t="shared" si="2"/>
@@ -22044,7 +22043,7 @@
       </c>
       <c r="BJ21">
         <f t="shared" si="3"/>
-        <v>409.51707619679991</v>
+        <v>434.08810076860789</v>
       </c>
       <c r="BK21">
         <f t="shared" si="3"/>
@@ -22072,7 +22071,7 @@
       </c>
       <c r="BQ21">
         <f t="shared" si="4"/>
-        <v>0.67811046788571416</v>
+        <v>0.71879709595885699</v>
       </c>
       <c r="BR21">
         <f t="shared" si="4"/>
@@ -22080,7 +22079,7 @@
       </c>
       <c r="BS21">
         <f t="shared" si="4"/>
-        <v>1.5069121508571426</v>
+        <v>0</v>
       </c>
       <c r="BT21">
         <f t="shared" si="9"/>
@@ -22088,7 +22087,7 @@
       </c>
       <c r="BU21">
         <f t="shared" si="5"/>
-        <v>6.4352683402354272</v>
+        <v>6.8213844406495525</v>
       </c>
       <c r="BV21">
         <f t="shared" si="5"/>
@@ -22100,11 +22099,11 @@
       </c>
       <c r="BX21">
         <f t="shared" si="10"/>
-        <v>0.45207364525714278</v>
+        <v>0.47919806397257136</v>
       </c>
       <c r="BY21">
         <f t="shared" si="11"/>
-        <v>8.6202909589782841</v>
+        <v>7.5401815366084097</v>
       </c>
     </row>
     <row r="22" spans="1:87" x14ac:dyDescent="0.2">
@@ -22154,7 +22153,7 @@
       </c>
       <c r="L22">
         <f>IF('Input Scenarios'!L43&lt;&gt;"", 'Input Scenarios'!L43,_xlfn.XLOOKUP($F22,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M22">
         <f>'Input Scenarios'!M43</f>
@@ -22248,9 +22247,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -22266,7 +22265,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -22314,11 +22313,11 @@
       </c>
       <c r="AZ22">
         <f t="shared" si="7"/>
-        <v>2.22456E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA22">
         <f t="shared" si="0"/>
-        <v>823.00489128000004</v>
+        <v>671.06552673600004</v>
       </c>
       <c r="BB22">
         <f t="shared" si="1"/>
@@ -22326,7 +22325,7 @@
       </c>
       <c r="BC22">
         <f t="shared" si="1"/>
-        <v>740.70440215200006</v>
+        <v>603.9589740624001</v>
       </c>
       <c r="BD22">
         <f t="shared" si="1"/>
@@ -22334,7 +22333,7 @@
       </c>
       <c r="BE22">
         <f t="shared" si="1"/>
-        <v>82.300489128000009</v>
+        <v>67.106552673600007</v>
       </c>
       <c r="BF22">
         <f t="shared" si="2"/>
@@ -22342,7 +22341,7 @@
       </c>
       <c r="BG22">
         <f t="shared" si="2"/>
-        <v>702.92847764224803</v>
+        <v>573.15706638521772</v>
       </c>
       <c r="BH22">
         <f t="shared" si="2"/>
@@ -22354,7 +22353,7 @@
       </c>
       <c r="BJ22">
         <f t="shared" si="3"/>
-        <v>702.92847764224803</v>
+        <v>573.15706638521772</v>
       </c>
       <c r="BK22">
         <f t="shared" si="3"/>
@@ -22382,7 +22381,7 @@
       </c>
       <c r="BQ22">
         <f t="shared" si="4"/>
-        <v>1.1639640605245716</v>
+        <v>0.94907838781234299</v>
       </c>
       <c r="BR22">
         <f t="shared" si="4"/>
@@ -22390,7 +22389,7 @@
       </c>
       <c r="BS22">
         <f t="shared" si="4"/>
-        <v>2.5865868011657147</v>
+        <v>0</v>
       </c>
       <c r="BT22">
         <f t="shared" si="9"/>
@@ -22398,7 +22397,7 @@
       </c>
       <c r="BU22">
         <f t="shared" si="5"/>
-        <v>11.046018934378184</v>
+        <v>9.0067539003391364</v>
       </c>
       <c r="BV22">
         <f t="shared" si="5"/>
@@ -22410,11 +22409,11 @@
       </c>
       <c r="BX22">
         <f t="shared" si="10"/>
-        <v>0.77597604034971435</v>
+        <v>0.63271892520822859</v>
       </c>
       <c r="BY22">
         <f t="shared" si="11"/>
-        <v>14.79656979606847</v>
+        <v>9.9558322881514787</v>
       </c>
     </row>
     <row r="23" spans="1:87" x14ac:dyDescent="0.2">
@@ -22558,9 +22557,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -22576,7 +22575,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -22700,7 +22699,7 @@
       </c>
       <c r="BS23">
         <f t="shared" si="4"/>
-        <v>8.897314875428572</v>
+        <v>0</v>
       </c>
       <c r="BT23">
         <f t="shared" si="9"/>
@@ -22724,11 +22723,11 @@
       </c>
       <c r="BY23">
         <f t="shared" si="11"/>
-        <v>9.2577055574105138</v>
+        <v>0.36039068198194296</v>
       </c>
       <c r="BZ23">
         <f>SUM(BX23:BY26)/1000</f>
-        <v>4.4235889220643497E-2</v>
+        <v>5.6073058181976007E-3</v>
       </c>
     </row>
     <row r="24" spans="1:87" x14ac:dyDescent="0.2">
@@ -22872,9 +22871,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -22890,7 +22889,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -23014,7 +23013,7 @@
       </c>
       <c r="BS24">
         <f t="shared" si="4"/>
-        <v>14.081565213257143</v>
+        <v>0</v>
       </c>
       <c r="BT24">
         <f t="shared" si="9"/>
@@ -23038,7 +23037,7 @@
       </c>
       <c r="BY24">
         <f t="shared" si="11"/>
-        <v>14.651946835311909</v>
+        <v>0.57038162205476572</v>
       </c>
     </row>
     <row r="25" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -23088,7 +23087,7 @@
       </c>
       <c r="L25">
         <f>IF('Input Scenarios'!L46&lt;&gt;"", 'Input Scenarios'!L46,_xlfn.XLOOKUP($F25,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M25">
         <f>'Input Scenarios'!M46</f>
@@ -23182,9 +23181,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -23200,7 +23199,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -23248,15 +23247,15 @@
       </c>
       <c r="AZ25">
         <f t="shared" si="7"/>
-        <v>1.2052799999999998E-3</v>
+        <v>1.4195519999999999E-3</v>
       </c>
       <c r="BA25">
         <f t="shared" si="0"/>
-        <v>223.09732799999995</v>
+        <v>262.75907519999998</v>
       </c>
       <c r="BB25">
         <f t="shared" si="1"/>
-        <v>22.309732799999995</v>
+        <v>26.275907520000001</v>
       </c>
       <c r="BC25">
         <f t="shared" si="1"/>
@@ -23268,11 +23267,11 @@
       </c>
       <c r="BE25">
         <f t="shared" si="1"/>
-        <v>200.78759519999997</v>
+        <v>236.48316767999998</v>
       </c>
       <c r="BF25">
         <f t="shared" si="2"/>
-        <v>15.594503227199995</v>
+        <v>18.366859356479999</v>
       </c>
       <c r="BG25">
         <f t="shared" si="2"/>
@@ -23288,11 +23287,11 @@
       </c>
       <c r="BJ25">
         <f t="shared" si="3"/>
-        <v>14.035052904479995</v>
+        <v>16.530173420832</v>
       </c>
       <c r="BK25">
         <f t="shared" si="3"/>
-        <v>1.5594503227199996</v>
+        <v>1.8366859356480001</v>
       </c>
       <c r="BL25">
         <f t="shared" si="3"/>
@@ -23312,7 +23311,7 @@
       </c>
       <c r="BP25">
         <f t="shared" si="8"/>
-        <v>3.5058151542857137E-2</v>
+        <v>4.1290711817142861E-2</v>
       </c>
       <c r="BQ25">
         <f t="shared" si="4"/>
@@ -23324,7 +23323,7 @@
       </c>
       <c r="BS25">
         <f t="shared" si="4"/>
-        <v>6.3104672777142845</v>
+        <v>0</v>
       </c>
       <c r="BT25">
         <f t="shared" si="9"/>
@@ -23332,7 +23331,7 @@
       </c>
       <c r="BU25">
         <f t="shared" si="5"/>
-        <v>0.2205508313561142</v>
+        <v>0.25975986804164569</v>
       </c>
       <c r="BV25">
         <f t="shared" si="5"/>
@@ -23344,11 +23343,11 @@
       </c>
       <c r="BX25">
         <f t="shared" si="10"/>
-        <v>0.63104672777142845</v>
+        <v>0.74323281270857144</v>
       </c>
       <c r="BY25">
         <f t="shared" si="11"/>
-        <v>6.5660762606132552</v>
+        <v>0.30105057985878858</v>
       </c>
       <c r="BZ25"/>
       <c r="CA25"/>
@@ -23502,9 +23501,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -23520,7 +23519,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -23644,7 +23643,7 @@
       </c>
       <c r="BS26">
         <f t="shared" si="4"/>
-        <v>9.4968637179428566</v>
+        <v>0</v>
       </c>
       <c r="BT26">
         <f t="shared" si="9"/>
@@ -23668,7 +23667,7 @@
       </c>
       <c r="BY26">
         <f t="shared" si="11"/>
-        <v>9.8815394588735312</v>
+        <v>0.38467574093067425</v>
       </c>
     </row>
     <row r="30" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -24265,9 +24264,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -24283,7 +24282,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -24587,9 +24586,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -24605,7 +24604,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -24905,9 +24904,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -24923,7 +24922,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -25223,9 +25222,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -25241,7 +25240,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -25541,9 +25540,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -25559,7 +25558,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -25871,9 +25870,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -25889,7 +25888,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -26189,9 +26188,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -26207,7 +26206,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -26507,9 +26506,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -26525,7 +26524,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -26825,9 +26824,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -26843,7 +26842,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -27147,9 +27146,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -27165,7 +27164,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -27474,9 +27473,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -27492,7 +27491,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -27792,9 +27791,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -27810,7 +27809,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -28110,9 +28109,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -28128,7 +28127,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -28432,9 +28431,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -28450,7 +28449,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -28750,9 +28749,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -28768,7 +28767,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -29077,9 +29076,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -29095,7 +29094,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -29841,7 +29840,7 @@
       </c>
       <c r="L11">
         <f>IF('Input Scenarios'!L32&lt;&gt;"", 'Input Scenarios'!L32,_xlfn.XLOOKUP($F11,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11">
         <f>'Input Scenarios'!M32</f>
@@ -29935,9 +29934,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -29953,7 +29952,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -30001,79 +30000,79 @@
       </c>
       <c r="AZ11">
         <f>AY11*(1-L11)</f>
-        <v>1.8867199999999999E-3</v>
+        <v>1.8304000000000003E-3</v>
       </c>
       <c r="BA11">
         <f t="shared" ref="BA11:BA26" si="0">G11*AZ11*H11</f>
-        <v>471.68</v>
+        <v>457.6</v>
       </c>
       <c r="BB11">
         <f t="shared" ref="BB11:BE26" si="1">$BA11*M11</f>
-        <v>47.168000000000006</v>
+        <v>45.760000000000005</v>
       </c>
       <c r="BC11">
         <f t="shared" si="1"/>
-        <v>94.336000000000013</v>
+        <v>91.52000000000001</v>
       </c>
       <c r="BD11">
         <f t="shared" si="1"/>
-        <v>141.50399999999999</v>
+        <v>137.28</v>
       </c>
       <c r="BE11">
         <f t="shared" si="1"/>
-        <v>188.67200000000003</v>
+        <v>183.04000000000002</v>
       </c>
       <c r="BF11">
         <f t="shared" ref="BF11:BH26" si="2">(BB11*(1-AG11-AK11))</f>
-        <v>32.970432000000002</v>
+        <v>31.986240000000002</v>
       </c>
       <c r="BG11">
         <f t="shared" si="2"/>
-        <v>89.524864000000008</v>
+        <v>86.85248</v>
       </c>
       <c r="BH11">
         <f t="shared" si="2"/>
-        <v>84.760895999999988</v>
+        <v>82.230719999999991</v>
       </c>
       <c r="BI11">
         <f t="shared" ref="BI11:BM26" si="3">($BF11*Q11)+($BG11*V11)+($BH11*AA11)</f>
-        <v>16.485216000000001</v>
+        <v>15.993120000000001</v>
       </c>
       <c r="BJ11">
         <f t="shared" si="3"/>
-        <v>16.485216000000001</v>
+        <v>15.993120000000001</v>
       </c>
       <c r="BK11">
         <f t="shared" si="3"/>
-        <v>67.143648000000013</v>
+        <v>65.139359999999996</v>
       </c>
       <c r="BL11">
         <f t="shared" si="3"/>
-        <v>22.381216000000002</v>
+        <v>21.71312</v>
       </c>
       <c r="BM11">
         <f t="shared" si="3"/>
-        <v>84.760895999999988</v>
+        <v>82.230719999999991</v>
       </c>
       <c r="BN11">
         <f>BB11*AG11</f>
-        <v>14.150400000000001</v>
+        <v>13.728000000000002</v>
       </c>
       <c r="BO11">
         <f t="shared" ref="BO11:BP26" si="4">BC11*AH11</f>
-        <v>4.716800000000001</v>
+        <v>4.5760000000000005</v>
       </c>
       <c r="BP11">
         <f t="shared" si="4"/>
-        <v>56.601599999999998</v>
+        <v>54.912000000000006</v>
       </c>
       <c r="BQ11">
         <f>BI11*AO11</f>
-        <v>3.2970432000000005</v>
+        <v>3.1986240000000006</v>
       </c>
       <c r="BR11">
         <f t="shared" ref="BR11:BT26" si="5">BJ11*AP11</f>
-        <v>3.2970432000000005</v>
+        <v>3.1986240000000006</v>
       </c>
       <c r="BS11">
         <f t="shared" si="5"/>
@@ -30085,7 +30084,7 @@
       </c>
       <c r="BU11">
         <f>SUM(BN11:BT11)</f>
-        <v>82.062886400000011</v>
+        <v>79.613247999999999</v>
       </c>
       <c r="BV11">
         <f>Constants!$K$2</f>
@@ -30093,7 +30092,7 @@
       </c>
       <c r="BW11">
         <f>BE11*BV11</f>
-        <v>39.621120000000005</v>
+        <v>38.438400000000001</v>
       </c>
       <c r="BX11">
         <f>IF(C11="", "", _xlfn.XLOOKUP(C11,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -30105,15 +30104,15 @@
       </c>
       <c r="BZ11">
         <f>BU11*BX11*BY11</f>
-        <v>0.23212073581714288</v>
+        <v>0.22519175862857141</v>
       </c>
       <c r="CA11">
         <f>BW11*BX11*BY11</f>
-        <v>0.11207116800000001</v>
+        <v>0.10872576</v>
       </c>
       <c r="CB11">
         <f>SUM(BZ11:CA14)/1000</f>
-        <v>1.356598296617143E-3</v>
+        <v>1.3437553151314288E-3</v>
       </c>
     </row>
     <row r="12" spans="1:88" x14ac:dyDescent="0.2">
@@ -30163,7 +30162,7 @@
       </c>
       <c r="L12">
         <f>IF('Input Scenarios'!L33&lt;&gt;"", 'Input Scenarios'!L33,_xlfn.XLOOKUP($F12,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M12">
         <f>'Input Scenarios'!M33</f>
@@ -30257,9 +30256,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -30275,7 +30274,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -30323,79 +30322,79 @@
       </c>
       <c r="AZ12">
         <f t="shared" ref="AZ12:AZ26" si="7">AY12*(1-L12)</f>
-        <v>2.0976000000000002E-3</v>
+        <v>2.0672000000000004E-3</v>
       </c>
       <c r="BA12">
         <f t="shared" si="0"/>
-        <v>524.40000000000009</v>
+        <v>516.80000000000007</v>
       </c>
       <c r="BB12">
         <f t="shared" si="1"/>
-        <v>52.440000000000012</v>
+        <v>51.680000000000007</v>
       </c>
       <c r="BC12">
         <f t="shared" si="1"/>
-        <v>104.88000000000002</v>
+        <v>103.36000000000001</v>
       </c>
       <c r="BD12">
         <f t="shared" si="1"/>
-        <v>157.32000000000002</v>
+        <v>155.04000000000002</v>
       </c>
       <c r="BE12">
         <f t="shared" si="1"/>
-        <v>209.76000000000005</v>
+        <v>206.72000000000003</v>
       </c>
       <c r="BF12">
         <f t="shared" si="2"/>
-        <v>36.655560000000008</v>
+        <v>36.124320000000004</v>
       </c>
       <c r="BG12">
         <f t="shared" si="2"/>
-        <v>99.531120000000016</v>
+        <v>98.088640000000012</v>
       </c>
       <c r="BH12">
         <f t="shared" si="2"/>
-        <v>94.234680000000012</v>
+        <v>92.868960000000015</v>
       </c>
       <c r="BI12">
         <f t="shared" si="3"/>
-        <v>18.327780000000004</v>
+        <v>18.062160000000002</v>
       </c>
       <c r="BJ12">
         <f t="shared" si="3"/>
-        <v>18.327780000000004</v>
+        <v>18.062160000000002</v>
       </c>
       <c r="BK12">
         <f t="shared" si="3"/>
-        <v>74.648340000000019</v>
+        <v>73.566480000000013</v>
       </c>
       <c r="BL12">
         <f t="shared" si="3"/>
-        <v>24.882780000000004</v>
+        <v>24.522160000000003</v>
       </c>
       <c r="BM12">
         <f t="shared" si="3"/>
-        <v>94.234680000000012</v>
+        <v>92.868960000000015</v>
       </c>
       <c r="BN12">
         <f t="shared" ref="BN12:BN26" si="8">BB12*AG12</f>
-        <v>15.732000000000003</v>
+        <v>15.504000000000001</v>
       </c>
       <c r="BO12">
         <f t="shared" si="4"/>
-        <v>5.2440000000000015</v>
+        <v>5.168000000000001</v>
       </c>
       <c r="BP12">
         <f t="shared" si="4"/>
-        <v>62.928000000000011</v>
+        <v>62.016000000000012</v>
       </c>
       <c r="BQ12">
         <f t="shared" ref="BQ12:BQ26" si="9">BI12*AO12</f>
-        <v>3.6655560000000009</v>
+        <v>3.6124320000000005</v>
       </c>
       <c r="BR12">
         <f t="shared" si="5"/>
-        <v>3.6655560000000009</v>
+        <v>3.6124320000000005</v>
       </c>
       <c r="BS12">
         <f t="shared" si="5"/>
@@ -30407,7 +30406,7 @@
       </c>
       <c r="BU12">
         <f t="shared" ref="BU12:BU26" si="10">SUM(BN12:BT12)</f>
-        <v>91.235112000000015</v>
+        <v>89.912864000000013</v>
       </c>
       <c r="BV12">
         <f>Constants!$K$2</f>
@@ -30415,7 +30414,7 @@
       </c>
       <c r="BW12">
         <f t="shared" ref="BW12:BW26" si="11">BE12*BV12</f>
-        <v>44.049600000000005</v>
+        <v>43.411200000000001</v>
       </c>
       <c r="BX12">
         <f>IF(C12="", "", _xlfn.XLOOKUP(C12,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -30427,11 +30426,11 @@
       </c>
       <c r="BZ12">
         <f t="shared" ref="BZ12:BZ26" si="12">BU12*BX12*BY12</f>
-        <v>0.25806503108571432</v>
+        <v>0.25432495817142864</v>
       </c>
       <c r="CA12">
         <f t="shared" ref="CA12:CA26" si="13">BW12*BX12*BY12</f>
-        <v>0.12459744</v>
+        <v>0.12279168</v>
       </c>
     </row>
     <row r="13" spans="1:88" x14ac:dyDescent="0.2">
@@ -30481,7 +30480,7 @@
       </c>
       <c r="L13">
         <f>IF('Input Scenarios'!L34&lt;&gt;"", 'Input Scenarios'!L34,_xlfn.XLOOKUP($F13,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="M13">
         <f>'Input Scenarios'!M34</f>
@@ -30575,9 +30574,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -30593,7 +30592,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -30641,79 +30640,79 @@
       </c>
       <c r="AZ13">
         <f t="shared" si="7"/>
-        <v>1.98E-3</v>
+        <v>1.908E-3</v>
       </c>
       <c r="BA13">
         <f t="shared" si="0"/>
-        <v>495</v>
+        <v>476.99999999999994</v>
       </c>
       <c r="BB13">
         <f t="shared" si="1"/>
-        <v>49.5</v>
+        <v>47.699999999999996</v>
       </c>
       <c r="BC13">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>95.399999999999991</v>
       </c>
       <c r="BD13">
         <f t="shared" si="1"/>
-        <v>148.5</v>
+        <v>143.09999999999997</v>
       </c>
       <c r="BE13">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>190.79999999999998</v>
       </c>
       <c r="BF13">
         <f t="shared" si="2"/>
-        <v>34.600499999999997</v>
+        <v>33.342299999999994</v>
       </c>
       <c r="BG13">
         <f t="shared" si="2"/>
-        <v>93.950999999999993</v>
+        <v>90.534599999999983</v>
       </c>
       <c r="BH13">
         <f t="shared" si="2"/>
-        <v>88.951499999999996</v>
+        <v>85.716899999999981</v>
       </c>
       <c r="BI13">
         <f t="shared" si="3"/>
-        <v>17.300249999999998</v>
+        <v>16.671149999999997</v>
       </c>
       <c r="BJ13">
         <f t="shared" si="3"/>
-        <v>17.300249999999998</v>
+        <v>16.671149999999997</v>
       </c>
       <c r="BK13">
         <f t="shared" si="3"/>
-        <v>70.463249999999988</v>
+        <v>67.900949999999995</v>
       </c>
       <c r="BL13">
         <f t="shared" si="3"/>
-        <v>23.487749999999998</v>
+        <v>22.633649999999996</v>
       </c>
       <c r="BM13">
         <f t="shared" si="3"/>
-        <v>88.951499999999996</v>
+        <v>85.716899999999981</v>
       </c>
       <c r="BN13">
         <f t="shared" si="8"/>
-        <v>14.85</v>
+        <v>14.309999999999999</v>
       </c>
       <c r="BO13">
         <f t="shared" si="4"/>
-        <v>4.95</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="BP13">
         <f t="shared" si="4"/>
-        <v>59.400000000000006</v>
+        <v>57.239999999999988</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="9"/>
-        <v>3.4600499999999998</v>
+        <v>3.3342299999999998</v>
       </c>
       <c r="BR13">
         <f t="shared" si="5"/>
-        <v>3.4600499999999998</v>
+        <v>3.3342299999999998</v>
       </c>
       <c r="BS13">
         <f t="shared" si="5"/>
@@ -30725,7 +30724,7 @@
       </c>
       <c r="BU13">
         <f t="shared" si="10"/>
-        <v>86.120099999999994</v>
+        <v>82.988460000000003</v>
       </c>
       <c r="BV13">
         <f>Constants!$K$2</f>
@@ -30733,7 +30732,7 @@
       </c>
       <c r="BW13">
         <f t="shared" si="11"/>
-        <v>41.58</v>
+        <v>40.067999999999998</v>
       </c>
       <c r="BX13">
         <f>IF(C13="", "", _xlfn.XLOOKUP(C13,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -30745,11 +30744,11 @@
       </c>
       <c r="BZ13">
         <f t="shared" si="12"/>
-        <v>0.24359685428571423</v>
+        <v>0.23473878685714286</v>
       </c>
       <c r="CA13">
         <f t="shared" si="13"/>
-        <v>0.11761199999999999</v>
+        <v>0.11333519999999998</v>
       </c>
     </row>
     <row r="14" spans="1:88" x14ac:dyDescent="0.2">
@@ -30799,7 +30798,7 @@
       </c>
       <c r="L14">
         <f>IF('Input Scenarios'!L35&lt;&gt;"", 'Input Scenarios'!L35,_xlfn.XLOOKUP($F14,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M14">
         <f>'Input Scenarios'!M35</f>
@@ -30893,9 +30892,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -30911,7 +30910,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -30959,79 +30958,79 @@
       </c>
       <c r="AZ14">
         <f t="shared" si="7"/>
-        <v>1.472E-3</v>
+        <v>1.56032E-3</v>
       </c>
       <c r="BA14">
         <f t="shared" si="0"/>
-        <v>368</v>
+        <v>390.08000000000004</v>
       </c>
       <c r="BB14">
         <f t="shared" si="1"/>
-        <v>36.800000000000004</v>
+        <v>39.00800000000001</v>
       </c>
       <c r="BC14">
         <f t="shared" si="1"/>
-        <v>73.600000000000009</v>
+        <v>78.01600000000002</v>
       </c>
       <c r="BD14">
         <f t="shared" si="1"/>
-        <v>110.39999999999999</v>
+        <v>117.024</v>
       </c>
       <c r="BE14">
         <f t="shared" si="1"/>
-        <v>147.20000000000002</v>
+        <v>156.03200000000004</v>
       </c>
       <c r="BF14">
         <f t="shared" si="2"/>
-        <v>25.723200000000002</v>
+        <v>27.266592000000006</v>
       </c>
       <c r="BG14">
         <f t="shared" si="2"/>
-        <v>69.846400000000003</v>
+        <v>74.037184000000011</v>
       </c>
       <c r="BH14">
         <f t="shared" si="2"/>
-        <v>66.129599999999996</v>
+        <v>70.097375999999997</v>
       </c>
       <c r="BI14">
         <f t="shared" si="3"/>
-        <v>12.861600000000001</v>
+        <v>13.633296000000003</v>
       </c>
       <c r="BJ14">
         <f t="shared" si="3"/>
-        <v>12.861600000000001</v>
+        <v>13.633296000000003</v>
       </c>
       <c r="BK14">
         <f t="shared" si="3"/>
-        <v>52.384799999999998</v>
+        <v>55.527888000000004</v>
       </c>
       <c r="BL14">
         <f t="shared" si="3"/>
-        <v>17.461600000000001</v>
+        <v>18.509296000000003</v>
       </c>
       <c r="BM14">
         <f t="shared" si="3"/>
-        <v>66.129599999999996</v>
+        <v>70.097375999999997</v>
       </c>
       <c r="BN14">
         <f t="shared" si="8"/>
-        <v>11.040000000000001</v>
+        <v>11.702400000000003</v>
       </c>
       <c r="BO14">
         <f t="shared" si="4"/>
-        <v>3.6800000000000006</v>
+        <v>3.9008000000000012</v>
       </c>
       <c r="BP14">
         <f t="shared" si="4"/>
-        <v>44.16</v>
+        <v>46.809600000000003</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="9"/>
-        <v>2.5723200000000004</v>
+        <v>2.7266592000000007</v>
       </c>
       <c r="BR14">
         <f t="shared" si="5"/>
-        <v>2.5723200000000004</v>
+        <v>2.7266592000000007</v>
       </c>
       <c r="BS14">
         <f t="shared" si="5"/>
@@ -31043,7 +31042,7 @@
       </c>
       <c r="BU14">
         <f t="shared" si="10"/>
-        <v>64.024639999999991</v>
+        <v>67.866118400000005</v>
       </c>
       <c r="BV14">
         <f>Constants!$K$2</f>
@@ -31051,7 +31050,7 @@
       </c>
       <c r="BW14">
         <f t="shared" si="11"/>
-        <v>30.912000000000003</v>
+        <v>32.766720000000007</v>
       </c>
       <c r="BX14">
         <f>IF(C14="", "", _xlfn.XLOOKUP(C14,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -31063,11 +31062,11 @@
       </c>
       <c r="BZ14">
         <f t="shared" si="12"/>
-        <v>0.18109826742857141</v>
+        <v>0.19196416347428572</v>
       </c>
       <c r="CA14">
         <f t="shared" si="13"/>
-        <v>8.7436800000000009E-2</v>
+        <v>9.2683008000000011E-2</v>
       </c>
     </row>
     <row r="15" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -31211,9 +31210,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -31229,7 +31228,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -31389,7 +31388,7 @@
       </c>
       <c r="CB15">
         <f>SUM(BZ15:CA18)/1000</f>
-        <v>8.1415733763672005E-3</v>
+        <v>8.073023123721601E-3</v>
       </c>
       <c r="CC15"/>
       <c r="CD15"/>
@@ -31541,9 +31540,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -31559,7 +31558,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -31765,7 +31764,7 @@
       </c>
       <c r="L17">
         <f>IF('Input Scenarios'!L38&lt;&gt;"", 'Input Scenarios'!L38,_xlfn.XLOOKUP($F17,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="M17">
         <f>'Input Scenarios'!M38</f>
@@ -31859,9 +31858,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -31877,7 +31876,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -31925,79 +31924,79 @@
       </c>
       <c r="AZ17">
         <f t="shared" si="7"/>
-        <v>1.7443200000000002E-3</v>
+        <v>1.5408160000000002E-3</v>
       </c>
       <c r="BA17">
         <f t="shared" si="0"/>
-        <v>490.59000000000003</v>
+        <v>433.35450000000003</v>
       </c>
       <c r="BB17">
         <f t="shared" si="1"/>
-        <v>196.23600000000002</v>
+        <v>173.34180000000003</v>
       </c>
       <c r="BC17">
         <f t="shared" si="1"/>
-        <v>147.17699999999999</v>
+        <v>130.00635</v>
       </c>
       <c r="BD17">
         <f t="shared" si="1"/>
-        <v>98.118000000000009</v>
+        <v>86.670900000000017</v>
       </c>
       <c r="BE17">
         <f t="shared" si="1"/>
-        <v>49.059000000000005</v>
+        <v>43.335450000000009</v>
       </c>
       <c r="BF17">
         <f t="shared" si="2"/>
-        <v>137.16896400000002</v>
+        <v>121.16591820000002</v>
       </c>
       <c r="BG17">
         <f t="shared" si="2"/>
-        <v>139.67097299999998</v>
+        <v>123.37602614999999</v>
       </c>
       <c r="BH17">
         <f t="shared" si="2"/>
-        <v>58.772682000000003</v>
+        <v>51.915869100000009</v>
       </c>
       <c r="BI17">
         <f t="shared" si="3"/>
-        <v>104.30826462</v>
+        <v>92.138967081000004</v>
       </c>
       <c r="BJ17">
         <f t="shared" si="3"/>
-        <v>132.78799529999998</v>
+        <v>117.296062515</v>
       </c>
       <c r="BK17">
         <f t="shared" si="3"/>
-        <v>42.126963300000007</v>
+        <v>37.212150915000009</v>
       </c>
       <c r="BL17">
         <f t="shared" si="3"/>
-        <v>34.292241000000004</v>
+        <v>30.291479550000005</v>
       </c>
       <c r="BM17">
         <f t="shared" si="3"/>
-        <v>22.097154780000004</v>
+        <v>19.519153389000003</v>
       </c>
       <c r="BN17">
         <f t="shared" si="8"/>
-        <v>58.870800000000003</v>
+        <v>52.00254000000001</v>
       </c>
       <c r="BO17">
         <f t="shared" si="4"/>
-        <v>7.3588500000000003</v>
+        <v>6.5003175000000004</v>
       </c>
       <c r="BP17">
         <f t="shared" si="4"/>
-        <v>39.247200000000007</v>
+        <v>34.668360000000007</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="9"/>
-        <v>20.861652924000001</v>
+        <v>18.4277934162</v>
       </c>
       <c r="BR17">
         <f t="shared" si="5"/>
-        <v>26.557599059999998</v>
+        <v>23.459212503000003</v>
       </c>
       <c r="BS17">
         <f t="shared" si="5"/>
@@ -32009,7 +32008,7 @@
       </c>
       <c r="BU17">
         <f t="shared" si="10"/>
-        <v>152.89610198400001</v>
+        <v>135.05822341920003</v>
       </c>
       <c r="BV17">
         <f>Constants!$K$2</f>
@@ -32017,7 +32016,7 @@
       </c>
       <c r="BW17">
         <f t="shared" si="11"/>
-        <v>10.302390000000001</v>
+        <v>9.1004445000000018</v>
       </c>
       <c r="BX17">
         <f>IF(C17="", "", _xlfn.XLOOKUP(C17,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -32029,11 +32028,11 @@
       </c>
       <c r="BZ17">
         <f t="shared" si="12"/>
-        <v>1.6818571218240002</v>
+        <v>1.4856404576112003</v>
       </c>
       <c r="CA17">
         <f t="shared" si="13"/>
-        <v>0.11332629000000001</v>
+        <v>0.10010488950000003</v>
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.2">
@@ -32083,7 +32082,7 @@
       </c>
       <c r="L18">
         <f>IF('Input Scenarios'!L39&lt;&gt;"", 'Input Scenarios'!L39,_xlfn.XLOOKUP($F18,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M18">
         <f>'Input Scenarios'!M39</f>
@@ -32177,9 +32176,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -32195,7 +32194,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -32243,79 +32242,79 @@
       </c>
       <c r="AZ18">
         <f t="shared" si="7"/>
-        <v>1.6769759999999999E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA18">
         <f t="shared" si="0"/>
-        <v>471.64949999999999</v>
+        <v>510.1515</v>
       </c>
       <c r="BB18">
         <f t="shared" si="1"/>
-        <v>188.65980000000002</v>
+        <v>204.06060000000002</v>
       </c>
       <c r="BC18">
         <f t="shared" si="1"/>
-        <v>141.49484999999999</v>
+        <v>153.04544999999999</v>
       </c>
       <c r="BD18">
         <f t="shared" si="1"/>
-        <v>94.329900000000009</v>
+        <v>102.03030000000001</v>
       </c>
       <c r="BE18">
         <f t="shared" si="1"/>
-        <v>47.164950000000005</v>
+        <v>51.015150000000006</v>
       </c>
       <c r="BF18">
         <f t="shared" si="2"/>
-        <v>131.87320020000001</v>
+        <v>142.63835940000001</v>
       </c>
       <c r="BG18">
         <f t="shared" si="2"/>
-        <v>134.27861264999999</v>
+        <v>145.24013204999997</v>
       </c>
       <c r="BH18">
         <f t="shared" si="2"/>
-        <v>56.503610100000003</v>
+        <v>61.116149700000001</v>
       </c>
       <c r="BI18">
         <f t="shared" si="3"/>
-        <v>100.28117339100001</v>
+        <v>108.467391627</v>
       </c>
       <c r="BJ18">
         <f t="shared" si="3"/>
-        <v>127.66137016499998</v>
+        <v>138.08270650499998</v>
       </c>
       <c r="BK18">
         <f t="shared" si="3"/>
-        <v>40.500542565000003</v>
+        <v>43.806709305000005</v>
       </c>
       <c r="BL18">
         <f t="shared" si="3"/>
-        <v>32.968300050000003</v>
+        <v>35.659589850000003</v>
       </c>
       <c r="BM18">
         <f t="shared" si="3"/>
-        <v>21.244036778999998</v>
+        <v>22.978243862999999</v>
       </c>
       <c r="BN18">
         <f t="shared" si="8"/>
-        <v>56.597940000000001</v>
+        <v>61.218180000000004</v>
       </c>
       <c r="BO18">
         <f t="shared" si="4"/>
-        <v>7.0747424999999993</v>
+        <v>7.6522724999999996</v>
       </c>
       <c r="BP18">
         <f t="shared" si="4"/>
-        <v>37.731960000000008</v>
+        <v>40.812120000000007</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="9"/>
-        <v>20.056234678200003</v>
+        <v>21.693478325400001</v>
       </c>
       <c r="BR18">
         <f t="shared" si="5"/>
-        <v>25.532274032999997</v>
+        <v>27.616541300999998</v>
       </c>
       <c r="BS18">
         <f t="shared" si="5"/>
@@ -32327,7 +32326,7 @@
       </c>
       <c r="BU18">
         <f t="shared" si="10"/>
-        <v>146.9931512112</v>
+        <v>158.99259212639998</v>
       </c>
       <c r="BV18">
         <f>Constants!$K$2</f>
@@ -32335,7 +32334,7 @@
       </c>
       <c r="BW18">
         <f t="shared" si="11"/>
-        <v>9.9046395</v>
+        <v>10.713181500000001</v>
       </c>
       <c r="BX18">
         <f>IF(C18="", "", _xlfn.XLOOKUP(C18,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -32347,11 +32346,11 @@
       </c>
       <c r="BZ18">
         <f t="shared" si="12"/>
-        <v>1.6169246633232</v>
+        <v>1.7489185133903999</v>
       </c>
       <c r="CA18">
         <f t="shared" si="13"/>
-        <v>0.1089510345</v>
+        <v>0.11784499650000002</v>
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.2">
@@ -32401,7 +32400,7 @@
       </c>
       <c r="L19">
         <f>IF('Input Scenarios'!L40&lt;&gt;"", 'Input Scenarios'!L40,_xlfn.XLOOKUP($F19,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M19">
         <f>'Input Scenarios'!M40</f>
@@ -32495,9 +32494,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -32513,7 +32512,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -32561,11 +32560,11 @@
       </c>
       <c r="AZ19">
         <f t="shared" si="7"/>
-        <v>1.7089919999999999E-3</v>
+        <v>1.6099199999999999E-3</v>
       </c>
       <c r="BA19">
         <f t="shared" si="0"/>
-        <v>632.26380729599998</v>
+        <v>595.61083295999993</v>
       </c>
       <c r="BB19">
         <f t="shared" si="1"/>
@@ -32573,7 +32572,7 @@
       </c>
       <c r="BC19">
         <f t="shared" si="1"/>
-        <v>569.03742656639997</v>
+        <v>536.04974966399993</v>
       </c>
       <c r="BD19">
         <f t="shared" si="1"/>
@@ -32581,7 +32580,7 @@
       </c>
       <c r="BE19">
         <f t="shared" si="1"/>
-        <v>63.226380729600002</v>
+        <v>59.561083295999993</v>
       </c>
       <c r="BF19">
         <f t="shared" si="2"/>
@@ -32589,7 +32588,7 @@
       </c>
       <c r="BG19">
         <f t="shared" si="2"/>
-        <v>540.01651781151349</v>
+        <v>508.71121243113589</v>
       </c>
       <c r="BH19">
         <f t="shared" si="2"/>
@@ -32601,7 +32600,7 @@
       </c>
       <c r="BJ19">
         <f t="shared" si="3"/>
-        <v>540.01651781151349</v>
+        <v>508.71121243113589</v>
       </c>
       <c r="BK19">
         <f t="shared" si="3"/>
@@ -32621,7 +32620,7 @@
       </c>
       <c r="BO19">
         <f t="shared" si="4"/>
-        <v>28.451871328319999</v>
+        <v>26.802487483199997</v>
       </c>
       <c r="BP19">
         <f t="shared" si="4"/>
@@ -32633,7 +32632,7 @@
       </c>
       <c r="BR19">
         <f t="shared" si="5"/>
-        <v>108.0033035623027</v>
+        <v>101.74224248622718</v>
       </c>
       <c r="BS19">
         <f t="shared" si="5"/>
@@ -32645,7 +32644,7 @@
       </c>
       <c r="BU19">
         <f t="shared" si="10"/>
-        <v>136.45517489062271</v>
+        <v>128.54472996942718</v>
       </c>
       <c r="BV19">
         <f>Constants!$K$2</f>
@@ -32653,7 +32652,7 @@
       </c>
       <c r="BW19">
         <f t="shared" si="11"/>
-        <v>13.277539953215999</v>
+        <v>12.507827492159999</v>
       </c>
       <c r="BX19">
         <f>IF(C19="", "", _xlfn.XLOOKUP(C19,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -32665,15 +32664,15 @@
       </c>
       <c r="BZ19">
         <f t="shared" si="12"/>
-        <v>1.265134407200202</v>
+        <v>1.1917932821451178</v>
       </c>
       <c r="CA19">
         <f t="shared" si="13"/>
-        <v>0.12310176328053118</v>
+        <v>0.11596542917731199</v>
       </c>
       <c r="CB19">
         <f>SUM(BZ19:CA22)/1000</f>
-        <v>5.6469650209977334E-3</v>
+        <v>5.6267026891457005E-3</v>
       </c>
     </row>
     <row r="20" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -32723,7 +32722,7 @@
       </c>
       <c r="L20">
         <f>IF('Input Scenarios'!L41&lt;&gt;"", 'Input Scenarios'!L41,_xlfn.XLOOKUP($F20,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="M20">
         <f>'Input Scenarios'!M41</f>
@@ -32817,9 +32816,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -32835,7 +32834,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -32883,11 +32882,11 @@
       </c>
       <c r="AZ20">
         <f t="shared" si="7"/>
-        <v>1.7221600000000004E-3</v>
+        <v>2.1292159999999997E-3</v>
       </c>
       <c r="BA20">
         <f t="shared" si="0"/>
-        <v>637.13548008000009</v>
+        <v>787.7311390079999</v>
       </c>
       <c r="BB20">
         <f t="shared" si="1"/>
@@ -32895,7 +32894,7 @@
       </c>
       <c r="BC20">
         <f t="shared" si="1"/>
-        <v>573.42193207200012</v>
+        <v>708.95802510719989</v>
       </c>
       <c r="BD20">
         <f t="shared" si="1"/>
@@ -32903,7 +32902,7 @@
       </c>
       <c r="BE20">
         <f t="shared" si="1"/>
-        <v>63.713548008000011</v>
+        <v>78.773113900799999</v>
       </c>
       <c r="BF20">
         <f t="shared" si="2"/>
@@ -32911,7 +32910,7 @@
       </c>
       <c r="BG20">
         <f t="shared" si="2"/>
-        <v>544.17741353632812</v>
+        <v>672.8011658267327</v>
       </c>
       <c r="BH20">
         <f t="shared" si="2"/>
@@ -32923,7 +32922,7 @@
       </c>
       <c r="BJ20">
         <f t="shared" si="3"/>
-        <v>544.17741353632812</v>
+        <v>672.8011658267327</v>
       </c>
       <c r="BK20">
         <f t="shared" si="3"/>
@@ -32943,7 +32942,7 @@
       </c>
       <c r="BO20">
         <f t="shared" si="4"/>
-        <v>28.671096603600006</v>
+        <v>35.447901255359994</v>
       </c>
       <c r="BP20">
         <f t="shared" si="4"/>
@@ -32955,7 +32954,7 @@
       </c>
       <c r="BR20">
         <f t="shared" si="5"/>
-        <v>108.83548270726563</v>
+        <v>134.56023316534655</v>
       </c>
       <c r="BS20">
         <f t="shared" si="5"/>
@@ -32967,7 +32966,7 @@
       </c>
       <c r="BU20">
         <f t="shared" si="10"/>
-        <v>137.50657931086562</v>
+        <v>170.00813442070654</v>
       </c>
       <c r="BV20">
         <f>Constants!$K$2</f>
@@ -32975,7 +32974,7 @@
       </c>
       <c r="BW20">
         <f t="shared" si="11"/>
-        <v>13.379845081680001</v>
+        <v>16.542353919168001</v>
       </c>
       <c r="BX20">
         <f>IF(C20="", "", _xlfn.XLOOKUP(C20,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -32987,11 +32986,11 @@
       </c>
       <c r="BZ20">
         <f t="shared" si="12"/>
-        <v>1.2748824281821682</v>
+        <v>1.5762182748434077</v>
       </c>
       <c r="CA20">
         <f t="shared" si="13"/>
-        <v>0.124050277971576</v>
+        <v>0.15337125276485761</v>
       </c>
       <c r="CB20"/>
       <c r="CC20"/>
@@ -33050,7 +33049,7 @@
       </c>
       <c r="L21">
         <f>IF('Input Scenarios'!L42&lt;&gt;"", 'Input Scenarios'!L42,_xlfn.XLOOKUP($F21,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M21">
         <f>'Input Scenarios'!M42</f>
@@ -33144,9 +33143,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -33162,7 +33161,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -33210,11 +33209,11 @@
       </c>
       <c r="AZ21">
         <f t="shared" si="7"/>
-        <v>1.2959999999999998E-3</v>
+        <v>1.3737599999999999E-3</v>
       </c>
       <c r="BA21">
         <f t="shared" si="0"/>
-        <v>479.47204799999992</v>
+        <v>508.24037087999994</v>
       </c>
       <c r="BB21">
         <f t="shared" si="1"/>
@@ -33222,7 +33221,7 @@
       </c>
       <c r="BC21">
         <f t="shared" si="1"/>
-        <v>431.52484319999991</v>
+        <v>457.41633379199993</v>
       </c>
       <c r="BD21">
         <f t="shared" si="1"/>
@@ -33230,7 +33229,7 @@
       </c>
       <c r="BE21">
         <f t="shared" si="1"/>
-        <v>47.947204799999994</v>
+        <v>50.824037087999997</v>
       </c>
       <c r="BF21">
         <f t="shared" si="2"/>
@@ -33238,7 +33237,7 @@
       </c>
       <c r="BG21">
         <f t="shared" si="2"/>
-        <v>409.51707619679991</v>
+        <v>434.08810076860789</v>
       </c>
       <c r="BH21">
         <f t="shared" si="2"/>
@@ -33250,7 +33249,7 @@
       </c>
       <c r="BJ21">
         <f t="shared" si="3"/>
-        <v>409.51707619679991</v>
+        <v>434.08810076860789</v>
       </c>
       <c r="BK21">
         <f t="shared" si="3"/>
@@ -33270,7 +33269,7 @@
       </c>
       <c r="BO21">
         <f t="shared" si="4"/>
-        <v>21.576242159999996</v>
+        <v>22.870816689599998</v>
       </c>
       <c r="BP21">
         <f t="shared" si="4"/>
@@ -33282,7 +33281,7 @@
       </c>
       <c r="BR21">
         <f t="shared" si="5"/>
-        <v>81.903415239359987</v>
+        <v>86.817620153721577</v>
       </c>
       <c r="BS21">
         <f t="shared" si="5"/>
@@ -33294,7 +33293,7 @@
       </c>
       <c r="BU21">
         <f t="shared" si="10"/>
-        <v>103.47965739935998</v>
+        <v>109.68843684332157</v>
       </c>
       <c r="BV21">
         <f>Constants!$K$2</f>
@@ -33302,7 +33301,7 @@
       </c>
       <c r="BW21">
         <f t="shared" si="11"/>
-        <v>10.068913007999999</v>
+        <v>10.673047788479998</v>
       </c>
       <c r="BX21">
         <f>IF(C21="", "", _xlfn.XLOOKUP(C21,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -33314,11 +33313,11 @@
       </c>
       <c r="BZ21">
         <f t="shared" si="12"/>
-        <v>0.959404252174066</v>
+        <v>1.0169685073045098</v>
       </c>
       <c r="CA21">
         <f t="shared" si="13"/>
-        <v>9.3353207745599992E-2</v>
+        <v>9.8954400210335983E-2</v>
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.2">
@@ -33368,7 +33367,7 @@
       </c>
       <c r="L22">
         <f>IF('Input Scenarios'!L43&lt;&gt;"", 'Input Scenarios'!L43,_xlfn.XLOOKUP($F22,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M22">
         <f>'Input Scenarios'!M43</f>
@@ -33462,9 +33461,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -33480,7 +33479,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -33528,11 +33527,11 @@
       </c>
       <c r="AZ22">
         <f t="shared" si="7"/>
-        <v>2.22456E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA22">
         <f t="shared" si="0"/>
-        <v>823.00489128000004</v>
+        <v>671.06552673600004</v>
       </c>
       <c r="BB22">
         <f t="shared" si="1"/>
@@ -33540,7 +33539,7 @@
       </c>
       <c r="BC22">
         <f t="shared" si="1"/>
-        <v>740.70440215200006</v>
+        <v>603.9589740624001</v>
       </c>
       <c r="BD22">
         <f t="shared" si="1"/>
@@ -33548,7 +33547,7 @@
       </c>
       <c r="BE22">
         <f t="shared" si="1"/>
-        <v>82.300489128000009</v>
+        <v>67.106552673600007</v>
       </c>
       <c r="BF22">
         <f t="shared" si="2"/>
@@ -33556,7 +33555,7 @@
       </c>
       <c r="BG22">
         <f t="shared" si="2"/>
-        <v>702.92847764224803</v>
+        <v>573.15706638521772</v>
       </c>
       <c r="BH22">
         <f t="shared" si="2"/>
@@ -33568,7 +33567,7 @@
       </c>
       <c r="BJ22">
         <f t="shared" si="3"/>
-        <v>702.92847764224803</v>
+        <v>573.15706638521772</v>
       </c>
       <c r="BK22">
         <f t="shared" si="3"/>
@@ -33588,7 +33587,7 @@
       </c>
       <c r="BO22">
         <f t="shared" si="4"/>
-        <v>37.035220107600004</v>
+        <v>30.197948703120005</v>
       </c>
       <c r="BP22">
         <f t="shared" si="4"/>
@@ -33600,7 +33599,7 @@
       </c>
       <c r="BR22">
         <f t="shared" si="5"/>
-        <v>140.58569552844961</v>
+        <v>114.63141327704355</v>
       </c>
       <c r="BS22">
         <f t="shared" si="5"/>
@@ -33612,7 +33611,7 @@
       </c>
       <c r="BU22">
         <f t="shared" si="10"/>
-        <v>177.6209156360496</v>
+        <v>144.82936198016355</v>
       </c>
       <c r="BV22">
         <f>Constants!$K$2</f>
@@ -33620,7 +33619,7 @@
       </c>
       <c r="BW22">
         <f t="shared" si="11"/>
-        <v>17.283102716880002</v>
+        <v>14.092376061456001</v>
       </c>
       <c r="BX22">
         <f>IF(C22="", "", _xlfn.XLOOKUP(C22,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -33632,11 +33631,11 @@
       </c>
       <c r="BZ22">
         <f t="shared" si="12"/>
-        <v>1.6467996321113743</v>
+        <v>1.3427750846446593</v>
       </c>
       <c r="CA22">
         <f t="shared" si="13"/>
-        <v>0.160239052332216</v>
+        <v>0.13065645805549922</v>
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.2">
@@ -33780,9 +33779,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -33798,7 +33797,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -33958,7 +33957,7 @@
       </c>
       <c r="CB23">
         <f>SUM(BZ23:CA26)/1000</f>
-        <v>3.9920837045930163E-3</v>
+        <v>4.1075516064681865E-3</v>
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.2">
@@ -34102,9 +34101,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -34120,7 +34119,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -34326,7 +34325,7 @@
       </c>
       <c r="L25">
         <f>IF('Input Scenarios'!L46&lt;&gt;"", 'Input Scenarios'!L46,_xlfn.XLOOKUP($F25,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M25">
         <f>'Input Scenarios'!M46</f>
@@ -34420,9 +34419,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -34438,7 +34437,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -34486,15 +34485,15 @@
       </c>
       <c r="AZ25">
         <f t="shared" si="7"/>
-        <v>1.2052799999999998E-3</v>
+        <v>1.4195519999999999E-3</v>
       </c>
       <c r="BA25">
         <f t="shared" si="0"/>
-        <v>223.09732799999995</v>
+        <v>262.75907519999998</v>
       </c>
       <c r="BB25">
         <f t="shared" si="1"/>
-        <v>22.309732799999995</v>
+        <v>26.275907520000001</v>
       </c>
       <c r="BC25">
         <f t="shared" si="1"/>
@@ -34506,11 +34505,11 @@
       </c>
       <c r="BE25">
         <f t="shared" si="1"/>
-        <v>200.78759519999997</v>
+        <v>236.48316767999998</v>
       </c>
       <c r="BF25">
         <f t="shared" si="2"/>
-        <v>15.594503227199995</v>
+        <v>18.366859356479999</v>
       </c>
       <c r="BG25">
         <f t="shared" si="2"/>
@@ -34526,11 +34525,11 @@
       </c>
       <c r="BJ25">
         <f t="shared" si="3"/>
-        <v>14.035052904479995</v>
+        <v>16.530173420832</v>
       </c>
       <c r="BK25">
         <f t="shared" si="3"/>
-        <v>1.5594503227199996</v>
+        <v>1.8366859356480001</v>
       </c>
       <c r="BL25">
         <f t="shared" si="3"/>
@@ -34542,7 +34541,7 @@
       </c>
       <c r="BN25">
         <f t="shared" si="8"/>
-        <v>6.6929198399999983</v>
+        <v>7.882772256</v>
       </c>
       <c r="BO25">
         <f t="shared" si="4"/>
@@ -34558,7 +34557,7 @@
       </c>
       <c r="BR25">
         <f t="shared" si="5"/>
-        <v>2.8070105808959993</v>
+        <v>3.3060346841664003</v>
       </c>
       <c r="BS25">
         <f t="shared" si="5"/>
@@ -34570,7 +34569,7 @@
       </c>
       <c r="BU25">
         <f t="shared" si="10"/>
-        <v>9.499930420895998</v>
+        <v>11.188806940166401</v>
       </c>
       <c r="BV25">
         <f>Constants!$K$2</f>
@@ -34578,7 +34577,7 @@
       </c>
       <c r="BW25">
         <f t="shared" si="11"/>
-        <v>42.165394991999989</v>
+        <v>49.661465212799996</v>
       </c>
       <c r="BX25">
         <f>IF(C25="", "", _xlfn.XLOOKUP(C25,Constants!$A$20:$A$24,Constants!$B$20:$B$24))</f>
@@ -34590,11 +34589,11 @@
       </c>
       <c r="BZ25">
         <f t="shared" si="12"/>
-        <v>0.11942769671983541</v>
+        <v>0.14065928724780619</v>
       </c>
       <c r="CA25">
         <f t="shared" si="13"/>
-        <v>0.53007925132799982</v>
+        <v>0.62431556267519994</v>
       </c>
       <c r="CB25"/>
       <c r="CC25"/>
@@ -34747,9 +34746,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -34765,7 +34764,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -35576,9 +35575,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -35594,7 +35593,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -35858,9 +35857,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -35876,7 +35875,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -36136,9 +36135,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -36154,7 +36153,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -36414,9 +36413,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -36432,7 +36431,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -36692,9 +36691,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -36710,7 +36709,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -36974,9 +36973,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -36992,7 +36991,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -37252,9 +37251,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -37270,7 +37269,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -37530,9 +37529,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -37548,7 +37547,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -37808,9 +37807,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -37826,7 +37825,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -38090,9 +38089,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -38108,7 +38107,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -38369,9 +38368,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -38387,7 +38386,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -38647,9 +38646,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -38665,7 +38664,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -38925,9 +38924,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -38943,7 +38942,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -39207,9 +39206,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -39225,7 +39224,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -39485,9 +39484,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -39503,7 +39502,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -39764,9 +39763,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -39782,7 +39781,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -40329,7 +40328,7 @@
       </c>
       <c r="L11">
         <f>IF('Input Scenarios'!L32&lt;&gt;"", 'Input Scenarios'!L32,_xlfn.XLOOKUP($F11,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="M11">
         <f>'Input Scenarios'!M32</f>
@@ -40423,9 +40422,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ11" t="str">
+      <c r="AJ11">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <f>Constants!$D$9</f>
@@ -40441,7 +40440,7 @@
       </c>
       <c r="AN11">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO11">
         <f>Constants!$C$12</f>
@@ -40489,43 +40488,43 @@
       </c>
       <c r="AZ11">
         <f>AY11*(1-L11)</f>
-        <v>1.8867199999999999E-3</v>
+        <v>1.8304000000000003E-3</v>
       </c>
       <c r="BA11">
         <f t="shared" ref="BA11:BA26" si="0">G11*AZ11*H11</f>
-        <v>471.68</v>
+        <v>457.6</v>
       </c>
       <c r="BB11">
         <f t="shared" ref="BB11:BE26" si="1">$BA11*M11</f>
-        <v>47.168000000000006</v>
+        <v>45.760000000000005</v>
       </c>
       <c r="BC11">
         <f t="shared" si="1"/>
-        <v>94.336000000000013</v>
+        <v>91.52000000000001</v>
       </c>
       <c r="BD11">
         <f t="shared" si="1"/>
-        <v>141.50399999999999</v>
+        <v>137.28</v>
       </c>
       <c r="BE11">
         <f t="shared" si="1"/>
-        <v>188.67200000000003</v>
+        <v>183.04000000000002</v>
       </c>
       <c r="BF11">
         <f t="shared" ref="BF11:BH26" si="2">(BB11*(1-AG11-AK11))</f>
-        <v>32.970432000000002</v>
+        <v>31.986240000000002</v>
       </c>
       <c r="BG11">
         <f t="shared" si="2"/>
-        <v>89.524864000000008</v>
+        <v>86.85248</v>
       </c>
       <c r="BH11">
         <f t="shared" si="2"/>
-        <v>84.760895999999988</v>
+        <v>82.230719999999991</v>
       </c>
       <c r="BI11">
         <f t="shared" ref="BI11:BI26" si="3">($BF11*Q11)+($BG11*V11)+($BH11*AA11)</f>
-        <v>16.485216000000001</v>
+        <v>15.993120000000001</v>
       </c>
       <c r="BJ11">
         <f>IF(E11, 1, 0)</f>
@@ -40537,11 +40536,11 @@
       </c>
       <c r="BL11">
         <f>BI11*BJ11*BK11</f>
-        <v>0.32970432000000005</v>
+        <v>0.31986240000000005</v>
       </c>
       <c r="BM11">
         <f>BE11*BJ11*BK11</f>
-        <v>3.7734400000000008</v>
+        <v>3.6608000000000005</v>
       </c>
       <c r="BN11">
         <f>Constants!$L$2</f>
@@ -40553,15 +40552,15 @@
       </c>
       <c r="BP11">
         <f>BL11*$BN11*$BO11</f>
-        <v>5.6991746742857145E-3</v>
+        <v>5.5290500571428579E-3</v>
       </c>
       <c r="BQ11">
         <f>BM11*$BN11*$BO11</f>
-        <v>6.5226605714285721E-2</v>
+        <v>6.3279542857142851E-2</v>
       </c>
       <c r="BR11">
         <f>SUM(BP11:BQ14)/1000</f>
-        <v>2.7954693818857141E-4</v>
+        <v>2.7690045384571427E-4</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.2">
@@ -40611,7 +40610,7 @@
       </c>
       <c r="L12">
         <f>IF('Input Scenarios'!L33&lt;&gt;"", 'Input Scenarios'!L33,_xlfn.XLOOKUP($F12,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="M12">
         <f>'Input Scenarios'!M33</f>
@@ -40705,9 +40704,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ12" t="str">
+      <c r="AJ12">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK12">
         <f>Constants!$D$9</f>
@@ -40723,7 +40722,7 @@
       </c>
       <c r="AN12">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO12">
         <f>Constants!$C$12</f>
@@ -40771,43 +40770,43 @@
       </c>
       <c r="AZ12">
         <f t="shared" ref="AZ12:AZ26" si="5">AY12*(1-L12)</f>
-        <v>2.0976000000000002E-3</v>
+        <v>2.0672000000000004E-3</v>
       </c>
       <c r="BA12">
         <f t="shared" si="0"/>
-        <v>524.40000000000009</v>
+        <v>516.80000000000007</v>
       </c>
       <c r="BB12">
         <f t="shared" si="1"/>
-        <v>52.440000000000012</v>
+        <v>51.680000000000007</v>
       </c>
       <c r="BC12">
         <f t="shared" si="1"/>
-        <v>104.88000000000002</v>
+        <v>103.36000000000001</v>
       </c>
       <c r="BD12">
         <f t="shared" si="1"/>
-        <v>157.32000000000002</v>
+        <v>155.04000000000002</v>
       </c>
       <c r="BE12">
         <f t="shared" si="1"/>
-        <v>209.76000000000005</v>
+        <v>206.72000000000003</v>
       </c>
       <c r="BF12">
         <f t="shared" si="2"/>
-        <v>36.655560000000008</v>
+        <v>36.124320000000004</v>
       </c>
       <c r="BG12">
         <f t="shared" si="2"/>
-        <v>99.531120000000016</v>
+        <v>98.088640000000012</v>
       </c>
       <c r="BH12">
         <f t="shared" si="2"/>
-        <v>94.234680000000012</v>
+        <v>92.868960000000015</v>
       </c>
       <c r="BI12">
         <f t="shared" si="3"/>
-        <v>18.327780000000004</v>
+        <v>18.062160000000002</v>
       </c>
       <c r="BJ12">
         <f t="shared" ref="BJ12:BJ26" si="6">IF(E12, 1, 0)</f>
@@ -40819,11 +40818,11 @@
       </c>
       <c r="BL12">
         <f t="shared" ref="BL12:BL26" si="7">BI12*BJ12*BK12</f>
-        <v>0.36655560000000009</v>
+        <v>0.36124320000000004</v>
       </c>
       <c r="BM12">
         <f t="shared" ref="BM12:BM26" si="8">BE12*BJ12*BK12</f>
-        <v>4.1952000000000007</v>
+        <v>4.1344000000000003</v>
       </c>
       <c r="BN12">
         <f>Constants!$L$2</f>
@@ -40835,11 +40834,11 @@
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BQ26" si="9">BL12*$BN12*$BO12</f>
-        <v>6.3361753714285722E-3</v>
+        <v>6.2443467428571434E-3</v>
       </c>
       <c r="BQ12">
         <f t="shared" si="9"/>
-        <v>7.2517028571428582E-2</v>
+        <v>7.1466057142857142E-2</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.2">
@@ -40889,7 +40888,7 @@
       </c>
       <c r="L13">
         <f>IF('Input Scenarios'!L34&lt;&gt;"", 'Input Scenarios'!L34,_xlfn.XLOOKUP($F13,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="M13">
         <f>'Input Scenarios'!M34</f>
@@ -40983,9 +40982,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ13" t="str">
+      <c r="AJ13">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK13">
         <f>Constants!$D$9</f>
@@ -41001,7 +41000,7 @@
       </c>
       <c r="AN13">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO13">
         <f>Constants!$C$12</f>
@@ -41049,43 +41048,43 @@
       </c>
       <c r="AZ13">
         <f t="shared" si="5"/>
-        <v>1.98E-3</v>
+        <v>1.908E-3</v>
       </c>
       <c r="BA13">
         <f t="shared" si="0"/>
-        <v>495</v>
+        <v>476.99999999999994</v>
       </c>
       <c r="BB13">
         <f t="shared" si="1"/>
-        <v>49.5</v>
+        <v>47.699999999999996</v>
       </c>
       <c r="BC13">
         <f t="shared" si="1"/>
-        <v>99</v>
+        <v>95.399999999999991</v>
       </c>
       <c r="BD13">
         <f t="shared" si="1"/>
-        <v>148.5</v>
+        <v>143.09999999999997</v>
       </c>
       <c r="BE13">
         <f t="shared" si="1"/>
-        <v>198</v>
+        <v>190.79999999999998</v>
       </c>
       <c r="BF13">
         <f t="shared" si="2"/>
-        <v>34.600499999999997</v>
+        <v>33.342299999999994</v>
       </c>
       <c r="BG13">
         <f t="shared" si="2"/>
-        <v>93.950999999999993</v>
+        <v>90.534599999999983</v>
       </c>
       <c r="BH13">
         <f t="shared" si="2"/>
-        <v>88.951499999999996</v>
+        <v>85.716899999999981</v>
       </c>
       <c r="BI13">
         <f t="shared" si="3"/>
-        <v>17.300249999999998</v>
+        <v>16.671149999999997</v>
       </c>
       <c r="BJ13">
         <f t="shared" si="6"/>
@@ -41097,11 +41096,11 @@
       </c>
       <c r="BL13">
         <f t="shared" si="7"/>
-        <v>0.34600499999999995</v>
+        <v>0.33342299999999997</v>
       </c>
       <c r="BM13">
         <f t="shared" si="8"/>
-        <v>3.96</v>
+        <v>3.8159999999999998</v>
       </c>
       <c r="BN13">
         <f>Constants!$L$2</f>
@@ -41113,11 +41112,11 @@
       </c>
       <c r="BP13">
         <f t="shared" si="9"/>
-        <v>5.9809435714285701E-3</v>
+        <v>5.7634547142857134E-3</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="9"/>
-        <v>6.8451428571428566E-2</v>
+        <v>6.5962285714285696E-2</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.2">
@@ -41167,7 +41166,7 @@
       </c>
       <c r="L14">
         <f>IF('Input Scenarios'!L35&lt;&gt;"", 'Input Scenarios'!L35,_xlfn.XLOOKUP($F14,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M14">
         <f>'Input Scenarios'!M35</f>
@@ -41261,9 +41260,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ14" t="str">
+      <c r="AJ14">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK14">
         <f>Constants!$D$9</f>
@@ -41279,7 +41278,7 @@
       </c>
       <c r="AN14">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO14">
         <f>Constants!$C$12</f>
@@ -41327,43 +41326,43 @@
       </c>
       <c r="AZ14">
         <f t="shared" si="5"/>
-        <v>1.472E-3</v>
+        <v>1.56032E-3</v>
       </c>
       <c r="BA14">
         <f t="shared" si="0"/>
-        <v>368</v>
+        <v>390.08000000000004</v>
       </c>
       <c r="BB14">
         <f t="shared" si="1"/>
-        <v>36.800000000000004</v>
+        <v>39.00800000000001</v>
       </c>
       <c r="BC14">
         <f t="shared" si="1"/>
-        <v>73.600000000000009</v>
+        <v>78.01600000000002</v>
       </c>
       <c r="BD14">
         <f t="shared" si="1"/>
-        <v>110.39999999999999</v>
+        <v>117.024</v>
       </c>
       <c r="BE14">
         <f t="shared" si="1"/>
-        <v>147.20000000000002</v>
+        <v>156.03200000000004</v>
       </c>
       <c r="BF14">
         <f t="shared" si="2"/>
-        <v>25.723200000000002</v>
+        <v>27.266592000000006</v>
       </c>
       <c r="BG14">
         <f t="shared" si="2"/>
-        <v>69.846400000000003</v>
+        <v>74.037184000000011</v>
       </c>
       <c r="BH14">
         <f t="shared" si="2"/>
-        <v>66.129599999999996</v>
+        <v>70.097375999999997</v>
       </c>
       <c r="BI14">
         <f t="shared" si="3"/>
-        <v>12.861600000000001</v>
+        <v>13.633296000000003</v>
       </c>
       <c r="BJ14">
         <f t="shared" si="6"/>
@@ -41375,11 +41374,11 @@
       </c>
       <c r="BL14">
         <f t="shared" si="7"/>
-        <v>0.25723200000000002</v>
+        <v>0.27266592000000006</v>
       </c>
       <c r="BM14">
         <f t="shared" si="8"/>
-        <v>2.9440000000000004</v>
+        <v>3.1206400000000007</v>
       </c>
       <c r="BN14">
         <f>Constants!$L$2</f>
@@ -41391,11 +41390,11 @@
       </c>
       <c r="BP14">
         <f t="shared" si="9"/>
-        <v>4.4464388571428572E-3</v>
+        <v>4.713225188571429E-3</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="9"/>
-        <v>5.0889142857142862E-2</v>
+        <v>5.394249142857143E-2</v>
       </c>
     </row>
     <row r="15" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -41539,9 +41538,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ15" t="str">
+      <c r="AJ15">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK15">
         <f>Constants!$D$9</f>
@@ -41557,7 +41556,7 @@
       </c>
       <c r="AN15">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO15">
         <f>Constants!$C$12</f>
@@ -41677,7 +41676,7 @@
       </c>
       <c r="BR15">
         <f>SUM(BP15:BQ18)/1000</f>
-        <v>2.4046369294266004E-4</v>
+        <v>2.3843904166933713E-4</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.2">
@@ -41821,9 +41820,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ16" t="str">
+      <c r="AJ16">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK16">
         <f>Constants!$D$9</f>
@@ -41839,7 +41838,7 @@
       </c>
       <c r="AN16">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO16">
         <f>Constants!$C$12</f>
@@ -42005,7 +42004,7 @@
       </c>
       <c r="L17">
         <f>IF('Input Scenarios'!L38&lt;&gt;"", 'Input Scenarios'!L38,_xlfn.XLOOKUP($F17,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.4</v>
+        <v>0.47</v>
       </c>
       <c r="M17">
         <f>'Input Scenarios'!M38</f>
@@ -42099,9 +42098,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ17" t="str">
+      <c r="AJ17">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK17">
         <f>Constants!$D$9</f>
@@ -42117,7 +42116,7 @@
       </c>
       <c r="AN17">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO17">
         <f>Constants!$C$12</f>
@@ -42165,43 +42164,43 @@
       </c>
       <c r="AZ17">
         <f t="shared" si="5"/>
-        <v>1.7443200000000002E-3</v>
+        <v>1.5408160000000002E-3</v>
       </c>
       <c r="BA17">
         <f t="shared" si="0"/>
-        <v>490.59000000000003</v>
+        <v>433.35450000000003</v>
       </c>
       <c r="BB17">
         <f t="shared" si="1"/>
-        <v>196.23600000000002</v>
+        <v>173.34180000000003</v>
       </c>
       <c r="BC17">
         <f t="shared" si="1"/>
-        <v>147.17699999999999</v>
+        <v>130.00635</v>
       </c>
       <c r="BD17">
         <f t="shared" si="1"/>
-        <v>98.118000000000009</v>
+        <v>86.670900000000017</v>
       </c>
       <c r="BE17">
         <f t="shared" si="1"/>
-        <v>49.059000000000005</v>
+        <v>43.335450000000009</v>
       </c>
       <c r="BF17">
         <f t="shared" si="2"/>
-        <v>137.16896400000002</v>
+        <v>121.16591820000002</v>
       </c>
       <c r="BG17">
         <f t="shared" si="2"/>
-        <v>139.67097299999998</v>
+        <v>123.37602614999999</v>
       </c>
       <c r="BH17">
         <f t="shared" si="2"/>
-        <v>58.772682000000003</v>
+        <v>51.915869100000009</v>
       </c>
       <c r="BI17">
         <f t="shared" si="3"/>
-        <v>104.30826462</v>
+        <v>92.138967081000004</v>
       </c>
       <c r="BJ17">
         <f t="shared" si="6"/>
@@ -42213,11 +42212,11 @@
       </c>
       <c r="BL17">
         <f t="shared" si="7"/>
-        <v>2.0861652924</v>
+        <v>1.84277934162</v>
       </c>
       <c r="BM17">
         <f t="shared" si="8"/>
-        <v>0.98118000000000016</v>
+        <v>0.86670900000000017</v>
       </c>
       <c r="BN17">
         <f>Constants!$L$2</f>
@@ -42229,11 +42228,11 @@
       </c>
       <c r="BP17">
         <f t="shared" si="9"/>
-        <v>3.6060857197200001E-2</v>
+        <v>3.1853757190859998E-2</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="9"/>
-        <v>1.6960397142857145E-2</v>
+        <v>1.4981684142857143E-2</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.2">
@@ -42283,7 +42282,7 @@
       </c>
       <c r="L18">
         <f>IF('Input Scenarios'!L39&lt;&gt;"", 'Input Scenarios'!L39,_xlfn.XLOOKUP($F18,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M18">
         <f>'Input Scenarios'!M39</f>
@@ -42377,9 +42376,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ18" t="str">
+      <c r="AJ18">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK18">
         <f>Constants!$D$9</f>
@@ -42395,7 +42394,7 @@
       </c>
       <c r="AN18">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO18">
         <f>Constants!$C$12</f>
@@ -42443,43 +42442,43 @@
       </c>
       <c r="AZ18">
         <f t="shared" si="5"/>
-        <v>1.6769759999999999E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA18">
         <f t="shared" si="0"/>
-        <v>471.64949999999999</v>
+        <v>510.1515</v>
       </c>
       <c r="BB18">
         <f t="shared" si="1"/>
-        <v>188.65980000000002</v>
+        <v>204.06060000000002</v>
       </c>
       <c r="BC18">
         <f t="shared" si="1"/>
-        <v>141.49484999999999</v>
+        <v>153.04544999999999</v>
       </c>
       <c r="BD18">
         <f t="shared" si="1"/>
-        <v>94.329900000000009</v>
+        <v>102.03030000000001</v>
       </c>
       <c r="BE18">
         <f t="shared" si="1"/>
-        <v>47.164950000000005</v>
+        <v>51.015150000000006</v>
       </c>
       <c r="BF18">
         <f t="shared" si="2"/>
-        <v>131.87320020000001</v>
+        <v>142.63835940000001</v>
       </c>
       <c r="BG18">
         <f t="shared" si="2"/>
-        <v>134.27861264999999</v>
+        <v>145.24013204999997</v>
       </c>
       <c r="BH18">
         <f t="shared" si="2"/>
-        <v>56.503610100000003</v>
+        <v>61.116149700000001</v>
       </c>
       <c r="BI18">
         <f t="shared" si="3"/>
-        <v>100.28117339100001</v>
+        <v>108.467391627</v>
       </c>
       <c r="BJ18">
         <f t="shared" si="6"/>
@@ -42491,11 +42490,11 @@
       </c>
       <c r="BL18">
         <f t="shared" si="7"/>
-        <v>2.0056234678200004</v>
+        <v>2.1693478325400002</v>
       </c>
       <c r="BM18">
         <f t="shared" si="8"/>
-        <v>0.94329900000000011</v>
+        <v>1.0203030000000002</v>
       </c>
       <c r="BN18">
         <f>Constants!$L$2</f>
@@ -42507,11 +42506,11 @@
       </c>
       <c r="BP18">
         <f t="shared" si="9"/>
-        <v>3.466863422946001E-2</v>
+        <v>3.749872681962E-2</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="9"/>
-        <v>1.6305597000000002E-2</v>
+        <v>1.7636666142857145E-2</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.2">
@@ -42561,7 +42560,7 @@
       </c>
       <c r="L19">
         <f>IF('Input Scenarios'!L40&lt;&gt;"", 'Input Scenarios'!L40,_xlfn.XLOOKUP($F19,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="M19">
         <f>'Input Scenarios'!M40</f>
@@ -42655,9 +42654,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ19" t="str">
+      <c r="AJ19">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK19">
         <f>Constants!$D$9</f>
@@ -42673,7 +42672,7 @@
       </c>
       <c r="AN19">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO19">
         <f>Constants!$C$12</f>
@@ -42721,11 +42720,11 @@
       </c>
       <c r="AZ19">
         <f t="shared" si="5"/>
-        <v>1.7089919999999999E-3</v>
+        <v>1.6099199999999999E-3</v>
       </c>
       <c r="BA19">
         <f t="shared" si="0"/>
-        <v>632.26380729599998</v>
+        <v>595.61083295999993</v>
       </c>
       <c r="BB19">
         <f t="shared" si="1"/>
@@ -42733,7 +42732,7 @@
       </c>
       <c r="BC19">
         <f t="shared" si="1"/>
-        <v>569.03742656639997</v>
+        <v>536.04974966399993</v>
       </c>
       <c r="BD19">
         <f t="shared" si="1"/>
@@ -42741,7 +42740,7 @@
       </c>
       <c r="BE19">
         <f t="shared" si="1"/>
-        <v>63.226380729600002</v>
+        <v>59.561083295999993</v>
       </c>
       <c r="BF19">
         <f t="shared" si="2"/>
@@ -42749,7 +42748,7 @@
       </c>
       <c r="BG19">
         <f t="shared" si="2"/>
-        <v>540.01651781151349</v>
+        <v>508.71121243113589</v>
       </c>
       <c r="BH19">
         <f t="shared" si="2"/>
@@ -42773,7 +42772,7 @@
       </c>
       <c r="BM19">
         <f t="shared" si="8"/>
-        <v>1.2645276145920001</v>
+        <v>1.1912216659199999</v>
       </c>
       <c r="BN19">
         <f>Constants!$L$2</f>
@@ -42789,11 +42788,11 @@
       </c>
       <c r="BQ19">
         <f t="shared" si="9"/>
-        <v>2.1858263052233144E-2</v>
+        <v>2.0591117368045711E-2</v>
       </c>
       <c r="BR19">
         <f>SUM(BP19:BQ22)/1000</f>
-        <v>8.8913435264393153E-5</v>
+        <v>8.8594397777046855E-5</v>
       </c>
     </row>
     <row r="20" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -42843,7 +42842,7 @@
       </c>
       <c r="L20">
         <f>IF('Input Scenarios'!L41&lt;&gt;"", 'Input Scenarios'!L41,_xlfn.XLOOKUP($F20,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="M20">
         <f>'Input Scenarios'!M41</f>
@@ -42937,9 +42936,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ20" t="str">
+      <c r="AJ20">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK20">
         <f>Constants!$D$9</f>
@@ -42955,7 +42954,7 @@
       </c>
       <c r="AN20">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO20">
         <f>Constants!$C$12</f>
@@ -43003,11 +43002,11 @@
       </c>
       <c r="AZ20">
         <f t="shared" si="5"/>
-        <v>1.7221600000000004E-3</v>
+        <v>2.1292159999999997E-3</v>
       </c>
       <c r="BA20">
         <f t="shared" si="0"/>
-        <v>637.13548008000009</v>
+        <v>787.7311390079999</v>
       </c>
       <c r="BB20">
         <f t="shared" si="1"/>
@@ -43015,7 +43014,7 @@
       </c>
       <c r="BC20">
         <f t="shared" si="1"/>
-        <v>573.42193207200012</v>
+        <v>708.95802510719989</v>
       </c>
       <c r="BD20">
         <f t="shared" si="1"/>
@@ -43023,7 +43022,7 @@
       </c>
       <c r="BE20">
         <f t="shared" si="1"/>
-        <v>63.713548008000011</v>
+        <v>78.773113900799999</v>
       </c>
       <c r="BF20">
         <f t="shared" si="2"/>
@@ -43031,7 +43030,7 @@
       </c>
       <c r="BG20">
         <f t="shared" si="2"/>
-        <v>544.17741353632812</v>
+        <v>672.8011658267327</v>
       </c>
       <c r="BH20">
         <f t="shared" si="2"/>
@@ -43055,7 +43054,7 @@
       </c>
       <c r="BM20">
         <f t="shared" si="8"/>
-        <v>1.2742709601600002</v>
+        <v>1.5754622780159999</v>
       </c>
       <c r="BN20">
         <f>Constants!$L$2</f>
@@ -43071,7 +43070,7 @@
       </c>
       <c r="BQ20">
         <f t="shared" si="9"/>
-        <v>2.2026683739908574E-2</v>
+        <v>2.7232990805705137E-2</v>
       </c>
       <c r="BR20"/>
     </row>
@@ -43122,7 +43121,7 @@
       </c>
       <c r="L21">
         <f>IF('Input Scenarios'!L42&lt;&gt;"", 'Input Scenarios'!L42,_xlfn.XLOOKUP($F21,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="M21">
         <f>'Input Scenarios'!M42</f>
@@ -43216,9 +43215,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ21" t="str">
+      <c r="AJ21">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK21">
         <f>Constants!$D$9</f>
@@ -43234,7 +43233,7 @@
       </c>
       <c r="AN21">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO21">
         <f>Constants!$C$12</f>
@@ -43282,11 +43281,11 @@
       </c>
       <c r="AZ21">
         <f t="shared" si="5"/>
-        <v>1.2959999999999998E-3</v>
+        <v>1.3737599999999999E-3</v>
       </c>
       <c r="BA21">
         <f t="shared" si="0"/>
-        <v>479.47204799999992</v>
+        <v>508.24037087999994</v>
       </c>
       <c r="BB21">
         <f t="shared" si="1"/>
@@ -43294,7 +43293,7 @@
       </c>
       <c r="BC21">
         <f t="shared" si="1"/>
-        <v>431.52484319999991</v>
+        <v>457.41633379199993</v>
       </c>
       <c r="BD21">
         <f t="shared" si="1"/>
@@ -43302,7 +43301,7 @@
       </c>
       <c r="BE21">
         <f t="shared" si="1"/>
-        <v>47.947204799999994</v>
+        <v>50.824037087999997</v>
       </c>
       <c r="BF21">
         <f t="shared" si="2"/>
@@ -43310,7 +43309,7 @@
       </c>
       <c r="BG21">
         <f t="shared" si="2"/>
-        <v>409.51707619679991</v>
+        <v>434.08810076860789</v>
       </c>
       <c r="BH21">
         <f t="shared" si="2"/>
@@ -43334,7 +43333,7 @@
       </c>
       <c r="BM21">
         <f t="shared" si="8"/>
-        <v>0.95894409599999986</v>
+        <v>1.0164807417599999</v>
       </c>
       <c r="BN21">
         <f>Constants!$L$2</f>
@@ -43350,7 +43349,7 @@
       </c>
       <c r="BQ21">
         <f t="shared" si="9"/>
-        <v>1.6576033659428568E-2</v>
+        <v>1.7570595678994282E-2</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.2">
@@ -43400,7 +43399,7 @@
       </c>
       <c r="L22">
         <f>IF('Input Scenarios'!L43&lt;&gt;"", 'Input Scenarios'!L43,_xlfn.XLOOKUP($F22,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M22">
         <f>'Input Scenarios'!M43</f>
@@ -43494,9 +43493,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ22" t="str">
+      <c r="AJ22">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK22">
         <f>Constants!$D$9</f>
@@ -43512,7 +43511,7 @@
       </c>
       <c r="AN22">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO22">
         <f>Constants!$C$12</f>
@@ -43560,11 +43559,11 @@
       </c>
       <c r="AZ22">
         <f t="shared" si="5"/>
-        <v>2.22456E-3</v>
+        <v>1.813872E-3</v>
       </c>
       <c r="BA22">
         <f t="shared" si="0"/>
-        <v>823.00489128000004</v>
+        <v>671.06552673600004</v>
       </c>
       <c r="BB22">
         <f t="shared" si="1"/>
@@ -43572,7 +43571,7 @@
       </c>
       <c r="BC22">
         <f t="shared" si="1"/>
-        <v>740.70440215200006</v>
+        <v>603.9589740624001</v>
       </c>
       <c r="BD22">
         <f t="shared" si="1"/>
@@ -43580,7 +43579,7 @@
       </c>
       <c r="BE22">
         <f t="shared" si="1"/>
-        <v>82.300489128000009</v>
+        <v>67.106552673600007</v>
       </c>
       <c r="BF22">
         <f t="shared" si="2"/>
@@ -43588,7 +43587,7 @@
       </c>
       <c r="BG22">
         <f t="shared" si="2"/>
-        <v>702.92847764224803</v>
+        <v>573.15706638521772</v>
       </c>
       <c r="BH22">
         <f t="shared" si="2"/>
@@ -43612,7 +43611,7 @@
       </c>
       <c r="BM22">
         <f t="shared" si="8"/>
-        <v>1.6460097825600002</v>
+        <v>1.3421310534720001</v>
       </c>
       <c r="BN22">
         <f>Constants!$L$2</f>
@@ -43628,7 +43627,7 @@
       </c>
       <c r="BQ22">
         <f t="shared" si="9"/>
-        <v>2.845245481282286E-2</v>
+        <v>2.3199693924301715E-2</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.2">
@@ -43772,9 +43771,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ23" t="str">
+      <c r="AJ23">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK23">
         <f>Constants!$D$9</f>
@@ -43790,7 +43789,7 @@
       </c>
       <c r="AN23">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <f>Constants!$C$12</f>
@@ -44054,9 +44053,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ24" t="str">
+      <c r="AJ24">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK24">
         <f>Constants!$D$9</f>
@@ -44072,7 +44071,7 @@
       </c>
       <c r="AN24">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO24">
         <f>Constants!$C$12</f>
@@ -44238,7 +44237,7 @@
       </c>
       <c r="L25">
         <f>IF('Input Scenarios'!L46&lt;&gt;"", 'Input Scenarios'!L46,_xlfn.XLOOKUP($F25,Constants!$A$2:$A$5,Constants!E$2:E$5))</f>
-        <v>0.55000000000000004</v>
+        <v>0.47</v>
       </c>
       <c r="M25">
         <f>'Input Scenarios'!M46</f>
@@ -44332,9 +44331,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ25" t="str">
+      <c r="AJ25">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK25">
         <f>Constants!$D$9</f>
@@ -44350,7 +44349,7 @@
       </c>
       <c r="AN25">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO25">
         <f>Constants!$C$12</f>
@@ -44398,15 +44397,15 @@
       </c>
       <c r="AZ25">
         <f t="shared" si="5"/>
-        <v>1.2052799999999998E-3</v>
+        <v>1.4195519999999999E-3</v>
       </c>
       <c r="BA25">
         <f t="shared" si="0"/>
-        <v>223.09732799999995</v>
+        <v>262.75907519999998</v>
       </c>
       <c r="BB25">
         <f t="shared" si="1"/>
-        <v>22.309732799999995</v>
+        <v>26.275907520000001</v>
       </c>
       <c r="BC25">
         <f t="shared" si="1"/>
@@ -44418,11 +44417,11 @@
       </c>
       <c r="BE25">
         <f t="shared" si="1"/>
-        <v>200.78759519999997</v>
+        <v>236.48316767999998</v>
       </c>
       <c r="BF25">
         <f t="shared" si="2"/>
-        <v>15.594503227199995</v>
+        <v>18.366859356479999</v>
       </c>
       <c r="BG25">
         <f t="shared" si="2"/>
@@ -44611,9 +44610,9 @@
         <f>Constants!$C$11</f>
         <v>0.4</v>
       </c>
-      <c r="AJ26" t="str">
+      <c r="AJ26">
         <f>Constants!$C$16</f>
-        <v>N/A</v>
+        <v>0</v>
       </c>
       <c r="AK26">
         <f>Constants!$D$9</f>
@@ -44629,7 +44628,7 @@
       </c>
       <c r="AN26">
         <f>Constants!$D$16</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AO26">
         <f>Constants!$C$12</f>
@@ -46563,19 +46562,17 @@
       <c r="H32">
         <v>50</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I32" s="20">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="J32" s="21">
+      <c r="J32" s="20">
         <v>0.8</v>
       </c>
-      <c r="K32" s="21">
-        <v>0.2</v>
-      </c>
-      <c r="L32" s="21">
-        <v>0.33</v>
-      </c>
-      <c r="M32" s="23">
+      <c r="K32" s="20">
+        <v>0.2</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="22">
         <v>0.1</v>
       </c>
       <c r="N32">
@@ -46587,7 +46584,7 @@
       <c r="P32">
         <v>0.4</v>
       </c>
-      <c r="Q32" s="23">
+      <c r="Q32" s="22">
         <v>0.5</v>
       </c>
       <c r="R32">
@@ -46602,7 +46599,7 @@
       <c r="U32">
         <v>0</v>
       </c>
-      <c r="V32" s="23">
+      <c r="V32" s="22">
         <v>0</v>
       </c>
       <c r="W32">
@@ -46617,7 +46614,7 @@
       <c r="Z32">
         <v>0</v>
       </c>
-      <c r="AA32" s="23">
+      <c r="AA32" s="22">
         <v>0</v>
       </c>
       <c r="AB32">
@@ -46658,19 +46655,17 @@
       <c r="H33">
         <v>50</v>
       </c>
-      <c r="I33" s="21">
+      <c r="I33" s="20">
         <v>0.1</v>
       </c>
-      <c r="J33" s="21">
+      <c r="J33" s="20">
         <v>0.8</v>
       </c>
-      <c r="K33" s="21">
+      <c r="K33" s="20">
         <v>0.19</v>
       </c>
-      <c r="L33" s="21">
-        <v>0.31</v>
-      </c>
-      <c r="M33" s="24">
+      <c r="L33" s="20"/>
+      <c r="M33" s="23">
         <v>0.1</v>
       </c>
       <c r="N33">
@@ -46682,7 +46677,7 @@
       <c r="P33">
         <v>0.4</v>
       </c>
-      <c r="Q33" s="24">
+      <c r="Q33" s="23">
         <v>0.5</v>
       </c>
       <c r="R33">
@@ -46697,7 +46692,7 @@
       <c r="U33">
         <v>0</v>
       </c>
-      <c r="V33" s="24">
+      <c r="V33" s="23">
         <v>0</v>
       </c>
       <c r="W33">
@@ -46712,7 +46707,7 @@
       <c r="Z33">
         <v>0</v>
       </c>
-      <c r="AA33" s="24">
+      <c r="AA33" s="23">
         <v>0</v>
       </c>
       <c r="AB33">
@@ -46753,19 +46748,17 @@
       <c r="H34">
         <v>50</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="20">
         <v>0.09</v>
       </c>
-      <c r="J34" s="21">
+      <c r="J34" s="20">
         <v>0.8</v>
       </c>
-      <c r="K34" s="21">
+      <c r="K34" s="20">
         <v>0.25</v>
       </c>
-      <c r="L34" s="21">
-        <v>0.45</v>
-      </c>
-      <c r="M34" s="24">
+      <c r="L34" s="20"/>
+      <c r="M34" s="23">
         <v>0.1</v>
       </c>
       <c r="N34">
@@ -46777,7 +46770,7 @@
       <c r="P34">
         <v>0.4</v>
       </c>
-      <c r="Q34" s="24">
+      <c r="Q34" s="23">
         <v>0.5</v>
       </c>
       <c r="R34">
@@ -46792,7 +46785,7 @@
       <c r="U34">
         <v>0</v>
       </c>
-      <c r="V34" s="24">
+      <c r="V34" s="23">
         <v>0</v>
       </c>
       <c r="W34">
@@ -46807,7 +46800,7 @@
       <c r="Z34">
         <v>0</v>
       </c>
-      <c r="AA34" s="24">
+      <c r="AA34" s="23">
         <v>0</v>
       </c>
       <c r="AB34">
@@ -46848,19 +46841,17 @@
       <c r="H35" s="11">
         <v>50</v>
       </c>
-      <c r="I35" s="22">
+      <c r="I35" s="21">
         <v>0.08</v>
       </c>
-      <c r="J35" s="22">
+      <c r="J35" s="21">
         <v>0.8</v>
       </c>
-      <c r="K35" s="22">
+      <c r="K35" s="21">
         <v>0.23</v>
       </c>
-      <c r="L35" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="M35" s="25">
+      <c r="L35" s="21"/>
+      <c r="M35" s="24">
         <v>0.1</v>
       </c>
       <c r="N35" s="11">
@@ -46872,7 +46863,7 @@
       <c r="P35" s="11">
         <v>0.4</v>
       </c>
-      <c r="Q35" s="25">
+      <c r="Q35" s="24">
         <v>0.5</v>
       </c>
       <c r="R35" s="11">
@@ -46887,7 +46878,7 @@
       <c r="U35" s="11">
         <v>0</v>
       </c>
-      <c r="V35" s="25">
+      <c r="V35" s="24">
         <v>0</v>
       </c>
       <c r="W35" s="11">
@@ -46902,7 +46893,7 @@
       <c r="Z35" s="11">
         <v>0</v>
       </c>
-      <c r="AA35" s="25">
+      <c r="AA35" s="24">
         <v>0</v>
       </c>
       <c r="AB35" s="11">
@@ -46922,7 +46913,7 @@
       <c r="A36" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36">
         <v>15</v>
       </c>
       <c r="C36" t="s">
@@ -46943,19 +46934,17 @@
       <c r="H36">
         <v>125</v>
       </c>
-      <c r="I36" s="21">
+      <c r="I36" s="20">
         <v>0.06</v>
       </c>
-      <c r="J36" s="21">
+      <c r="J36" s="20">
         <v>0.9</v>
       </c>
-      <c r="K36" s="21">
+      <c r="K36" s="20">
         <v>0.24</v>
       </c>
-      <c r="L36" s="21">
-        <v>0.35</v>
-      </c>
-      <c r="M36" s="24">
+      <c r="L36" s="20"/>
+      <c r="M36" s="23">
         <v>0.4</v>
       </c>
       <c r="N36">
@@ -46967,7 +46956,7 @@
       <c r="P36">
         <v>0.1</v>
       </c>
-      <c r="Q36" s="24">
+      <c r="Q36" s="23">
         <v>0.2</v>
       </c>
       <c r="R36">
@@ -46982,7 +46971,7 @@
       <c r="U36">
         <v>0.1</v>
       </c>
-      <c r="V36" s="24">
+      <c r="V36" s="23">
         <v>0.34</v>
       </c>
       <c r="W36">
@@ -46997,7 +46986,7 @@
       <c r="Z36">
         <v>0.06</v>
       </c>
-      <c r="AA36" s="24">
+      <c r="AA36" s="23">
         <v>0.5</v>
       </c>
       <c r="AB36">
@@ -47017,7 +47006,7 @@
       <c r="A37" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37">
         <v>15</v>
       </c>
       <c r="C37" t="s">
@@ -47038,19 +47027,17 @@
       <c r="H37">
         <v>125</v>
       </c>
-      <c r="I37" s="21">
+      <c r="I37" s="20">
         <v>0.11</v>
       </c>
-      <c r="J37" s="21">
+      <c r="J37" s="20">
         <v>0.8</v>
       </c>
-      <c r="K37" s="21">
+      <c r="K37" s="20">
         <v>0.25</v>
       </c>
-      <c r="L37" s="21">
-        <v>0.32</v>
-      </c>
-      <c r="M37" s="24">
+      <c r="L37" s="20"/>
+      <c r="M37" s="23">
         <v>0.4</v>
       </c>
       <c r="N37">
@@ -47062,7 +47049,7 @@
       <c r="P37">
         <v>0.1</v>
       </c>
-      <c r="Q37" s="24">
+      <c r="Q37" s="23">
         <v>0.2</v>
       </c>
       <c r="R37">
@@ -47077,7 +47064,7 @@
       <c r="U37">
         <v>0.1</v>
       </c>
-      <c r="V37" s="24">
+      <c r="V37" s="23">
         <v>0.34</v>
       </c>
       <c r="W37">
@@ -47092,7 +47079,7 @@
       <c r="Z37">
         <v>0.06</v>
       </c>
-      <c r="AA37" s="24">
+      <c r="AA37" s="23">
         <v>0.5</v>
       </c>
       <c r="AB37">
@@ -47112,7 +47099,7 @@
       <c r="A38" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38">
         <v>15</v>
       </c>
       <c r="C38" t="s">
@@ -47133,19 +47120,17 @@
       <c r="H38">
         <v>125</v>
       </c>
-      <c r="I38" s="21">
+      <c r="I38" s="20">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="J38" s="21">
+      <c r="J38" s="20">
         <v>0.8</v>
       </c>
-      <c r="K38" s="21">
+      <c r="K38" s="20">
         <v>0.23</v>
       </c>
-      <c r="L38" s="21">
-        <v>0.4</v>
-      </c>
-      <c r="M38" s="24">
+      <c r="L38" s="20"/>
+      <c r="M38" s="23">
         <v>0.4</v>
       </c>
       <c r="N38">
@@ -47157,7 +47142,7 @@
       <c r="P38">
         <v>0.1</v>
       </c>
-      <c r="Q38" s="24">
+      <c r="Q38" s="23">
         <v>0.2</v>
       </c>
       <c r="R38">
@@ -47172,7 +47157,7 @@
       <c r="U38">
         <v>0.1</v>
       </c>
-      <c r="V38" s="24">
+      <c r="V38" s="23">
         <v>0.34</v>
       </c>
       <c r="W38">
@@ -47187,7 +47172,7 @@
       <c r="Z38">
         <v>0.06</v>
       </c>
-      <c r="AA38" s="24">
+      <c r="AA38" s="23">
         <v>0.5</v>
       </c>
       <c r="AB38">
@@ -47228,19 +47213,17 @@
       <c r="H39" s="11">
         <v>125</v>
       </c>
-      <c r="I39" s="22">
+      <c r="I39" s="21">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J39" s="22">
+      <c r="J39" s="21">
         <v>0.8</v>
       </c>
-      <c r="K39" s="22">
+      <c r="K39" s="21">
         <v>0.23</v>
       </c>
-      <c r="L39" s="22">
-        <v>0.51</v>
-      </c>
-      <c r="M39" s="25">
+      <c r="L39" s="21"/>
+      <c r="M39" s="24">
         <v>0.4</v>
       </c>
       <c r="N39" s="11">
@@ -47252,7 +47235,7 @@
       <c r="P39" s="11">
         <v>0.1</v>
       </c>
-      <c r="Q39" s="25">
+      <c r="Q39" s="24">
         <v>0.2</v>
       </c>
       <c r="R39" s="11">
@@ -47267,7 +47250,7 @@
       <c r="U39" s="11">
         <v>0.1</v>
       </c>
-      <c r="V39" s="25">
+      <c r="V39" s="24">
         <v>0.34</v>
       </c>
       <c r="W39" s="11">
@@ -47282,7 +47265,7 @@
       <c r="Z39" s="11">
         <v>0.06</v>
       </c>
-      <c r="AA39" s="25">
+      <c r="AA39" s="24">
         <v>0.5</v>
       </c>
       <c r="AB39" s="11">
@@ -47302,7 +47285,7 @@
       <c r="A40" t="s">
         <v>75</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40">
         <v>20</v>
       </c>
       <c r="C40" t="s">
@@ -47323,19 +47306,17 @@
       <c r="H40">
         <v>111</v>
       </c>
-      <c r="I40" s="21">
+      <c r="I40" s="20">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J40" s="21">
+      <c r="J40" s="20">
         <v>0.9</v>
       </c>
-      <c r="K40" s="21">
+      <c r="K40" s="20">
         <v>0.18</v>
       </c>
-      <c r="L40" s="21">
-        <v>0.31</v>
-      </c>
-      <c r="M40" s="24">
+      <c r="L40" s="20"/>
+      <c r="M40" s="23">
         <v>0</v>
       </c>
       <c r="N40">
@@ -47347,7 +47328,7 @@
       <c r="P40">
         <v>0.1</v>
       </c>
-      <c r="Q40" s="24">
+      <c r="Q40" s="23">
         <v>1</v>
       </c>
       <c r="R40">
@@ -47362,7 +47343,7 @@
       <c r="U40">
         <v>0</v>
       </c>
-      <c r="V40" s="24">
+      <c r="V40" s="23">
         <v>0</v>
       </c>
       <c r="W40">
@@ -47377,7 +47358,7 @@
       <c r="Z40">
         <v>0</v>
       </c>
-      <c r="AA40" s="24">
+      <c r="AA40" s="23">
         <v>0</v>
       </c>
       <c r="AB40">
@@ -47397,7 +47378,7 @@
       <c r="A41" t="s">
         <v>75</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41">
         <v>20</v>
       </c>
       <c r="C41" t="s">
@@ -47418,19 +47399,17 @@
       <c r="H41">
         <v>111</v>
       </c>
-      <c r="I41" s="21">
+      <c r="I41" s="20">
         <v>0.10299999999999999</v>
       </c>
-      <c r="J41" s="21">
+      <c r="J41" s="20">
         <v>0.7</v>
       </c>
-      <c r="K41" s="21">
+      <c r="K41" s="20">
         <v>0.19</v>
       </c>
-      <c r="L41" s="21">
-        <v>0.45</v>
-      </c>
-      <c r="M41" s="24">
+      <c r="L41" s="20"/>
+      <c r="M41" s="23">
         <v>0</v>
       </c>
       <c r="N41">
@@ -47442,7 +47421,7 @@
       <c r="P41">
         <v>0.1</v>
       </c>
-      <c r="Q41" s="24">
+      <c r="Q41" s="23">
         <v>1</v>
       </c>
       <c r="R41">
@@ -47457,7 +47436,7 @@
       <c r="U41">
         <v>0</v>
       </c>
-      <c r="V41" s="24">
+      <c r="V41" s="23">
         <v>0</v>
       </c>
       <c r="W41">
@@ -47472,7 +47451,7 @@
       <c r="Z41">
         <v>0</v>
       </c>
-      <c r="AA41" s="24">
+      <c r="AA41" s="23">
         <v>0</v>
       </c>
       <c r="AB41">
@@ -47492,7 +47471,7 @@
       <c r="A42" t="s">
         <v>75</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42">
         <v>20</v>
       </c>
       <c r="C42" t="s">
@@ -47513,19 +47492,17 @@
       <c r="H42">
         <v>111</v>
       </c>
-      <c r="I42" s="21">
+      <c r="I42" s="20">
         <v>0.09</v>
       </c>
-      <c r="J42" s="21">
+      <c r="J42" s="20">
         <v>0.9</v>
       </c>
-      <c r="K42" s="21">
+      <c r="K42" s="20">
         <v>0.18</v>
       </c>
-      <c r="L42" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="M42" s="24">
+      <c r="L42" s="20"/>
+      <c r="M42" s="23">
         <v>0</v>
       </c>
       <c r="N42">
@@ -47537,7 +47514,7 @@
       <c r="P42">
         <v>0.1</v>
       </c>
-      <c r="Q42" s="24">
+      <c r="Q42" s="23">
         <v>1</v>
       </c>
       <c r="R42">
@@ -47552,7 +47529,7 @@
       <c r="U42">
         <v>0</v>
       </c>
-      <c r="V42" s="24">
+      <c r="V42" s="23">
         <v>0</v>
       </c>
       <c r="W42">
@@ -47567,7 +47544,7 @@
       <c r="Z42">
         <v>0</v>
       </c>
-      <c r="AA42" s="24">
+      <c r="AA42" s="23">
         <v>0</v>
       </c>
       <c r="AB42">
@@ -47608,19 +47585,17 @@
       <c r="H43" s="11">
         <v>111</v>
       </c>
-      <c r="I43" s="22">
+      <c r="I43" s="21">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J43" s="22">
+      <c r="J43" s="21">
         <v>0.7</v>
       </c>
-      <c r="K43" s="22">
+      <c r="K43" s="21">
         <v>0.23</v>
       </c>
-      <c r="L43" s="22">
-        <v>0.35</v>
-      </c>
-      <c r="M43" s="25">
+      <c r="L43" s="21"/>
+      <c r="M43" s="24">
         <v>0</v>
       </c>
       <c r="N43" s="11">
@@ -47632,7 +47607,7 @@
       <c r="P43" s="11">
         <v>0.1</v>
       </c>
-      <c r="Q43" s="25">
+      <c r="Q43" s="24">
         <v>1</v>
       </c>
       <c r="R43" s="11">
@@ -47647,7 +47622,7 @@
       <c r="U43" s="11">
         <v>0</v>
       </c>
-      <c r="V43" s="25">
+      <c r="V43" s="24">
         <v>0</v>
       </c>
       <c r="W43" s="11">
@@ -47662,7 +47637,7 @@
       <c r="Z43" s="11">
         <v>0</v>
       </c>
-      <c r="AA43" s="25">
+      <c r="AA43" s="24">
         <v>0</v>
       </c>
       <c r="AB43" s="11">
@@ -47682,7 +47657,7 @@
       <c r="A44" t="s">
         <v>71</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44">
         <v>27</v>
       </c>
       <c r="C44" t="s">
@@ -47703,19 +47678,17 @@
       <c r="H44">
         <v>150</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="20">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="J44" s="21">
+      <c r="J44" s="20">
         <v>0.8</v>
       </c>
-      <c r="K44" s="21">
+      <c r="K44" s="20">
         <v>0.19</v>
       </c>
-      <c r="L44" s="21">
-        <v>0.35</v>
-      </c>
-      <c r="M44" s="24">
+      <c r="L44" s="20"/>
+      <c r="M44" s="23">
         <v>0.1</v>
       </c>
       <c r="N44">
@@ -47727,7 +47700,7 @@
       <c r="P44">
         <v>0.9</v>
       </c>
-      <c r="Q44" s="24">
+      <c r="Q44" s="23">
         <v>0</v>
       </c>
       <c r="R44">
@@ -47742,7 +47715,7 @@
       <c r="U44">
         <v>0</v>
       </c>
-      <c r="V44" s="24">
+      <c r="V44" s="23">
         <v>0</v>
       </c>
       <c r="W44">
@@ -47757,7 +47730,7 @@
       <c r="Z44">
         <v>0</v>
       </c>
-      <c r="AA44" s="24">
+      <c r="AA44" s="23">
         <v>0</v>
       </c>
       <c r="AB44">
@@ -47777,7 +47750,7 @@
       <c r="A45" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45">
         <v>27</v>
       </c>
       <c r="C45" t="s">
@@ -47798,19 +47771,17 @@
       <c r="H45">
         <v>150</v>
       </c>
-      <c r="I45" s="21">
+      <c r="I45" s="20">
         <v>0.10299999999999999</v>
       </c>
-      <c r="J45" s="21">
+      <c r="J45" s="20">
         <v>0.8</v>
       </c>
-      <c r="K45" s="21">
+      <c r="K45" s="20">
         <v>0.24</v>
       </c>
-      <c r="L45" s="21">
-        <v>0.32</v>
-      </c>
-      <c r="M45" s="24">
+      <c r="L45" s="20"/>
+      <c r="M45" s="23">
         <v>0.1</v>
       </c>
       <c r="N45">
@@ -47822,7 +47793,7 @@
       <c r="P45">
         <v>0.9</v>
       </c>
-      <c r="Q45" s="24">
+      <c r="Q45" s="23">
         <v>0</v>
       </c>
       <c r="R45">
@@ -47837,7 +47808,7 @@
       <c r="U45">
         <v>0</v>
       </c>
-      <c r="V45" s="24">
+      <c r="V45" s="23">
         <v>0</v>
       </c>
       <c r="W45">
@@ -47852,7 +47823,7 @@
       <c r="Z45">
         <v>0</v>
       </c>
-      <c r="AA45" s="24">
+      <c r="AA45" s="23">
         <v>0</v>
       </c>
       <c r="AB45">
@@ -47872,7 +47843,7 @@
       <c r="A46" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46">
         <v>27</v>
       </c>
       <c r="C46" t="s">
@@ -47893,19 +47864,17 @@
       <c r="H46">
         <v>150</v>
       </c>
-      <c r="I46" s="21">
+      <c r="I46" s="20">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J46" s="21">
+      <c r="J46" s="20">
         <v>0.8</v>
       </c>
-      <c r="K46" s="21">
+      <c r="K46" s="20">
         <v>0.18</v>
       </c>
-      <c r="L46" s="21">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="M46" s="24">
+      <c r="L46" s="20"/>
+      <c r="M46" s="23">
         <v>0.1</v>
       </c>
       <c r="N46">
@@ -47917,7 +47886,7 @@
       <c r="P46">
         <v>0.9</v>
       </c>
-      <c r="Q46" s="24">
+      <c r="Q46" s="23">
         <v>0</v>
       </c>
       <c r="R46">
@@ -47932,7 +47901,7 @@
       <c r="U46">
         <v>0</v>
       </c>
-      <c r="V46" s="24">
+      <c r="V46" s="23">
         <v>0</v>
       </c>
       <c r="W46">
@@ -47947,7 +47916,7 @@
       <c r="Z46">
         <v>0</v>
       </c>
-      <c r="AA46" s="24">
+      <c r="AA46" s="23">
         <v>0</v>
       </c>
       <c r="AB46">
@@ -47988,19 +47957,17 @@
       <c r="H47" s="11">
         <v>150</v>
       </c>
-      <c r="I47" s="22">
+      <c r="I47" s="21">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="J47" s="22">
+      <c r="J47" s="21">
         <v>0.8</v>
       </c>
-      <c r="K47" s="22">
+      <c r="K47" s="21">
         <v>0.23</v>
       </c>
-      <c r="L47" s="22">
-        <v>0.47</v>
-      </c>
-      <c r="M47" s="25">
+      <c r="L47" s="21"/>
+      <c r="M47" s="24">
         <v>0.1</v>
       </c>
       <c r="N47" s="11">
@@ -48012,7 +47979,7 @@
       <c r="P47" s="11">
         <v>0.9</v>
       </c>
-      <c r="Q47" s="25">
+      <c r="Q47" s="24">
         <v>0</v>
       </c>
       <c r="R47" s="11">
@@ -48027,7 +47994,7 @@
       <c r="U47" s="11">
         <v>0</v>
       </c>
-      <c r="V47" s="25">
+      <c r="V47" s="24">
         <v>0</v>
       </c>
       <c r="W47" s="11">
@@ -48042,7 +48009,7 @@
       <c r="Z47" s="11">
         <v>0</v>
       </c>
-      <c r="AA47" s="25">
+      <c r="AA47" s="24">
         <v>0</v>
       </c>
       <c r="AB47" s="11">

--- a/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
+++ b/packages/calculators/src/modules/test/4.6-poultry-manure/4.6-poultry-manure.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators-internal/packages/calculators/src/modules/test/4.6-poultry-manure/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888616D6-A447-A348-9176-28A0B5556B9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837CB1E4-B72B-D34F-8BA8-52541F817BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15940" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="15940" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="4.6.1.1" sheetId="5" r:id="rId1"/>
@@ -24,6 +19,9 @@
     <sheet name="Input Scenarios" sheetId="8" r:id="rId9"/>
     <sheet name="Constants" sheetId="2" r:id="rId10"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId11"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -901,6 +899,31 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6475,8 +6498,8 @@
         <v>0.6784</v>
       </c>
       <c r="J2">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
       <c r="K2">
         <v>0.21</v>
@@ -13476,19 +13499,19 @@
       </c>
       <c r="BO11">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP11">
         <f>BB11*AK11*$BO11</f>
-        <v>6.6760571428571433E-2</v>
+        <v>6.6699880000000017E-2</v>
       </c>
       <c r="BQ11">
         <f t="shared" ref="BQ11:BS11" si="13">BC11*AL11*$BO11</f>
-        <v>0.13352114285714287</v>
+        <v>0.13339976000000003</v>
       </c>
       <c r="BR11">
         <f t="shared" si="13"/>
-        <v>0.20028171428571429</v>
+        <v>0.20009964000000002</v>
       </c>
       <c r="BS11">
         <f t="shared" si="13"/>
@@ -13496,11 +13519,11 @@
       </c>
       <c r="BT11">
         <f>BI11*AT11*$BO11</f>
-        <v>0.22000946314285716</v>
+        <v>0.21980945454000003</v>
       </c>
       <c r="BU11">
         <f t="shared" ref="BU11:BW11" si="14">BJ11*AU11*$BO11</f>
-        <v>0.58669190171428576</v>
+        <v>0.58615854544000001</v>
       </c>
       <c r="BV11">
         <f t="shared" si="14"/>
@@ -13512,15 +13535,15 @@
       </c>
       <c r="BX11">
         <f>BE11* BN11*BO11</f>
-        <v>1.6022537142857147</v>
+        <v>1.6007971200000006</v>
       </c>
       <c r="BY11">
         <f>SUM(BP11:BW11)</f>
-        <v>1.2072647934285716</v>
+        <v>1.2061672799800001</v>
       </c>
       <c r="BZ11">
         <f>SUM(BX11:BY14)/1000</f>
-        <v>1.2327387392571429E-2</v>
+        <v>1.2316180676760002E-2</v>
       </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.2">
@@ -13790,19 +13813,19 @@
       </c>
       <c r="BO12">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BP26" si="17">BB12*AK12*$BO12</f>
-        <v>8.3647771428571438E-2</v>
+        <v>8.3571728000000012E-2</v>
       </c>
       <c r="BQ12">
         <f t="shared" ref="BQ12:BQ26" si="18">BC12*AL12*$BO12</f>
-        <v>0.16729554285714288</v>
+        <v>0.16714345600000002</v>
       </c>
       <c r="BR12">
         <f t="shared" ref="BR12:BR26" si="19">BD12*AM12*$BO12</f>
-        <v>0.25094331428571426</v>
+        <v>0.25071518399999998</v>
       </c>
       <c r="BS12">
         <f t="shared" ref="BS12:BS26" si="20">BE12*AN12*$BO12</f>
@@ -13810,11 +13833,11 @@
       </c>
       <c r="BT12">
         <f t="shared" ref="BT12:BT26" si="21">BI12*AT12*$BO12</f>
-        <v>0.27566123074285709</v>
+        <v>0.27541062962399998</v>
       </c>
       <c r="BU12">
         <f t="shared" ref="BU12:BU26" si="22">BJ12*AU12*$BO12</f>
-        <v>0.73509661531428572</v>
+        <v>0.73442834566400006</v>
       </c>
       <c r="BV12">
         <f t="shared" ref="BV12:BV26" si="23">BK12*AV12*$BO12</f>
@@ -13826,11 +13849,11 @@
       </c>
       <c r="BX12">
         <f t="shared" ref="BX12:BX26" si="25">BE12* BN12*BO12</f>
-        <v>2.0075465142857145</v>
+        <v>2.0057214720000003</v>
       </c>
       <c r="BY12">
         <f t="shared" ref="BY12:BY26" si="26">SUM(BP12:BW12)</f>
-        <v>1.5126444746285714</v>
+        <v>1.5112693432880002</v>
       </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.2">
@@ -14100,19 +14123,19 @@
       </c>
       <c r="BO13">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP13">
         <f t="shared" si="17"/>
-        <v>7.1259257142857135E-2</v>
+        <v>7.1194476000000007E-2</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="18"/>
-        <v>0.14251851428571427</v>
+        <v>0.14238895200000001</v>
       </c>
       <c r="BR13">
         <f t="shared" si="19"/>
-        <v>0.21377777142857138</v>
+        <v>0.21358342799999996</v>
       </c>
       <c r="BS13">
         <f t="shared" si="20"/>
@@ -14120,11 +14143,11 @@
       </c>
       <c r="BT13">
         <f t="shared" si="21"/>
-        <v>0.2348348819142857</v>
+        <v>0.234621395658</v>
       </c>
       <c r="BU13">
         <f t="shared" si="22"/>
-        <v>0.62622635177142871</v>
+        <v>0.62565705508800018</v>
       </c>
       <c r="BV13">
         <f t="shared" si="23"/>
@@ -14136,11 +14159,11 @@
       </c>
       <c r="BX13">
         <f t="shared" si="25"/>
-        <v>1.7102221714285715</v>
+        <v>1.7086674240000002</v>
       </c>
       <c r="BY13">
         <f t="shared" si="26"/>
-        <v>1.2886167765428573</v>
+        <v>1.2874453067460001</v>
       </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.2">
@@ -14410,19 +14433,19 @@
       </c>
       <c r="BO14">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP14">
         <f t="shared" si="17"/>
-        <v>7.1259257142857135E-2</v>
+        <v>7.1194476000000007E-2</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="18"/>
-        <v>0.14251851428571427</v>
+        <v>0.14238895200000001</v>
       </c>
       <c r="BR14">
         <f t="shared" si="19"/>
-        <v>0.21377777142857138</v>
+        <v>0.21358342799999996</v>
       </c>
       <c r="BS14">
         <f t="shared" si="20"/>
@@ -14430,11 +14453,11 @@
       </c>
       <c r="BT14">
         <f t="shared" si="21"/>
-        <v>0.2348348819142857</v>
+        <v>0.234621395658</v>
       </c>
       <c r="BU14">
         <f t="shared" si="22"/>
-        <v>0.62622635177142871</v>
+        <v>0.62565705508800018</v>
       </c>
       <c r="BV14">
         <f t="shared" si="23"/>
@@ -14446,11 +14469,11 @@
       </c>
       <c r="BX14">
         <f t="shared" si="25"/>
-        <v>1.7102221714285715</v>
+        <v>1.7086674240000002</v>
       </c>
       <c r="BY14">
         <f t="shared" si="26"/>
-        <v>1.2886167765428573</v>
+        <v>1.2874453067460001</v>
       </c>
     </row>
     <row r="15" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -14720,19 +14743,19 @@
       </c>
       <c r="BO15">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP15">
         <f t="shared" si="17"/>
-        <v>0.30042257142857148</v>
+        <v>0.30014946000000009</v>
       </c>
       <c r="BQ15">
         <f t="shared" si="18"/>
-        <v>0.22531692857142857</v>
+        <v>0.22511209500000001</v>
       </c>
       <c r="BR15">
         <f t="shared" si="19"/>
-        <v>0.15021128571428574</v>
+        <v>0.15007473000000005</v>
       </c>
       <c r="BS15">
         <f t="shared" si="20"/>
@@ -14740,11 +14763,11 @@
       </c>
       <c r="BT15">
         <f t="shared" si="21"/>
-        <v>0.51379770278571424</v>
+        <v>0.51333061396500002</v>
       </c>
       <c r="BU15">
         <f t="shared" si="22"/>
-        <v>1.2844942569642859</v>
+        <v>1.2833265349125</v>
       </c>
       <c r="BV15">
         <f t="shared" si="23"/>
@@ -14756,15 +14779,15 @@
       </c>
       <c r="BX15">
         <f t="shared" si="25"/>
-        <v>0.15021128571428574</v>
+        <v>0.15007473000000005</v>
       </c>
       <c r="BY15">
         <f t="shared" si="26"/>
-        <v>2.4742427454642861</v>
+        <v>2.4719934338775005</v>
       </c>
       <c r="BZ15">
         <f>SUM(BX15:BY18)/1000</f>
-        <v>1.1515375836642855E-2</v>
+        <v>1.1504907313154998E-2</v>
       </c>
       <c r="CA15"/>
       <c r="CB15"/>
@@ -15043,19 +15066,19 @@
       </c>
       <c r="BO16">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP16">
         <f t="shared" si="17"/>
-        <v>0.37641497142857139</v>
+        <v>0.37607277599999994</v>
       </c>
       <c r="BQ16">
         <f t="shared" si="18"/>
-        <v>0.28231122857142849</v>
+        <v>0.28205458199999994</v>
       </c>
       <c r="BR16">
         <f t="shared" si="19"/>
-        <v>0.18820748571428569</v>
+        <v>0.18803638799999997</v>
       </c>
       <c r="BS16">
         <f t="shared" si="20"/>
@@ -15063,11 +15086,11 @@
       </c>
       <c r="BT16">
         <f t="shared" si="21"/>
-        <v>0.64376370488571411</v>
+        <v>0.64317846515399979</v>
       </c>
       <c r="BU16">
         <f t="shared" si="22"/>
-        <v>1.6094092622142855</v>
+        <v>1.6079461628849998</v>
       </c>
       <c r="BV16">
         <f t="shared" si="23"/>
@@ -15079,11 +15102,11 @@
       </c>
       <c r="BX16">
         <f t="shared" si="25"/>
-        <v>0.18820748571428569</v>
+        <v>0.18803638799999997</v>
       </c>
       <c r="BY16">
         <f t="shared" si="26"/>
-        <v>3.1001066528142851</v>
+        <v>3.0972883740389996</v>
       </c>
     </row>
     <row r="17" spans="1:87" x14ac:dyDescent="0.2">
@@ -15353,19 +15376,19 @@
       </c>
       <c r="BO17">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP17">
         <f t="shared" si="17"/>
-        <v>0.32066665714285719</v>
+        <v>0.32037514200000006</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="18"/>
-        <v>0.24049999285714285</v>
+        <v>0.24028135650000002</v>
       </c>
       <c r="BR17">
         <f t="shared" si="19"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BS17">
         <f t="shared" si="20"/>
@@ -15373,11 +15396,11 @@
       </c>
       <c r="BT17">
         <f t="shared" si="21"/>
-        <v>0.54842015037857139</v>
+        <v>0.54792158660550006</v>
       </c>
       <c r="BU17">
         <f t="shared" si="22"/>
-        <v>1.3710503759464283</v>
+        <v>1.3698039665137498</v>
       </c>
       <c r="BV17">
         <f t="shared" si="23"/>
@@ -15389,11 +15412,11 @@
       </c>
       <c r="BX17">
         <f t="shared" si="25"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BY17">
         <f t="shared" si="26"/>
-        <v>2.640970504896428</v>
+        <v>2.6385696226192499</v>
       </c>
     </row>
     <row r="18" spans="1:87" x14ac:dyDescent="0.2">
@@ -15663,19 +15686,19 @@
       </c>
       <c r="BO18">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP18">
         <f t="shared" si="17"/>
-        <v>0.32066665714285719</v>
+        <v>0.32037514200000006</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="18"/>
-        <v>0.24049999285714285</v>
+        <v>0.24028135650000002</v>
       </c>
       <c r="BR18">
         <f t="shared" si="19"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BS18">
         <f t="shared" si="20"/>
@@ -15683,11 +15706,11 @@
       </c>
       <c r="BT18">
         <f t="shared" si="21"/>
-        <v>0.54842015037857139</v>
+        <v>0.54792158660550006</v>
       </c>
       <c r="BU18">
         <f t="shared" si="22"/>
-        <v>1.3710503759464283</v>
+        <v>1.3698039665137498</v>
       </c>
       <c r="BV18">
         <f t="shared" si="23"/>
@@ -15699,11 +15722,11 @@
       </c>
       <c r="BX18">
         <f t="shared" si="25"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BY18">
         <f t="shared" si="26"/>
-        <v>2.640970504896428</v>
+        <v>2.6385696226192499</v>
       </c>
     </row>
     <row r="19" spans="1:87" x14ac:dyDescent="0.2">
@@ -15973,7 +15996,7 @@
       </c>
       <c r="BO19">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP19">
         <f t="shared" si="17"/>
@@ -15981,7 +16004,7 @@
       </c>
       <c r="BQ19">
         <f t="shared" si="18"/>
-        <v>0.88916188634742876</v>
+        <v>0.88835355735984023</v>
       </c>
       <c r="BR19">
         <f t="shared" si="19"/>
@@ -15993,11 +16016,11 @@
       </c>
       <c r="BT19">
         <f t="shared" si="21"/>
-        <v>1.4344848712443068</v>
+        <v>1.4331807940886301</v>
       </c>
       <c r="BU19">
         <f t="shared" si="22"/>
-        <v>5.0628877808622592</v>
+        <v>5.0582851556069297</v>
       </c>
       <c r="BV19">
         <f t="shared" si="23"/>
@@ -16009,15 +16032,15 @@
       </c>
       <c r="BX19">
         <f t="shared" si="25"/>
-        <v>0.59277459089828577</v>
+        <v>0.59223570490656008</v>
       </c>
       <c r="BY19">
         <f t="shared" si="26"/>
-        <v>7.3865345384539953</v>
+        <v>7.3798195070553998</v>
       </c>
       <c r="BZ19">
         <f>SUM(BX19:BY22)/1000</f>
-        <v>3.5010993696080864E-2</v>
+        <v>3.4979165519993527E-2</v>
       </c>
     </row>
     <row r="20" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -16287,7 +16310,7 @@
       </c>
       <c r="BO20">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP20">
         <f t="shared" si="17"/>
@@ -16295,7 +16318,7 @@
       </c>
       <c r="BQ20">
         <f t="shared" si="18"/>
-        <v>1.1140768965970282</v>
+        <v>1.1130640994183039</v>
       </c>
       <c r="BR20">
         <f t="shared" si="19"/>
@@ -16307,11 +16330,11 @@
       </c>
       <c r="BT20">
         <f t="shared" si="21"/>
-        <v>1.7973402572799859</v>
+        <v>1.7957063115915497</v>
       </c>
       <c r="BU20">
         <f t="shared" si="22"/>
-        <v>6.34355384922348</v>
+        <v>6.3377869820878221</v>
       </c>
       <c r="BV20">
         <f t="shared" si="23"/>
@@ -16323,11 +16346,11 @@
       </c>
       <c r="BX20">
         <f t="shared" si="25"/>
-        <v>0.74271793106468564</v>
+        <v>0.74204273294553602</v>
       </c>
       <c r="BY20">
         <f t="shared" si="26"/>
-        <v>9.2549710031004935</v>
+        <v>9.2465573930976745</v>
       </c>
       <c r="BZ20"/>
       <c r="CA20"/>
@@ -16607,7 +16630,7 @@
       </c>
       <c r="BO21">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP21">
         <f t="shared" si="17"/>
@@ -16615,7 +16638,7 @@
       </c>
       <c r="BQ21">
         <f t="shared" si="18"/>
-        <v>0.94907838781234299</v>
+        <v>0.94821558927796812</v>
       </c>
       <c r="BR21">
         <f t="shared" si="19"/>
@@ -16627,11 +16650,11 @@
       </c>
       <c r="BT21">
         <f t="shared" si="21"/>
-        <v>1.5311481630576531</v>
+        <v>1.5297562101821462</v>
       </c>
       <c r="BU21">
         <f t="shared" si="22"/>
-        <v>5.4040523402034806</v>
+        <v>5.3991395653487508</v>
       </c>
       <c r="BV21">
         <f t="shared" si="23"/>
@@ -16643,11 +16666,11 @@
       </c>
       <c r="BX21">
         <f t="shared" si="25"/>
-        <v>0.63271892520822859</v>
+        <v>0.63214372618531212</v>
       </c>
       <c r="BY21">
         <f t="shared" si="26"/>
-        <v>7.8842788910734765</v>
+        <v>7.8771113648088651</v>
       </c>
     </row>
     <row r="22" spans="1:87" x14ac:dyDescent="0.2">
@@ -16917,7 +16940,7 @@
       </c>
       <c r="BO22">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP22">
         <f t="shared" si="17"/>
@@ -16925,7 +16948,7 @@
       </c>
       <c r="BQ22">
         <f t="shared" si="18"/>
-        <v>0.94907838781234299</v>
+        <v>0.94821558927796812</v>
       </c>
       <c r="BR22">
         <f t="shared" si="19"/>
@@ -16937,11 +16960,11 @@
       </c>
       <c r="BT22">
         <f t="shared" si="21"/>
-        <v>1.5311481630576531</v>
+        <v>1.5297562101821462</v>
       </c>
       <c r="BU22">
         <f t="shared" si="22"/>
-        <v>5.4040523402034806</v>
+        <v>5.3991395653487508</v>
       </c>
       <c r="BV22">
         <f t="shared" si="23"/>
@@ -16953,11 +16976,11 @@
       </c>
       <c r="BX22">
         <f t="shared" si="25"/>
-        <v>0.63271892520822859</v>
+        <v>0.63214372618531212</v>
       </c>
       <c r="BY22">
         <f t="shared" si="26"/>
-        <v>7.8842788910734765</v>
+        <v>7.8771113648088651</v>
       </c>
     </row>
     <row r="23" spans="1:87" x14ac:dyDescent="0.2">
@@ -17227,11 +17250,11 @@
       </c>
       <c r="BO23">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP23">
         <f t="shared" si="17"/>
-        <v>4.9429527085714298E-2</v>
+        <v>4.9384591152000015E-2</v>
       </c>
       <c r="BQ23">
         <f t="shared" si="18"/>
@@ -17247,11 +17270,11 @@
       </c>
       <c r="BT23">
         <f t="shared" si="21"/>
-        <v>8.637809858228572E-2</v>
+        <v>8.6299573038120012E-2</v>
       </c>
       <c r="BU23">
         <f t="shared" si="22"/>
-        <v>8.637809858228572E-2</v>
+        <v>8.6299573038120012E-2</v>
       </c>
       <c r="BV23">
         <f t="shared" si="23"/>
@@ -17263,15 +17286,15 @@
       </c>
       <c r="BX23">
         <f t="shared" si="25"/>
-        <v>0.88973148754285736</v>
+        <v>0.88892264073600025</v>
       </c>
       <c r="BY23">
         <f t="shared" si="26"/>
-        <v>0.22218572425028577</v>
+        <v>0.22198373722824005</v>
       </c>
       <c r="BZ23">
         <f>SUM(BX23:BY26)/1000</f>
-        <v>4.8787840979177136E-3</v>
+        <v>4.8743488396468804E-3</v>
       </c>
     </row>
     <row r="24" spans="1:87" x14ac:dyDescent="0.2">
@@ -17541,11 +17564,11 @@
       </c>
       <c r="BO24">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP24">
         <f t="shared" si="17"/>
-        <v>6.1932809965714278E-2</v>
+        <v>6.1876507411199995E-2</v>
       </c>
       <c r="BQ24">
         <f t="shared" si="18"/>
@@ -17561,11 +17584,11 @@
       </c>
       <c r="BT24">
         <f t="shared" si="21"/>
-        <v>0.10822758541508568</v>
+        <v>0.10812919670107196</v>
       </c>
       <c r="BU24">
         <f t="shared" si="22"/>
-        <v>0.10822758541508568</v>
+        <v>0.10812919670107196</v>
       </c>
       <c r="BV24">
         <f t="shared" si="23"/>
@@ -17577,11 +17600,11 @@
       </c>
       <c r="BX24">
         <f t="shared" si="25"/>
-        <v>1.114790579382857</v>
+        <v>1.1137771334016</v>
       </c>
       <c r="BY24">
         <f t="shared" si="26"/>
-        <v>0.27838798079588567</v>
+        <v>0.27813490081334391</v>
       </c>
     </row>
     <row r="25" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -17851,11 +17874,11 @@
       </c>
       <c r="BO25">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP25">
         <f t="shared" si="17"/>
-        <v>5.2760353988571415E-2</v>
+        <v>5.2712390030399993E-2</v>
       </c>
       <c r="BQ25">
         <f t="shared" si="18"/>
@@ -17871,11 +17894,11 @@
       </c>
       <c r="BT25">
         <f t="shared" si="21"/>
-        <v>9.2198718595028567E-2</v>
+        <v>9.2114901578123992E-2</v>
       </c>
       <c r="BU25">
         <f t="shared" si="22"/>
-        <v>9.2198718595028567E-2</v>
+        <v>9.2114901578123992E-2</v>
       </c>
       <c r="BV25">
         <f t="shared" si="23"/>
@@ -17887,11 +17910,11 @@
       </c>
       <c r="BX25">
         <f t="shared" si="25"/>
-        <v>0.94968637179428561</v>
+        <v>0.94882302054720002</v>
       </c>
       <c r="BY25">
         <f t="shared" si="26"/>
-        <v>0.23715779117862854</v>
+        <v>0.23694219318664797</v>
       </c>
       <c r="BZ25"/>
       <c r="CA25"/>
@@ -18171,11 +18194,11 @@
       </c>
       <c r="BO26">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP26">
         <f t="shared" si="17"/>
-        <v>5.2760353988571415E-2</v>
+        <v>5.2712390030399993E-2</v>
       </c>
       <c r="BQ26">
         <f t="shared" si="18"/>
@@ -18191,11 +18214,11 @@
       </c>
       <c r="BT26">
         <f t="shared" si="21"/>
-        <v>9.2198718595028567E-2</v>
+        <v>9.2114901578123992E-2</v>
       </c>
       <c r="BU26">
         <f t="shared" si="22"/>
-        <v>9.2198718595028567E-2</v>
+        <v>9.2114901578123992E-2</v>
       </c>
       <c r="BV26">
         <f t="shared" si="23"/>
@@ -18207,11 +18230,11 @@
       </c>
       <c r="BX26">
         <f t="shared" si="25"/>
-        <v>0.94968637179428561</v>
+        <v>0.94882302054720002</v>
       </c>
       <c r="BY26">
         <f t="shared" si="26"/>
-        <v>0.23715779117862854</v>
+        <v>0.23694219318664797</v>
       </c>
     </row>
     <row r="30" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -18932,19 +18955,19 @@
       </c>
       <c r="BO11">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP11">
         <f>BB11*AK11*$BO11</f>
-        <v>7.1908571428571447E-2</v>
+        <v>7.1843200000000024E-2</v>
       </c>
       <c r="BQ11">
         <f t="shared" ref="BQ11:BS26" si="4">BC11*AL11*$BO11</f>
-        <v>0.14381714285714289</v>
+        <v>0.14368640000000005</v>
       </c>
       <c r="BR11">
         <f t="shared" si="4"/>
-        <v>0.2157257142857143</v>
+        <v>0.21552960000000002</v>
       </c>
       <c r="BS11">
         <f t="shared" si="4"/>
@@ -18952,11 +18975,11 @@
       </c>
       <c r="BT11">
         <f>BI11*AT11*$BO11</f>
-        <v>0.12566022857142858</v>
+        <v>0.12554599200000002</v>
       </c>
       <c r="BU11">
         <f t="shared" ref="BU11:BW26" si="5">BJ11*AU11*$BO11</f>
-        <v>0.25132045714285717</v>
+        <v>0.25109198400000005</v>
       </c>
       <c r="BV11">
         <f t="shared" si="5"/>
@@ -18968,15 +18991,15 @@
       </c>
       <c r="BX11">
         <f>BE11* BN11*BO11</f>
-        <v>1.7258057142857144</v>
+        <v>1.7242368000000001</v>
       </c>
       <c r="BY11">
         <f>SUM(BP11:BW11)</f>
-        <v>0.80843211428571449</v>
+        <v>0.80769717600000024</v>
       </c>
       <c r="BZ11">
         <f>SUM(BX11:BY14)/1000</f>
-        <v>1.0198313541428573E-2</v>
+        <v>1.01890423473E-2</v>
       </c>
     </row>
     <row r="12" spans="1:87" x14ac:dyDescent="0.2">
@@ -19246,19 +19269,19 @@
       </c>
       <c r="BO12">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BP26" si="8">BB12*AK12*$BO12</f>
-        <v>8.1211428571428587E-2</v>
+        <v>8.1137600000000018E-2</v>
       </c>
       <c r="BQ12">
         <f t="shared" si="4"/>
-        <v>0.16242285714285717</v>
+        <v>0.16227520000000004</v>
       </c>
       <c r="BR12">
         <f t="shared" si="4"/>
-        <v>0.24363428571428572</v>
+        <v>0.24341280000000004</v>
       </c>
       <c r="BS12">
         <f t="shared" si="4"/>
@@ -19266,11 +19289,11 @@
       </c>
       <c r="BT12">
         <f t="shared" ref="BT12:BT26" si="9">BI12*AT12*$BO12</f>
-        <v>0.14191697142857143</v>
+        <v>0.14178795600000002</v>
       </c>
       <c r="BU12">
         <f t="shared" si="5"/>
-        <v>0.28383394285714286</v>
+        <v>0.28357591200000004</v>
       </c>
       <c r="BV12">
         <f t="shared" si="5"/>
@@ -19282,11 +19305,11 @@
       </c>
       <c r="BX12">
         <f t="shared" ref="BX12:BX26" si="10">BE12* BN12*BO12</f>
-        <v>1.9490742857142858</v>
+        <v>1.9473024000000003</v>
       </c>
       <c r="BY12">
         <f t="shared" ref="BY12:BY26" si="11">SUM(BP12:BW12)</f>
-        <v>0.91301948571428571</v>
+        <v>0.91218946800000023</v>
       </c>
     </row>
     <row r="13" spans="1:87" x14ac:dyDescent="0.2">
@@ -19556,19 +19579,19 @@
       </c>
       <c r="BO13">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP13">
         <f t="shared" si="8"/>
-        <v>7.4957142857142861E-2</v>
+        <v>7.4888999999999997E-2</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="4"/>
-        <v>0.14991428571428572</v>
+        <v>0.14977799999999999</v>
       </c>
       <c r="BR13">
         <f t="shared" si="4"/>
-        <v>0.22487142857142853</v>
+        <v>0.22466699999999998</v>
       </c>
       <c r="BS13">
         <f t="shared" si="4"/>
@@ -19576,11 +19599,11 @@
       </c>
       <c r="BT13">
         <f t="shared" si="9"/>
-        <v>0.13098760714285712</v>
+        <v>0.1308685275</v>
       </c>
       <c r="BU13">
         <f t="shared" si="5"/>
-        <v>0.26197521428571424</v>
+        <v>0.261737055</v>
       </c>
       <c r="BV13">
         <f t="shared" si="5"/>
@@ -19592,11 +19615,11 @@
       </c>
       <c r="BX13">
         <f t="shared" si="10"/>
-        <v>1.7989714285714282</v>
+        <v>1.7973359999999998</v>
       </c>
       <c r="BY13">
         <f t="shared" si="11"/>
-        <v>0.84270567857142853</v>
+        <v>0.84193958250000001</v>
       </c>
     </row>
     <row r="14" spans="1:87" x14ac:dyDescent="0.2">
@@ -19866,19 +19889,19 @@
       </c>
       <c r="BO14">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP14">
         <f t="shared" si="8"/>
-        <v>6.1298285714285729E-2</v>
+        <v>6.1242560000000015E-2</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="4"/>
-        <v>0.12259657142857146</v>
+        <v>0.12248512000000003</v>
       </c>
       <c r="BR14">
         <f t="shared" si="4"/>
-        <v>0.18389485714285714</v>
+        <v>0.18372768</v>
       </c>
       <c r="BS14">
         <f t="shared" si="4"/>
@@ -19886,11 +19909,11 @@
       </c>
       <c r="BT14">
         <f t="shared" si="9"/>
-        <v>0.10711875428571431</v>
+        <v>0.10702137360000002</v>
       </c>
       <c r="BU14">
         <f t="shared" si="5"/>
-        <v>0.21423750857142862</v>
+        <v>0.21404274720000005</v>
       </c>
       <c r="BV14">
         <f t="shared" si="5"/>
@@ -19902,11 +19925,11 @@
       </c>
       <c r="BX14">
         <f t="shared" si="10"/>
-        <v>1.4711588571428575</v>
+        <v>1.4698214400000005</v>
       </c>
       <c r="BY14">
         <f t="shared" si="11"/>
-        <v>0.6891459771428573</v>
+        <v>0.68851948080000014</v>
       </c>
     </row>
     <row r="15" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -20176,19 +20199,19 @@
       </c>
       <c r="BO15">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP15">
         <f t="shared" si="8"/>
-        <v>0.26475428571428578</v>
+        <v>0.26451360000000007</v>
       </c>
       <c r="BQ15">
         <f t="shared" si="4"/>
-        <v>0.19856571428571432</v>
+        <v>0.19838520000000004</v>
       </c>
       <c r="BR15">
         <f t="shared" si="4"/>
-        <v>0.13237714285714289</v>
+        <v>0.13225680000000004</v>
       </c>
       <c r="BS15">
         <f t="shared" si="4"/>
@@ -20196,11 +20219,11 @@
       </c>
       <c r="BT15">
         <f t="shared" si="9"/>
-        <v>0.70364408400000011</v>
+        <v>0.70300440756000016</v>
       </c>
       <c r="BU15">
         <f t="shared" si="5"/>
-        <v>1.791526062857143</v>
+        <v>1.7898974028000003</v>
       </c>
       <c r="BV15">
         <f t="shared" si="5"/>
@@ -20212,15 +20235,15 @@
       </c>
       <c r="BX15">
         <f t="shared" si="10"/>
-        <v>0.13237714285714289</v>
+        <v>0.13225680000000004</v>
       </c>
       <c r="BY15">
         <f t="shared" si="11"/>
-        <v>3.0908672897142857</v>
+        <v>3.0880574103600007</v>
       </c>
       <c r="BZ15">
         <f>SUM(BX15:BY18)/1000</f>
-        <v>1.6883051297734285E-2</v>
+        <v>1.6867703069281804E-2</v>
       </c>
       <c r="CA15"/>
       <c r="CB15"/>
@@ -20499,19 +20522,19 @@
       </c>
       <c r="BO16">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP16">
         <f t="shared" si="8"/>
-        <v>0.52894285714285705</v>
+        <v>0.52846199999999999</v>
       </c>
       <c r="BQ16">
         <f t="shared" si="4"/>
-        <v>0.39670714285714276</v>
+        <v>0.39634649999999993</v>
       </c>
       <c r="BR16">
         <f t="shared" si="4"/>
-        <v>0.26447142857142852</v>
+        <v>0.26423099999999999</v>
       </c>
       <c r="BS16">
         <f t="shared" si="4"/>
@@ -20519,11 +20542,11 @@
       </c>
       <c r="BT16">
         <f t="shared" si="9"/>
-        <v>1.4057846549999997</v>
+        <v>1.4045066689499999</v>
       </c>
       <c r="BU16">
         <f t="shared" si="5"/>
-        <v>3.5792240785714271</v>
+        <v>3.5759702384999987</v>
       </c>
       <c r="BV16">
         <f t="shared" si="5"/>
@@ -20535,11 +20558,11 @@
       </c>
       <c r="BX16">
         <f t="shared" si="10"/>
-        <v>0.26447142857142852</v>
+        <v>0.26423099999999999</v>
       </c>
       <c r="BY16">
         <f t="shared" si="11"/>
-        <v>6.1751301621428549</v>
+        <v>6.1695164074499989</v>
       </c>
     </row>
     <row r="17" spans="1:87" x14ac:dyDescent="0.2">
@@ -20809,19 +20832,19 @@
       </c>
       <c r="BO17">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP17">
         <f t="shared" si="8"/>
-        <v>0.2723942571428572</v>
+        <v>0.27214662600000006</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="4"/>
-        <v>0.20429569285714283</v>
+        <v>0.20410996949999999</v>
       </c>
       <c r="BR17">
         <f t="shared" si="4"/>
-        <v>0.1361971285714286</v>
+        <v>0.13607331300000003</v>
       </c>
       <c r="BS17">
         <f t="shared" si="4"/>
@@ -20829,11 +20852,11 @@
       </c>
       <c r="BT17">
         <f t="shared" si="9"/>
-        <v>0.72394902706499997</v>
+        <v>0.72329089158585003</v>
       </c>
       <c r="BU17">
         <f t="shared" si="5"/>
-        <v>1.8432238395214284</v>
+        <v>1.8415481814855001</v>
       </c>
       <c r="BV17">
         <f t="shared" si="5"/>
@@ -20845,11 +20868,11 @@
       </c>
       <c r="BX17">
         <f t="shared" si="10"/>
-        <v>0.1361971285714286</v>
+        <v>0.13607331300000003</v>
       </c>
       <c r="BY17">
         <f t="shared" si="11"/>
-        <v>3.1800599451578568</v>
+        <v>3.1771689815713504</v>
       </c>
     </row>
     <row r="18" spans="1:87" x14ac:dyDescent="0.2">
@@ -21119,19 +21142,19 @@
       </c>
       <c r="BO18">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP18">
         <f t="shared" si="8"/>
-        <v>0.32066665714285719</v>
+        <v>0.32037514200000006</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="4"/>
-        <v>0.24049999285714285</v>
+        <v>0.24028135650000002</v>
       </c>
       <c r="BR18">
         <f t="shared" si="4"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BS18">
         <f t="shared" si="4"/>
@@ -21139,11 +21162,11 @@
       </c>
       <c r="BT18">
         <f t="shared" si="9"/>
-        <v>0.85224379135500006</v>
+        <v>0.85146902427195015</v>
       </c>
       <c r="BU18">
         <f t="shared" si="5"/>
-        <v>2.1698711022214283</v>
+        <v>2.1678984921284998</v>
       </c>
       <c r="BV18">
         <f t="shared" si="5"/>
@@ -21155,11 +21178,11 @@
       </c>
       <c r="BX18">
         <f t="shared" si="10"/>
-        <v>0.1603333285714286</v>
+        <v>0.16018757100000003</v>
       </c>
       <c r="BY18">
         <f t="shared" si="11"/>
-        <v>3.743614872147857</v>
+        <v>3.7402115859004503</v>
       </c>
     </row>
     <row r="19" spans="1:87" x14ac:dyDescent="0.2">
@@ -21429,7 +21452,7 @@
       </c>
       <c r="BO19">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP19">
         <f t="shared" si="8"/>
@@ -21437,7 +21460,7 @@
       </c>
       <c r="BQ19">
         <f t="shared" si="4"/>
-        <v>0.84236389232914277</v>
+        <v>0.84159810697248005</v>
       </c>
       <c r="BR19">
         <f t="shared" si="4"/>
@@ -21453,7 +21476,7 @@
       </c>
       <c r="BU19">
         <f t="shared" si="5"/>
-        <v>7.9940333382035638</v>
+        <v>7.9867660351688334</v>
       </c>
       <c r="BV19">
         <f t="shared" si="5"/>
@@ -21465,15 +21488,15 @@
       </c>
       <c r="BX19">
         <f t="shared" si="10"/>
-        <v>0.56157592821942848</v>
+        <v>0.56106540464831989</v>
       </c>
       <c r="BY19">
         <f t="shared" si="11"/>
-        <v>8.8363972305327074</v>
+        <v>8.8283641421413144</v>
       </c>
       <c r="BZ19">
         <f>SUM(BX19:BY22)/1000</f>
-        <v>4.0435288549060339E-2</v>
+        <v>4.0398529195833921E-2</v>
       </c>
     </row>
     <row r="20" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -21743,7 +21766,7 @@
       </c>
       <c r="BO20">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP20">
         <f t="shared" si="8"/>
@@ -21751,7 +21774,7 @@
       </c>
       <c r="BQ20">
         <f t="shared" si="4"/>
-        <v>1.1140768965970282</v>
+        <v>1.1130640994183039</v>
       </c>
       <c r="BR20">
         <f t="shared" si="4"/>
@@ -21767,7 +21790,7 @@
       </c>
       <c r="BU20">
         <f t="shared" si="5"/>
-        <v>10.5725897487058</v>
+        <v>10.562978303479705</v>
       </c>
       <c r="BV20">
         <f t="shared" si="5"/>
@@ -21779,11 +21802,11 @@
       </c>
       <c r="BX20">
         <f t="shared" si="10"/>
-        <v>0.74271793106468564</v>
+        <v>0.74204273294553602</v>
       </c>
       <c r="BY20">
         <f t="shared" si="11"/>
-        <v>11.686666645302829</v>
+        <v>11.676042402898009</v>
       </c>
       <c r="BZ20"/>
       <c r="CA20"/>
@@ -22063,7 +22086,7 @@
       </c>
       <c r="BO21">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP21">
         <f t="shared" si="8"/>
@@ -22071,7 +22094,7 @@
       </c>
       <c r="BQ21">
         <f t="shared" si="4"/>
-        <v>0.71879709595885699</v>
+        <v>0.71814364405343989</v>
       </c>
       <c r="BR21">
         <f t="shared" si="4"/>
@@ -22087,7 +22110,7 @@
       </c>
       <c r="BU21">
         <f t="shared" si="5"/>
-        <v>6.8213844406495525</v>
+        <v>6.8151831820671438</v>
       </c>
       <c r="BV21">
         <f t="shared" si="5"/>
@@ -22099,11 +22122,11 @@
       </c>
       <c r="BX21">
         <f t="shared" si="10"/>
-        <v>0.47919806397257136</v>
+        <v>0.47876242936895996</v>
       </c>
       <c r="BY21">
         <f t="shared" si="11"/>
-        <v>7.5401815366084097</v>
+        <v>7.5333268261205841</v>
       </c>
     </row>
     <row r="22" spans="1:87" x14ac:dyDescent="0.2">
@@ -22373,7 +22396,7 @@
       </c>
       <c r="BO22">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP22">
         <f t="shared" si="8"/>
@@ -22381,7 +22404,7 @@
       </c>
       <c r="BQ22">
         <f t="shared" si="4"/>
-        <v>0.94907838781234299</v>
+        <v>0.94821558927796812</v>
       </c>
       <c r="BR22">
         <f t="shared" si="4"/>
@@ -22397,7 +22420,7 @@
       </c>
       <c r="BU22">
         <f t="shared" si="5"/>
-        <v>9.0067539003391364</v>
+        <v>8.9985659422479181</v>
       </c>
       <c r="BV22">
         <f t="shared" si="5"/>
@@ -22409,11 +22432,11 @@
       </c>
       <c r="BX22">
         <f t="shared" si="10"/>
-        <v>0.63271892520822859</v>
+        <v>0.63214372618531212</v>
       </c>
       <c r="BY22">
         <f t="shared" si="11"/>
-        <v>9.9558322881514787</v>
+        <v>9.9467815315258861</v>
       </c>
     </row>
     <row r="23" spans="1:87" x14ac:dyDescent="0.2">
@@ -22683,11 +22706,11 @@
       </c>
       <c r="BO23">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP23">
         <f t="shared" si="8"/>
-        <v>4.9429527085714298E-2</v>
+        <v>4.9384591152000015E-2</v>
       </c>
       <c r="BQ23">
         <f t="shared" si="4"/>
@@ -22707,7 +22730,7 @@
       </c>
       <c r="BU23">
         <f t="shared" si="5"/>
-        <v>0.31096115489622866</v>
+        <v>0.31067846293723211</v>
       </c>
       <c r="BV23">
         <f t="shared" si="5"/>
@@ -22719,15 +22742,15 @@
       </c>
       <c r="BX23">
         <f t="shared" si="10"/>
-        <v>0.88973148754285736</v>
+        <v>0.88892264073600025</v>
       </c>
       <c r="BY23">
         <f t="shared" si="11"/>
-        <v>0.36039068198194296</v>
+        <v>0.36006305408923212</v>
       </c>
       <c r="BZ23">
         <f>SUM(BX23:BY26)/1000</f>
-        <v>5.6073058181976007E-3</v>
+        <v>5.6022082674537848E-3</v>
       </c>
     </row>
     <row r="24" spans="1:87" x14ac:dyDescent="0.2">
@@ -22997,11 +23020,11 @@
       </c>
       <c r="BO24">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP24">
         <f t="shared" si="8"/>
-        <v>7.8230917851428564E-2</v>
+        <v>7.8159798835199995E-2</v>
       </c>
       <c r="BQ24">
         <f t="shared" si="4"/>
@@ -23021,7 +23044,7 @@
       </c>
       <c r="BU24">
         <f t="shared" si="5"/>
-        <v>0.49215070420333717</v>
+        <v>0.49170329447224326</v>
       </c>
       <c r="BV24">
         <f t="shared" si="5"/>
@@ -23033,11 +23056,11 @@
       </c>
       <c r="BX24">
         <f t="shared" si="10"/>
-        <v>1.4081565213257141</v>
+        <v>1.4068763790335999</v>
       </c>
       <c r="BY24">
         <f t="shared" si="11"/>
-        <v>0.57038162205476572</v>
+        <v>0.56986309330744322</v>
       </c>
     </row>
     <row r="25" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -23307,11 +23330,11 @@
       </c>
       <c r="BO25">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP25">
         <f t="shared" si="8"/>
-        <v>4.1290711817142861E-2</v>
+        <v>4.1253174806400006E-2</v>
       </c>
       <c r="BQ25">
         <f t="shared" si="4"/>
@@ -23331,7 +23354,7 @@
       </c>
       <c r="BU25">
         <f t="shared" si="5"/>
-        <v>0.25975986804164569</v>
+        <v>0.25952372270706242</v>
       </c>
       <c r="BV25">
         <f t="shared" si="5"/>
@@ -23343,11 +23366,11 @@
       </c>
       <c r="BX25">
         <f t="shared" si="10"/>
-        <v>0.74323281270857144</v>
+        <v>0.7425571465152</v>
       </c>
       <c r="BY25">
         <f t="shared" si="11"/>
-        <v>0.30105057985878858</v>
+        <v>0.30077689751346243</v>
       </c>
       <c r="BZ25"/>
       <c r="CA25"/>
@@ -23627,11 +23650,11 @@
       </c>
       <c r="BO26">
         <f>Constants!$J$2</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP26">
         <f t="shared" si="8"/>
-        <v>5.2760353988571415E-2</v>
+        <v>5.2712390030399993E-2</v>
       </c>
       <c r="BQ26">
         <f t="shared" si="4"/>
@@ -23651,7 +23674,7 @@
       </c>
       <c r="BU26">
         <f t="shared" si="5"/>
-        <v>0.33191538694210282</v>
+        <v>0.33161364568124641</v>
       </c>
       <c r="BV26">
         <f t="shared" si="5"/>
@@ -23663,11 +23686,11 @@
       </c>
       <c r="BX26">
         <f t="shared" si="10"/>
-        <v>0.94968637179428561</v>
+        <v>0.94882302054720002</v>
       </c>
       <c r="BY26">
         <f t="shared" si="11"/>
-        <v>0.38467574093067425</v>
+        <v>0.38432603571164642</v>
       </c>
     </row>
     <row r="30" spans="1:87" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -24430,19 +24453,19 @@
       </c>
       <c r="BY11">
         <f>IF(BU11="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ11">
         <f>BU11*BX11*BY11</f>
-        <v>0.22923203552228569</v>
+        <v>0.22902364276272</v>
       </c>
       <c r="CA11">
         <f>BW11*BX11*BY11</f>
-        <v>0.10094198400000001</v>
+        <v>0.10085021856000001</v>
       </c>
       <c r="CB11">
         <f>SUM(BZ11:CA14)/1000</f>
-        <v>1.4487119534674284E-3</v>
+        <v>1.44739494260064E-3</v>
       </c>
     </row>
     <row r="12" spans="1:88" x14ac:dyDescent="0.2">
@@ -24752,15 +24775,15 @@
       </c>
       <c r="BY12">
         <f>IF(BU12="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ12">
         <f t="shared" ref="BZ12:BZ26" si="26">BU12*BX12*BY12</f>
-        <v>0.28721666847908567</v>
+        <v>0.28695556241683196</v>
       </c>
       <c r="CA12">
         <f t="shared" ref="CA12:CA26" si="27">BW12*BX12*BY12</f>
-        <v>0.12647543040000001</v>
+        <v>0.126360452736</v>
       </c>
     </row>
     <row r="13" spans="1:88" x14ac:dyDescent="0.2">
@@ -25070,15 +25093,15 @@
       </c>
       <c r="BY13">
         <f>IF(BU13="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ13">
         <f t="shared" si="26"/>
-        <v>0.24467892073302858</v>
+        <v>0.24445648535054401</v>
       </c>
       <c r="CA13">
         <f t="shared" si="27"/>
-        <v>0.10774399679999999</v>
+        <v>0.107646047712</v>
       </c>
     </row>
     <row r="14" spans="1:88" x14ac:dyDescent="0.2">
@@ -25388,15 +25411,15 @@
       </c>
       <c r="BY14">
         <f>IF(BU14="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ14">
         <f t="shared" si="26"/>
-        <v>0.24467892073302858</v>
+        <v>0.24445648535054401</v>
       </c>
       <c r="CA14">
         <f t="shared" si="27"/>
-        <v>0.10774399679999999</v>
+        <v>0.107646047712</v>
       </c>
     </row>
     <row r="15" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -25706,19 +25729,19 @@
       </c>
       <c r="BY15">
         <f>IF(BU15="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ15">
         <f t="shared" si="26"/>
-        <v>1.454032477755</v>
+        <v>1.4527106300479502</v>
       </c>
       <c r="CA15">
         <f t="shared" si="27"/>
-        <v>0.110405295</v>
+        <v>0.11030492655000002</v>
       </c>
       <c r="CB15">
         <f>SUM(BZ15:CA18)/1000</f>
-        <v>6.8643187163099986E-3</v>
+        <v>6.8580784265679E-3</v>
       </c>
       <c r="CC15"/>
       <c r="CD15"/>
@@ -26036,15 +26059,15 @@
       </c>
       <c r="BY16">
         <f>IF(BU16="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ16">
         <f t="shared" si="26"/>
-        <v>1.8218324640779997</v>
+        <v>1.8201762527470198</v>
       </c>
       <c r="CA16">
         <f t="shared" si="27"/>
-        <v>0.138332502</v>
+        <v>0.13820674517999998</v>
       </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.2">
@@ -26354,15 +26377,15 @@
       </c>
       <c r="BY17">
         <f>IF(BU17="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ17">
         <f t="shared" si="26"/>
-        <v>1.5520129922385</v>
+        <v>1.550602071336465</v>
       </c>
       <c r="CA17">
         <f t="shared" si="27"/>
-        <v>0.11784499650000002</v>
+        <v>0.11773786468500003</v>
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.2">
@@ -26672,15 +26695,15 @@
       </c>
       <c r="BY18">
         <f>IF(BU18="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ18">
         <f t="shared" si="26"/>
-        <v>1.5520129922385</v>
+        <v>1.550602071336465</v>
       </c>
       <c r="CA18">
         <f t="shared" si="27"/>
-        <v>0.11784499650000002</v>
+        <v>0.11773786468500003</v>
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.2">
@@ -26990,19 +27013,19 @@
       </c>
       <c r="BY19">
         <f>IF(BU19="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ19">
         <f t="shared" si="26"/>
-        <v>1.1982619442278943</v>
+        <v>1.1971726151876874</v>
       </c>
       <c r="CA19">
         <f t="shared" si="27"/>
-        <v>0.12240795302049601</v>
+        <v>0.12229667306320466</v>
       </c>
       <c r="CB19">
         <f>SUM(BZ19:CA22)/1000</f>
-        <v>5.7947329396073341E-3</v>
+        <v>5.7894650005713266E-3</v>
       </c>
     </row>
     <row r="20" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -27312,15 +27335,15 @@
       </c>
       <c r="BY20">
         <f>IF(BU20="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ20">
         <f t="shared" si="26"/>
-        <v>1.5013643394225709</v>
+        <v>1.4999994627503686</v>
       </c>
       <c r="CA20">
         <f t="shared" si="27"/>
-        <v>0.15337125276485761</v>
+        <v>0.15323182435325319</v>
       </c>
       <c r="CB20"/>
       <c r="CC20"/>
@@ -27639,15 +27662,15 @@
       </c>
       <c r="BY21">
         <f>IF(BU21="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ21">
         <f t="shared" si="26"/>
-        <v>1.2790072670302579</v>
+        <v>1.2778445331511397</v>
       </c>
       <c r="CA21">
         <f t="shared" si="27"/>
-        <v>0.13065645805549922</v>
+        <v>0.13053767945726694</v>
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.2">
@@ -27957,15 +27980,15 @@
       </c>
       <c r="BY22">
         <f>IF(BU22="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ22">
         <f t="shared" si="26"/>
-        <v>1.2790072670302579</v>
+        <v>1.2778445331511397</v>
       </c>
       <c r="CA22">
         <f t="shared" si="27"/>
-        <v>0.13065645805549922</v>
+        <v>0.13053767945726694</v>
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.2">
@@ -28275,19 +28298,19 @@
       </c>
       <c r="BY23">
         <f>IF(BU23="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ23">
         <f t="shared" si="26"/>
-        <v>0.16009235232521146</v>
+        <v>0.15994681382309764</v>
       </c>
       <c r="CA23">
         <f t="shared" si="27"/>
-        <v>0.74737444953600007</v>
+        <v>0.74669501821824014</v>
       </c>
       <c r="CB23">
         <f>SUM(BZ23:CA26)/1000</f>
-        <v>3.9817124470705369E-3</v>
+        <v>3.978092708482291E-3</v>
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.2">
@@ -28597,15 +28620,15 @@
       </c>
       <c r="BY24">
         <f>IF(BU24="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ24">
         <f t="shared" si="26"/>
-        <v>0.20058798491695537</v>
+        <v>0.2004056322033945</v>
       </c>
       <c r="CA24">
         <f t="shared" si="27"/>
-        <v>0.93642408668159982</v>
+        <v>0.93557279205734378</v>
       </c>
     </row>
     <row r="25" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -28915,15 +28938,15 @@
       </c>
       <c r="BY25">
         <f>IF(BU25="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ25">
         <f t="shared" si="26"/>
-        <v>0.1708802344981851</v>
+        <v>0.17072488883045947</v>
       </c>
       <c r="CA25">
         <f t="shared" si="27"/>
-        <v>0.79773655230719998</v>
+        <v>0.79701133725964801</v>
       </c>
       <c r="CB25"/>
       <c r="CC25"/>
@@ -29242,15 +29265,15 @@
       </c>
       <c r="BY26">
         <f>IF(BU26="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ26">
         <f t="shared" si="26"/>
-        <v>0.1708802344981851</v>
+        <v>0.17072488883045947</v>
       </c>
       <c r="CA26">
         <f t="shared" si="27"/>
-        <v>0.79773655230719998</v>
+        <v>0.79701133725964801</v>
       </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.2">
@@ -30100,19 +30123,19 @@
       </c>
       <c r="BY11">
         <f>IF(BU11="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ11">
         <f>BU11*BX11*BY11</f>
-        <v>0.22519175862857141</v>
+        <v>0.224987038848</v>
       </c>
       <c r="CA11">
         <f>BW11*BX11*BY11</f>
-        <v>0.10872576</v>
+        <v>0.10862691840000001</v>
       </c>
       <c r="CB11">
         <f>SUM(BZ11:CA14)/1000</f>
-        <v>1.3437553151314288E-3</v>
+        <v>1.3425337193904003E-3</v>
       </c>
     </row>
     <row r="12" spans="1:88" x14ac:dyDescent="0.2">
@@ -30422,15 +30445,15 @@
       </c>
       <c r="BY12">
         <f>IF(BU12="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ12">
         <f t="shared" ref="BZ12:BZ26" si="12">BU12*BX12*BY12</f>
-        <v>0.25432495817142864</v>
+        <v>0.25409375366400005</v>
       </c>
       <c r="CA12">
         <f t="shared" ref="CA12:CA26" si="13">BW12*BX12*BY12</f>
-        <v>0.12279168</v>
+        <v>0.1226800512</v>
       </c>
     </row>
     <row r="13" spans="1:88" x14ac:dyDescent="0.2">
@@ -30740,15 +30763,15 @@
       </c>
       <c r="BY13">
         <f>IF(BU13="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ13">
         <f t="shared" si="12"/>
-        <v>0.23473878685714286</v>
+        <v>0.23452538796000003</v>
       </c>
       <c r="CA13">
         <f t="shared" si="13"/>
-        <v>0.11333519999999998</v>
+        <v>0.11323216799999999</v>
       </c>
     </row>
     <row r="14" spans="1:88" x14ac:dyDescent="0.2">
@@ -31058,15 +31081,15 @@
       </c>
       <c r="BY14">
         <f>IF(BU14="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ14">
         <f t="shared" si="12"/>
-        <v>0.19196416347428572</v>
+        <v>0.19178965059840003</v>
       </c>
       <c r="CA14">
         <f t="shared" si="13"/>
-        <v>9.2683008000000011E-2</v>
+        <v>9.2598750720000025E-2</v>
       </c>
     </row>
     <row r="15" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -31376,19 +31399,19 @@
       </c>
       <c r="BY15">
         <f>IF(BU15="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ15">
         <f t="shared" si="12"/>
-        <v>1.4439719923200003</v>
+        <v>1.4426592905088003</v>
       </c>
       <c r="CA15">
         <f t="shared" si="13"/>
-        <v>9.7297200000000028E-2</v>
+        <v>9.7208748000000025E-2</v>
       </c>
       <c r="CB15">
         <f>SUM(BZ15:CA18)/1000</f>
-        <v>8.073023123721601E-3</v>
+        <v>8.065684011790945E-3</v>
       </c>
       <c r="CC15"/>
       <c r="CD15"/>
@@ -31706,15 +31729,15 @@
       </c>
       <c r="BY16">
         <f>IF(BU16="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ16">
         <f t="shared" si="12"/>
-        <v>2.8848585743999995</v>
+        <v>2.8822359756959997</v>
       </c>
       <c r="CA16">
         <f t="shared" si="13"/>
-        <v>0.19438649999999999</v>
+        <v>0.194209785</v>
       </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.2">
@@ -32024,15 +32047,15 @@
       </c>
       <c r="BY17">
         <f>IF(BU17="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ17">
         <f t="shared" si="12"/>
-        <v>1.4856404576112003</v>
+        <v>1.4842898753770084</v>
       </c>
       <c r="CA17">
         <f t="shared" si="13"/>
-        <v>0.10010488950000003</v>
+        <v>0.10001388505500003</v>
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.2">
@@ -32342,15 +32365,15 @@
       </c>
       <c r="BY18">
         <f>IF(BU18="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ18">
         <f t="shared" si="12"/>
-        <v>1.7489185133903999</v>
+        <v>1.747328587469136</v>
       </c>
       <c r="CA18">
         <f t="shared" si="13"/>
-        <v>0.11784499650000002</v>
+        <v>0.11773786468500003</v>
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.2">
@@ -32660,19 +32683,19 @@
       </c>
       <c r="BY19">
         <f>IF(BU19="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ19">
         <f t="shared" si="12"/>
-        <v>1.1917932821451178</v>
+        <v>1.1907098337068041</v>
       </c>
       <c r="CA19">
         <f t="shared" si="13"/>
-        <v>0.11596542917731199</v>
+        <v>0.11586000605987808</v>
       </c>
       <c r="CB19">
         <f>SUM(BZ19:CA22)/1000</f>
-        <v>5.6267026891457005E-3</v>
+        <v>5.6215875048828395E-3</v>
       </c>
     </row>
     <row r="20" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -32982,15 +33005,15 @@
       </c>
       <c r="BY20">
         <f>IF(BU20="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ20">
         <f t="shared" si="12"/>
-        <v>1.5762182748434077</v>
+        <v>1.5747853491390047</v>
       </c>
       <c r="CA20">
         <f t="shared" si="13"/>
-        <v>0.15337125276485761</v>
+        <v>0.15323182435325319</v>
       </c>
       <c r="CB20"/>
       <c r="CC20"/>
@@ -33309,15 +33332,15 @@
       </c>
       <c r="BY21">
         <f>IF(BU21="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ21">
         <f t="shared" si="12"/>
-        <v>1.0169685073045098</v>
+        <v>1.0160439904796876</v>
       </c>
       <c r="CA21">
         <f t="shared" si="13"/>
-        <v>9.8954400210335983E-2</v>
+        <v>9.8864441664690231E-2</v>
       </c>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.2">
@@ -33627,15 +33650,15 @@
       </c>
       <c r="BY22">
         <f>IF(BU22="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ22">
         <f t="shared" si="12"/>
-        <v>1.3427750846446593</v>
+        <v>1.3415543800222551</v>
       </c>
       <c r="CA22">
         <f t="shared" si="13"/>
-        <v>0.13065645805549922</v>
+        <v>0.13053767945726694</v>
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.2">
@@ -33945,19 +33968,19 @@
       </c>
       <c r="BY23">
         <f>IF(BU23="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ23">
         <f t="shared" si="12"/>
-        <v>0.16838464978911089</v>
+        <v>0.16823157283475715</v>
       </c>
       <c r="CA23">
         <f t="shared" si="13"/>
-        <v>0.74737444953600007</v>
+        <v>0.74669501821824014</v>
       </c>
       <c r="CB23">
         <f>SUM(BZ23:CA26)/1000</f>
-        <v>4.1075516064681865E-3</v>
+        <v>4.1038174686441253E-3</v>
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.2">
@@ -34267,15 +34290,15 @@
       </c>
       <c r="BY24">
         <f>IF(BU24="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ24">
         <f t="shared" si="12"/>
-        <v>0.26649831551596248</v>
+        <v>0.26625604432003885</v>
       </c>
       <c r="CA24">
         <f t="shared" si="13"/>
-        <v>1.1828514779135999</v>
+        <v>1.181776158388224</v>
       </c>
     </row>
     <row r="25" spans="1:88" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -34585,15 +34608,15 @@
       </c>
       <c r="BY25">
         <f>IF(BU25="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ25">
         <f t="shared" si="12"/>
-        <v>0.14065928724780619</v>
+        <v>0.14053141516849002</v>
       </c>
       <c r="CA25">
         <f t="shared" si="13"/>
-        <v>0.62431556267519994</v>
+        <v>0.62374800307276801</v>
       </c>
       <c r="CB25"/>
       <c r="CC25"/>
@@ -34912,15 +34935,15 @@
       </c>
       <c r="BY26">
         <f>IF(BU26="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BZ26">
         <f t="shared" si="12"/>
-        <v>0.17973131148330784</v>
+        <v>0.1795679193819594</v>
       </c>
       <c r="CA26">
         <f t="shared" si="13"/>
-        <v>0.79773655230719998</v>
+        <v>0.79701133725964801</v>
       </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.2">
@@ -35701,19 +35724,19 @@
       </c>
       <c r="BO11">
         <f>IF(BJ11="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP11">
         <f>BL11*$BN11*$BO11</f>
-        <v>9.6804163782857142E-3</v>
+        <v>9.6716159997600002E-3</v>
       </c>
       <c r="BQ11">
         <f>BM11*$BN11*$BO11</f>
-        <v>5.8749302857142874E-2</v>
+        <v>5.8695894400000018E-2</v>
       </c>
       <c r="BR11">
         <f>SUM(BP11:BQ14)/1000</f>
-        <v>3.0025061442514293E-4</v>
+        <v>2.9997765932112004E-4</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.2">
@@ -35983,15 +36006,15 @@
       </c>
       <c r="BO12">
         <f>IF(BJ12="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BP26" si="9">BL12*$BN12*$BO12</f>
-        <v>1.2129094152685713E-2</v>
+        <v>1.2118067703455998E-2</v>
       </c>
       <c r="BQ12">
         <f t="shared" ref="BQ12:BQ26" si="10">BM12*$BN12*$BO12</f>
-        <v>7.3610038857142845E-2</v>
+        <v>7.3543120640000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.2">
@@ -36261,15 +36284,15 @@
       </c>
       <c r="BO13">
         <f>IF(BJ13="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP13">
         <f t="shared" si="9"/>
-        <v>1.0332734804228571E-2</v>
+        <v>1.0323341408951999E-2</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="10"/>
-        <v>6.2708146285714292E-2</v>
+        <v>6.2651138880000012E-2</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.2">
@@ -36539,15 +36562,15 @@
       </c>
       <c r="BO14">
         <f>IF(BJ14="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP14">
         <f t="shared" si="9"/>
-        <v>1.0332734804228571E-2</v>
+        <v>1.0323341408951999E-2</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="10"/>
-        <v>6.2708146285714292E-2</v>
+        <v>6.2651138880000012E-2</v>
       </c>
     </row>
     <row r="15" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -36817,19 +36840,19 @@
       </c>
       <c r="BO15">
         <f>IF(BJ15="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP15">
         <f t="shared" si="9"/>
-        <v>2.2607098922571425E-2</v>
+        <v>2.2586547014459998E-2</v>
       </c>
       <c r="BQ15">
         <f t="shared" si="10"/>
-        <v>1.6523241428571429E-2</v>
+        <v>1.6508220300000001E-2</v>
       </c>
       <c r="BR15">
         <f>SUM(BP15:BQ18)/1000</f>
-        <v>1.7169307231371426E-4</v>
+        <v>1.7153698770252E-4</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.2">
@@ -37099,15 +37122,15 @@
       </c>
       <c r="BO16">
         <f>IF(BJ16="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP16">
         <f t="shared" si="9"/>
-        <v>2.8325603014971414E-2</v>
+        <v>2.8299852466775986E-2</v>
       </c>
       <c r="BQ16">
         <f t="shared" si="10"/>
-        <v>2.0702823428571427E-2</v>
+        <v>2.0684002679999997E-2</v>
       </c>
     </row>
     <row r="17" spans="1:70" x14ac:dyDescent="0.2">
@@ -37377,15 +37400,15 @@
       </c>
       <c r="BO17">
         <f>IF(BJ17="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP17">
         <f t="shared" si="9"/>
-        <v>2.4130486616657142E-2</v>
+        <v>2.4108549810642001E-2</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="10"/>
-        <v>1.7636666142857145E-2</v>
+        <v>1.7620632810000005E-2</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.2">
@@ -37655,15 +37678,15 @@
       </c>
       <c r="BO18">
         <f>IF(BJ18="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP18">
         <f t="shared" si="9"/>
-        <v>2.4130486616657142E-2</v>
+        <v>2.4108549810642001E-2</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="10"/>
-        <v>1.7636666142857145E-2</v>
+        <v>1.7620632810000005E-2</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.2">
@@ -37933,19 +37956,19 @@
       </c>
       <c r="BO19">
         <f>IF(BJ19="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP19">
         <f t="shared" si="9"/>
-        <v>6.3117334334749489E-2</v>
+        <v>6.3059954939899715E-2</v>
       </c>
       <c r="BQ19">
         <f t="shared" si="10"/>
-        <v>2.1735068332937146E-2</v>
+        <v>2.1715309179907206E-2</v>
       </c>
       <c r="BR19">
         <f>SUM(BP19:BQ22)/1000</f>
-        <v>3.7230879099138802E-4</v>
+        <v>3.7197032845412317E-4</v>
       </c>
     </row>
     <row r="20" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -38215,15 +38238,15 @@
       </c>
       <c r="BO20">
         <f>IF(BJ20="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP20">
         <f t="shared" si="9"/>
-        <v>7.9082971320319384E-2</v>
+        <v>7.9011077710028188E-2</v>
       </c>
       <c r="BQ20">
         <f t="shared" si="10"/>
-        <v>2.7232990805705137E-2</v>
+        <v>2.7208233541336318E-2</v>
       </c>
       <c r="BR20"/>
     </row>
@@ -38494,15 +38517,15 @@
       </c>
       <c r="BO21">
         <f>IF(BJ21="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP21">
         <f t="shared" si="9"/>
-        <v>6.7370519174536736E-2</v>
+        <v>6.7309273248014431E-2</v>
       </c>
       <c r="BQ21">
         <f t="shared" si="10"/>
-        <v>2.3199693924301715E-2</v>
+        <v>2.3178603293461442E-2</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.2">
@@ -38772,15 +38795,15 @@
       </c>
       <c r="BO22">
         <f>IF(BJ22="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP22">
         <f t="shared" si="9"/>
-        <v>6.7370519174536736E-2</v>
+        <v>6.7309273248014431E-2</v>
       </c>
       <c r="BQ22">
         <f t="shared" si="10"/>
-        <v>2.3199693924301715E-2</v>
+        <v>2.3178603293461442E-2</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.2">
@@ -39050,7 +39073,7 @@
       </c>
       <c r="BO23">
         <f>IF(BJ23="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP23">
         <f t="shared" si="9"/>
@@ -39332,7 +39355,7 @@
       </c>
       <c r="BO24">
         <f>IF(BJ24="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP24">
         <f t="shared" si="9"/>
@@ -39610,7 +39633,7 @@
       </c>
       <c r="BO25">
         <f>IF(BJ25="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP25">
         <f t="shared" si="9"/>
@@ -39889,7 +39912,7 @@
       </c>
       <c r="BO26">
         <f>IF(BJ26="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP26">
         <f t="shared" si="9"/>
@@ -40548,19 +40571,19 @@
       </c>
       <c r="BO11">
         <f>IF(BJ11="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP11">
         <f>BL11*$BN11*$BO11</f>
-        <v>5.5290500571428579E-3</v>
+        <v>5.5240236480000012E-3</v>
       </c>
       <c r="BQ11">
         <f>BM11*$BN11*$BO11</f>
-        <v>6.3279542857142851E-2</v>
+        <v>6.3222016000000006E-2</v>
       </c>
       <c r="BR11">
         <f>SUM(BP11:BQ14)/1000</f>
-        <v>2.7690045384571427E-4</v>
+        <v>2.7664872616039998E-4</v>
       </c>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.2">
@@ -40830,15 +40853,15 @@
       </c>
       <c r="BO12">
         <f>IF(BJ12="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP12">
         <f t="shared" ref="BP12:BQ26" si="9">BL12*$BN12*$BO12</f>
-        <v>6.2443467428571434E-3</v>
+        <v>6.2386700640000006E-3</v>
       </c>
       <c r="BQ12">
         <f t="shared" si="9"/>
-        <v>7.1466057142857142E-2</v>
+        <v>7.1401088000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.2">
@@ -41108,15 +41131,15 @@
       </c>
       <c r="BO13">
         <f>IF(BJ13="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP13">
         <f t="shared" si="9"/>
-        <v>5.7634547142857134E-3</v>
+        <v>5.7582152099999997E-3</v>
       </c>
       <c r="BQ13">
         <f t="shared" si="9"/>
-        <v>6.5962285714285696E-2</v>
+        <v>6.5902319999999986E-2</v>
       </c>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.2">
@@ -41386,15 +41409,15 @@
       </c>
       <c r="BO14">
         <f>IF(BJ14="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP14">
         <f t="shared" si="9"/>
-        <v>4.713225188571429E-3</v>
+        <v>4.7089404384000012E-3</v>
       </c>
       <c r="BQ14">
         <f t="shared" si="9"/>
-        <v>5.394249142857143E-2</v>
+        <v>5.3893452800000005E-2</v>
       </c>
     </row>
     <row r="15" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -41664,19 +41687,19 @@
       </c>
       <c r="BO15">
         <f>IF(BJ15="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP15">
         <f t="shared" si="9"/>
-        <v>3.0960339696000004E-2</v>
+        <v>3.0932193932640004E-2</v>
       </c>
       <c r="BQ15">
         <f t="shared" si="9"/>
-        <v>1.4561485714285718E-2</v>
+        <v>1.4548248000000005E-2</v>
       </c>
       <c r="BR15">
         <f>SUM(BP15:BQ18)/1000</f>
-        <v>2.3843904166933713E-4</v>
+        <v>2.3822227890418323E-4</v>
       </c>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.2">
@@ -41946,15 +41969,15 @@
       </c>
       <c r="BO16">
         <f>IF(BJ16="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP16">
         <f t="shared" si="9"/>
-        <v>6.1854524819999993E-2</v>
+        <v>6.17982934338E-2</v>
       </c>
       <c r="BQ16">
         <f t="shared" si="9"/>
-        <v>2.9091857142857138E-2</v>
+        <v>2.906541E-2</v>
       </c>
     </row>
     <row r="17" spans="1:70" x14ac:dyDescent="0.2">
@@ -42224,15 +42247,15 @@
       </c>
       <c r="BO17">
         <f>IF(BJ17="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP17">
         <f t="shared" si="9"/>
-        <v>3.1853757190859998E-2</v>
+        <v>3.1824799229777399E-2</v>
       </c>
       <c r="BQ17">
         <f t="shared" si="9"/>
-        <v>1.4981684142857143E-2</v>
+        <v>1.4968064430000002E-2</v>
       </c>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.2">
@@ -42502,15 +42525,15 @@
       </c>
       <c r="BO18">
         <f>IF(BJ18="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP18">
         <f t="shared" si="9"/>
-        <v>3.749872681962E-2</v>
+        <v>3.7464637067965802E-2</v>
       </c>
       <c r="BQ18">
         <f t="shared" si="9"/>
-        <v>1.7636666142857145E-2</v>
+        <v>1.7620632810000005E-2</v>
       </c>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.2">
@@ -42780,7 +42803,7 @@
       </c>
       <c r="BO19">
         <f>IF(BJ19="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP19">
         <f t="shared" si="9"/>
@@ -42788,11 +42811,11 @@
       </c>
       <c r="BQ19">
         <f t="shared" si="9"/>
-        <v>2.0591117368045711E-2</v>
+        <v>2.0572398170438398E-2</v>
       </c>
       <c r="BR19">
         <f>SUM(BP19:BQ22)/1000</f>
-        <v>8.8594397777046855E-5</v>
+        <v>8.8513857415431363E-5</v>
       </c>
     </row>
     <row r="20" spans="1:70" s="11" customFormat="1" x14ac:dyDescent="0.2">
@@ -43062,7 +43085,7 @@
       </c>
       <c r="BO20">
         <f>IF(BJ20="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP20">
         <f t="shared" si="9"/>
@@ -43070,7 +43093,7 @@
       </c>
       <c r="BQ20">
         <f t="shared" si="9"/>
-        <v>2.7232990805705137E-2</v>
+        <v>2.7208233541336318E-2</v>
       </c>
       <c r="BR20"/>
     </row>
@@ -43341,7 +43364,7 @@
       </c>
       <c r="BO21">
         <f>IF(BJ21="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP21">
         <f t="shared" si="9"/>
@@ -43349,7 +43372,7 @@
       </c>
       <c r="BQ21">
         <f t="shared" si="9"/>
-        <v>1.7570595678994282E-2</v>
+        <v>1.75546224101952E-2</v>
       </c>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.2">
@@ -43619,7 +43642,7 @@
       </c>
       <c r="BO22">
         <f>IF(BJ22="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP22">
         <f t="shared" si="9"/>
@@ -43627,7 +43650,7 @@
       </c>
       <c r="BQ22">
         <f t="shared" si="9"/>
-        <v>2.3199693924301715E-2</v>
+        <v>2.3178603293461442E-2</v>
       </c>
     </row>
     <row r="23" spans="1:70" x14ac:dyDescent="0.2">
@@ -43897,7 +43920,7 @@
       </c>
       <c r="BO23">
         <f>IF(BJ23="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP23">
         <f t="shared" si="9"/>
@@ -44179,7 +44202,7 @@
       </c>
       <c r="BO24">
         <f>IF(BJ24="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP24">
         <f t="shared" si="9"/>
@@ -44457,7 +44480,7 @@
       </c>
       <c r="BO25">
         <f>IF(BJ25="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP25">
         <f t="shared" si="9"/>
@@ -44736,7 +44759,7 @@
       </c>
       <c r="BO26">
         <f>IF(BJ26="","",Constants!$J$2)</f>
-        <v>1.5714285714285714</v>
+        <v>1.57</v>
       </c>
       <c r="BP26">
         <f t="shared" si="9"/>
